--- a/excel files/Part_Qualification_FF_Tracker_2026.xlsx
+++ b/excel files/Part_Qualification_FF_Tracker_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nutreco1-my.sharepoint.com/personal/hari_bojja_eruvaka_com/Documents/Desktop/VV_dashboard/excel files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nutreco1.sharepoint.com/sites/ProductDesign/Shared Documents/Product Engineering/PE_Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{70FBDE81-E981-4D6F-A42E-7D28A214AADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-2760" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="5" state="hidden" r:id="rId1"/>
@@ -1490,7 +1490,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2842,38 +2842,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2882,6 +2850,75 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2940,24 +2977,6 @@
     <xf numFmtId="0" fontId="31" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="14" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2967,47 +2986,26 @@
     <xf numFmtId="0" fontId="32" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3033,6 +3031,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="20% - Accent1" xfId="2" builtinId="30"/>
@@ -3242,7 +3242,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3728,7 +3728,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4128,7 +4128,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4528,7 +4528,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4928,7 +4928,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8452,25 +8452,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28093AD-9BA0-41A7-AE2B-B036016F0F5C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" customWidth="1"/>
-    <col min="2" max="2" width="66.7265625" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" customWidth="1"/>
+    <col min="2" max="2" width="66.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="117" t="s">
+    <row r="1" spans="1:2" ht="48" customHeight="1">
+      <c r="A1" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="118" t="s">
+      <c r="B1" s="180"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="118"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B2" s="181"/>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="61" t="s">
         <v>2</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" s="62" t="s">
         <v>4</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" s="62" t="s">
         <v>6</v>
       </c>
@@ -8494,7 +8494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" s="62" t="s">
         <v>8</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" s="62" t="s">
         <v>10</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" s="64" t="s">
         <v>12</v>
       </c>
@@ -8530,302 +8530,302 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088C5475-CFD5-4F00-BF8C-4260C487A5C9}">
   <dimension ref="A1:S58"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.26953125" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.54296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" style="15" customWidth="1"/>
-    <col min="5" max="9" width="9.54296875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="9.453125" style="15" customWidth="1"/>
-    <col min="11" max="18" width="9.54296875" style="15" customWidth="1"/>
-    <col min="19" max="19" width="9.1796875" style="15" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="15" customWidth="1"/>
+    <col min="5" max="9" width="9.5703125" style="15" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" style="15" customWidth="1"/>
+    <col min="11" max="18" width="9.5703125" style="15" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="15" hidden="1" customWidth="1"/>
     <col min="20" max="16384" width="0" style="15" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="161" t="s">
+    <row r="1" spans="1:18" ht="48" customHeight="1">
+      <c r="A1" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="162"/>
-      <c r="C1" s="162"/>
-      <c r="D1" s="162"/>
-      <c r="E1" s="162"/>
-      <c r="F1" s="162"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="162"/>
-      <c r="I1" s="162"/>
-      <c r="J1" s="162"/>
-      <c r="K1" s="162"/>
-      <c r="L1" s="162"/>
-      <c r="M1" s="162"/>
-      <c r="N1" s="162"/>
-      <c r="O1" s="162"/>
-      <c r="P1" s="162"/>
-      <c r="Q1" s="162"/>
-      <c r="R1" s="163"/>
-    </row>
-    <row r="2" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="164" t="str">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="123"/>
+    </row>
+    <row r="2" spans="1:18" ht="14.45">
+      <c r="A2" s="124" t="str">
         <f ca="1">"Live view from FF_2026 • Updated "&amp;TEXT(NOW(),"dd-mmm-yyyy hh:mm")</f>
-        <v>Live view from FF_2026 • Updated 28-Sep-2026 05:54</v>
-      </c>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
-      <c r="I2" s="165"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="165"/>
-      <c r="L2" s="165"/>
-      <c r="M2" s="165"/>
-      <c r="N2" s="165"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="165"/>
-      <c r="Q2" s="165"/>
-      <c r="R2" s="166"/>
-    </row>
-    <row r="3" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="170"/>
-      <c r="B3" s="171"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="171"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
-      <c r="I3" s="171"/>
-      <c r="J3" s="171"/>
-      <c r="K3" s="171"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="171"/>
-      <c r="N3" s="171"/>
-      <c r="O3" s="171"/>
-      <c r="P3" s="171"/>
-      <c r="Q3" s="171"/>
-      <c r="R3" s="172"/>
-    </row>
-    <row r="4" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="167" t="s">
+        <v>Live view from FF_2026 • Updated 25-Sep-2026 15:14</v>
+      </c>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="126"/>
+    </row>
+    <row r="3" spans="1:18" ht="14.45">
+      <c r="A3" s="130"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="131"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="131"/>
+      <c r="P3" s="131"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="132"/>
+    </row>
+    <row r="4" spans="1:18" ht="14.45">
+      <c r="A4" s="127" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="168"/>
-      <c r="C4" s="168"/>
-      <c r="D4" s="168" t="s">
+      <c r="B4" s="128"/>
+      <c r="C4" s="128"/>
+      <c r="D4" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="168"/>
-      <c r="F4" s="168"/>
-      <c r="G4" s="160" t="s">
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="160"/>
-      <c r="I4" s="160"/>
-      <c r="J4" s="160" t="s">
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="160"/>
-      <c r="L4" s="160"/>
-      <c r="M4" s="168" t="s">
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="168"/>
-      <c r="O4" s="168"/>
-      <c r="P4" s="168" t="s">
+      <c r="N4" s="128"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="Q4" s="168"/>
-      <c r="R4" s="169"/>
-    </row>
-    <row r="5" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="142">
+      <c r="Q4" s="128"/>
+      <c r="R4" s="129"/>
+    </row>
+    <row r="5" spans="1:18" ht="32.25" customHeight="1">
+      <c r="A5" s="153">
         <f>SUM(B14:B24)/SUM(C14:C24)</f>
         <v>0.20283018867924529</v>
       </c>
-      <c r="B5" s="136"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="143">
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="154">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="135">
+      <c r="E5" s="147"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="146">
         <f>COUNTIF(FF_2026!H3:H1145,"Mech")</f>
         <v>82</v>
       </c>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="135">
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="146">
         <f>COUNTIF(FF_2026!H3:H1145,"HW")</f>
         <v>24</v>
       </c>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
-      <c r="M5" s="144">
+      <c r="K5" s="147"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="155">
         <f>COUNTIFS(FF_2026!$A$3:$A$176,"&lt;&gt;",FF_2026!$P$3:$P$176,"&gt;0")+COUNTIFS(FF_2026!$A$3:$A$176,"&lt;&gt;",FF_2026!$S$3:$S$176,"&gt;0")-COUNTIFS(FF_2026!$A$3:$A$176,"&lt;&gt;",FF_2026!$P$3:$P$176,"&gt;0",FF_2026!$S$3:$S$176,"&gt;0")</f>
         <v>4</v>
       </c>
-      <c r="N5" s="136"/>
-      <c r="O5" s="136"/>
-      <c r="P5" s="145">
+      <c r="N5" s="147"/>
+      <c r="O5" s="147"/>
+      <c r="P5" s="156">
         <f>IFERROR(MIN(FF_2026!$V$3:$V$176),"")</f>
         <v>46280</v>
       </c>
-      <c r="Q5" s="136"/>
-      <c r="R5" s="146"/>
-    </row>
-    <row r="6" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="137"/>
-      <c r="B6" s="138"/>
-      <c r="C6" s="138"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
-      <c r="J6" s="137"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="138"/>
-      <c r="O6" s="138"/>
-      <c r="P6" s="137"/>
-      <c r="Q6" s="138"/>
-      <c r="R6" s="147"/>
-    </row>
-    <row r="7" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="152"/>
-      <c r="N7" s="152"/>
-      <c r="O7" s="152"/>
-      <c r="P7" s="152"/>
-      <c r="Q7" s="152"/>
-      <c r="R7" s="153"/>
-    </row>
-    <row r="8" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="139" t="s">
+      <c r="Q5" s="147"/>
+      <c r="R5" s="157"/>
+    </row>
+    <row r="6" spans="1:18" ht="32.25" customHeight="1">
+      <c r="A6" s="148"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="149"/>
+      <c r="I6" s="149"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="149"/>
+      <c r="L6" s="149"/>
+      <c r="M6" s="148"/>
+      <c r="N6" s="149"/>
+      <c r="O6" s="149"/>
+      <c r="P6" s="148"/>
+      <c r="Q6" s="149"/>
+      <c r="R6" s="158"/>
+    </row>
+    <row r="7" spans="1:18" ht="14.45">
+      <c r="A7" s="136"/>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="137"/>
+      <c r="H7" s="137"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
+      <c r="M7" s="137"/>
+      <c r="N7" s="137"/>
+      <c r="O7" s="137"/>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="137"/>
+      <c r="R7" s="138"/>
+    </row>
+    <row r="8" spans="1:18" ht="14.45">
+      <c r="A8" s="150" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="140"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="140"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="140"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="140"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="140"/>
-      <c r="N8" s="140"/>
-      <c r="O8" s="140"/>
-      <c r="P8" s="140"/>
-      <c r="Q8" s="140"/>
-      <c r="R8" s="141"/>
-    </row>
-    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="148" t="str">
+      <c r="B8" s="151"/>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="151"/>
+      <c r="K8" s="151"/>
+      <c r="L8" s="151"/>
+      <c r="M8" s="151"/>
+      <c r="N8" s="151"/>
+      <c r="O8" s="151"/>
+      <c r="P8" s="151"/>
+      <c r="Q8" s="151"/>
+      <c r="R8" s="152"/>
+    </row>
+    <row r="9" spans="1:18" ht="27.75" customHeight="1">
+      <c r="A9" s="159" t="str">
         <f>"Overall gate progress is "&amp;TEXT(A5,"0%")&amp;" across "&amp;TEXT(D5,"0")&amp;" tracked parts. Design and part qualification are complete; sourcing is at "&amp;TEXT(D18,"0%")&amp;". Supplier qualification, sample procurement and factory handover remain at 0%, making downstream execution the critical path. "&amp;TEXT(M5,"0")&amp;" parts currently show a positive design or qualification delay."</f>
         <v>Overall gate progress is 20% across 106 tracked parts. Design and part qualification are complete; sourcing is at 16%. Supplier qualification, sample procurement and factory handover remain at 0%, making downstream execution the critical path. 4 parts currently show a positive design or qualification delay.</v>
       </c>
-      <c r="B9" s="149"/>
-      <c r="C9" s="149"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="149"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="149"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="149"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="149"/>
-      <c r="L9" s="149"/>
-      <c r="M9" s="149"/>
-      <c r="N9" s="149"/>
-      <c r="O9" s="149"/>
-      <c r="P9" s="149"/>
-      <c r="Q9" s="149"/>
-      <c r="R9" s="150"/>
-    </row>
-    <row r="10" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="148"/>
-      <c r="B10" s="149"/>
-      <c r="C10" s="149"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
-      <c r="I10" s="149"/>
-      <c r="J10" s="149"/>
-      <c r="K10" s="149"/>
-      <c r="L10" s="149"/>
-      <c r="M10" s="149"/>
-      <c r="N10" s="149"/>
-      <c r="O10" s="149"/>
-      <c r="P10" s="149"/>
-      <c r="Q10" s="149"/>
-      <c r="R10" s="150"/>
-    </row>
-    <row r="11" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="154"/>
-      <c r="B11" s="155"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="155"/>
-      <c r="I11" s="155"/>
-      <c r="J11" s="155"/>
-      <c r="K11" s="155"/>
-      <c r="L11" s="155"/>
-      <c r="M11" s="155"/>
-      <c r="N11" s="155"/>
-      <c r="O11" s="155"/>
-      <c r="P11" s="155"/>
-      <c r="Q11" s="155"/>
-      <c r="R11" s="156"/>
-    </row>
-    <row r="12" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="139" t="s">
+      <c r="B9" s="160"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
+      <c r="L9" s="160"/>
+      <c r="M9" s="160"/>
+      <c r="N9" s="160"/>
+      <c r="O9" s="160"/>
+      <c r="P9" s="160"/>
+      <c r="Q9" s="160"/>
+      <c r="R9" s="161"/>
+    </row>
+    <row r="10" spans="1:18" ht="27.75" customHeight="1">
+      <c r="A10" s="159"/>
+      <c r="B10" s="160"/>
+      <c r="C10" s="160"/>
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="160"/>
+      <c r="J10" s="160"/>
+      <c r="K10" s="160"/>
+      <c r="L10" s="160"/>
+      <c r="M10" s="160"/>
+      <c r="N10" s="160"/>
+      <c r="O10" s="160"/>
+      <c r="P10" s="160"/>
+      <c r="Q10" s="160"/>
+      <c r="R10" s="161"/>
+    </row>
+    <row r="11" spans="1:18" ht="14.45">
+      <c r="A11" s="133"/>
+      <c r="B11" s="134"/>
+      <c r="C11" s="134"/>
+      <c r="D11" s="134"/>
+      <c r="E11" s="134"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
+      <c r="N11" s="134"/>
+      <c r="O11" s="134"/>
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="135"/>
+    </row>
+    <row r="12" spans="1:18" ht="14.45">
+      <c r="A12" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="140"/>
-      <c r="C12" s="140"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="140"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="140"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="140"/>
-      <c r="L12" s="140"/>
-      <c r="M12" s="140"/>
-      <c r="N12" s="140"/>
-      <c r="O12" s="140"/>
-      <c r="P12" s="140"/>
-      <c r="Q12" s="140"/>
-      <c r="R12" s="141"/>
-    </row>
-    <row r="13" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="151"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="151"/>
+      <c r="L12" s="151"/>
+      <c r="M12" s="151"/>
+      <c r="N12" s="151"/>
+      <c r="O12" s="151"/>
+      <c r="P12" s="151"/>
+      <c r="Q12" s="151"/>
+      <c r="R12" s="152"/>
+    </row>
+    <row r="13" spans="1:18" ht="14.45">
       <c r="A13" s="93" t="s">
         <v>23</v>
       </c>
@@ -8838,368 +8838,368 @@
       <c r="D13" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="170"/>
-      <c r="G13" s="171"/>
-      <c r="H13" s="171"/>
-      <c r="I13" s="171"/>
-      <c r="J13" s="171"/>
-      <c r="K13" s="171"/>
-      <c r="L13" s="171"/>
-      <c r="M13" s="171"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="171"/>
-      <c r="Q13" s="171"/>
-      <c r="R13" s="172"/>
-    </row>
-    <row r="14" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="173" t="s">
+      <c r="F13" s="130"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="131"/>
+      <c r="P13" s="131"/>
+      <c r="Q13" s="131"/>
+      <c r="R13" s="132"/>
+    </row>
+    <row r="14" spans="1:18" ht="14.45">
+      <c r="A14" s="139" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="128">
+      <c r="B14" s="141">
         <f>COUNT(FF_2026!$M$3:$M$176)</f>
         <v>93</v>
       </c>
-      <c r="C14" s="128">
+      <c r="C14" s="141">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D14" s="122">
+      <c r="D14" s="165">
         <f>IFERROR(B14/C14,0)</f>
         <v>0.87735849056603776</v>
       </c>
-      <c r="F14" s="154"/>
-      <c r="G14" s="155"/>
-      <c r="H14" s="155"/>
-      <c r="I14" s="155"/>
-      <c r="J14" s="155"/>
-      <c r="K14" s="155"/>
-      <c r="L14" s="155"/>
-      <c r="M14" s="155"/>
-      <c r="N14" s="155"/>
-      <c r="O14" s="155"/>
-      <c r="P14" s="155"/>
-      <c r="Q14" s="155"/>
-      <c r="R14" s="156"/>
-    </row>
-    <row r="15" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="126"/>
-      <c r="B15" s="120"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="123"/>
-      <c r="F15" s="154"/>
-      <c r="G15" s="155"/>
-      <c r="H15" s="155"/>
-      <c r="I15" s="155"/>
-      <c r="J15" s="155"/>
-      <c r="K15" s="155"/>
-      <c r="L15" s="155"/>
-      <c r="M15" s="155"/>
-      <c r="N15" s="155"/>
-      <c r="O15" s="155"/>
-      <c r="P15" s="155"/>
-      <c r="Q15" s="155"/>
-      <c r="R15" s="156"/>
-    </row>
-    <row r="16" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="125" t="s">
+      <c r="F14" s="133"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="134"/>
+      <c r="J14" s="134"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
+      <c r="N14" s="134"/>
+      <c r="O14" s="134"/>
+      <c r="P14" s="134"/>
+      <c r="Q14" s="134"/>
+      <c r="R14" s="135"/>
+    </row>
+    <row r="15" spans="1:18" ht="14.45">
+      <c r="A15" s="140"/>
+      <c r="B15" s="142"/>
+      <c r="C15" s="142"/>
+      <c r="D15" s="166"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="134"/>
+      <c r="N15" s="134"/>
+      <c r="O15" s="134"/>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="135"/>
+    </row>
+    <row r="16" spans="1:18" ht="14.45">
+      <c r="A16" s="167" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="119">
+      <c r="B16" s="168">
         <f>COUNT(FF_2026!$R$3:$R$176)</f>
         <v>19</v>
       </c>
-      <c r="C16" s="119">
+      <c r="C16" s="168">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D16" s="122">
+      <c r="D16" s="165">
         <f>IFERROR(B16/C16,0)</f>
         <v>0.17924528301886791</v>
       </c>
-      <c r="F16" s="154"/>
-      <c r="G16" s="155"/>
-      <c r="H16" s="155"/>
-      <c r="I16" s="155"/>
-      <c r="J16" s="155"/>
-      <c r="K16" s="155"/>
-      <c r="L16" s="155"/>
-      <c r="M16" s="155"/>
-      <c r="N16" s="155"/>
-      <c r="O16" s="155"/>
-      <c r="P16" s="155"/>
-      <c r="Q16" s="155"/>
-      <c r="R16" s="156"/>
-    </row>
-    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="126"/>
-      <c r="B17" s="120"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="123"/>
-      <c r="F17" s="154"/>
-      <c r="G17" s="155"/>
-      <c r="H17" s="155"/>
-      <c r="I17" s="155"/>
-      <c r="J17" s="155"/>
-      <c r="K17" s="155"/>
-      <c r="L17" s="155"/>
-      <c r="M17" s="155"/>
-      <c r="N17" s="155"/>
-      <c r="O17" s="155"/>
-      <c r="P17" s="155"/>
-      <c r="Q17" s="155"/>
-      <c r="R17" s="156"/>
-    </row>
-    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="125" t="s">
+      <c r="F16" s="133"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="134"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="134"/>
+      <c r="N16" s="134"/>
+      <c r="O16" s="134"/>
+      <c r="P16" s="134"/>
+      <c r="Q16" s="134"/>
+      <c r="R16" s="135"/>
+    </row>
+    <row r="17" spans="1:18" ht="14.45">
+      <c r="A17" s="140"/>
+      <c r="B17" s="142"/>
+      <c r="C17" s="142"/>
+      <c r="D17" s="166"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="134"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="134"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="134"/>
+      <c r="O17" s="134"/>
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="135"/>
+    </row>
+    <row r="18" spans="1:18" ht="14.45">
+      <c r="A18" s="167" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="119">
+      <c r="B18" s="168">
         <f>COUNT(FF_2026!$AD$3:$AD$176)</f>
         <v>17</v>
       </c>
-      <c r="C18" s="119">
+      <c r="C18" s="168">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D18" s="122">
+      <c r="D18" s="165">
         <f>IFERROR(B18/C18,0)</f>
         <v>0.16037735849056603</v>
       </c>
-      <c r="F18" s="154"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="155"/>
-      <c r="I18" s="155"/>
-      <c r="J18" s="155"/>
-      <c r="K18" s="155"/>
-      <c r="L18" s="155"/>
-      <c r="M18" s="155"/>
-      <c r="N18" s="155"/>
-      <c r="O18" s="155"/>
-      <c r="P18" s="155"/>
-      <c r="Q18" s="155"/>
-      <c r="R18" s="156"/>
-    </row>
-    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="126"/>
-      <c r="B19" s="120"/>
-      <c r="C19" s="120"/>
-      <c r="D19" s="123"/>
-      <c r="F19" s="154"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="155"/>
-      <c r="J19" s="155"/>
-      <c r="K19" s="155"/>
-      <c r="L19" s="155"/>
-      <c r="M19" s="155"/>
-      <c r="N19" s="155"/>
-      <c r="O19" s="155"/>
-      <c r="P19" s="155"/>
-      <c r="Q19" s="155"/>
-      <c r="R19" s="156"/>
-    </row>
-    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="125" t="s">
+      <c r="F18" s="133"/>
+      <c r="G18" s="134"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="134"/>
+      <c r="M18" s="134"/>
+      <c r="N18" s="134"/>
+      <c r="O18" s="134"/>
+      <c r="P18" s="134"/>
+      <c r="Q18" s="134"/>
+      <c r="R18" s="135"/>
+    </row>
+    <row r="19" spans="1:18" ht="14.45">
+      <c r="A19" s="140"/>
+      <c r="B19" s="142"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="166"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="134"/>
+      <c r="H19" s="134"/>
+      <c r="I19" s="134"/>
+      <c r="J19" s="134"/>
+      <c r="K19" s="134"/>
+      <c r="L19" s="134"/>
+      <c r="M19" s="134"/>
+      <c r="N19" s="134"/>
+      <c r="O19" s="134"/>
+      <c r="P19" s="134"/>
+      <c r="Q19" s="134"/>
+      <c r="R19" s="135"/>
+    </row>
+    <row r="20" spans="1:18" ht="14.45">
+      <c r="A20" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="119">
+      <c r="B20" s="168">
         <f>COUNT(FF_2026!$AO$3:$AO$176)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="119">
+      <c r="C20" s="168">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D20" s="122">
+      <c r="D20" s="165">
         <f>IFERROR(B20/C20,0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="154"/>
-      <c r="G20" s="155"/>
-      <c r="H20" s="155"/>
-      <c r="I20" s="155"/>
-      <c r="J20" s="155"/>
-      <c r="K20" s="155"/>
-      <c r="L20" s="155"/>
-      <c r="M20" s="155"/>
-      <c r="N20" s="155"/>
-      <c r="O20" s="155"/>
-      <c r="P20" s="155"/>
-      <c r="Q20" s="155"/>
-      <c r="R20" s="156"/>
-    </row>
-    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="126"/>
-      <c r="B21" s="120"/>
-      <c r="C21" s="120"/>
-      <c r="D21" s="123"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="155"/>
-      <c r="I21" s="155"/>
-      <c r="J21" s="155"/>
-      <c r="K21" s="155"/>
-      <c r="L21" s="155"/>
-      <c r="M21" s="155"/>
-      <c r="N21" s="155"/>
-      <c r="O21" s="155"/>
-      <c r="P21" s="155"/>
-      <c r="Q21" s="155"/>
-      <c r="R21" s="156"/>
-    </row>
-    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="125" t="s">
+      <c r="F20" s="133"/>
+      <c r="G20" s="134"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
+      <c r="K20" s="134"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
+      <c r="N20" s="134"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="135"/>
+    </row>
+    <row r="21" spans="1:18" ht="14.45">
+      <c r="A21" s="140"/>
+      <c r="B21" s="142"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="166"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="134"/>
+      <c r="H21" s="134"/>
+      <c r="I21" s="134"/>
+      <c r="J21" s="134"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="134"/>
+      <c r="N21" s="134"/>
+      <c r="O21" s="134"/>
+      <c r="P21" s="134"/>
+      <c r="Q21" s="134"/>
+      <c r="R21" s="135"/>
+    </row>
+    <row r="22" spans="1:18" ht="14.45">
+      <c r="A22" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="119">
+      <c r="B22" s="168">
         <f>COUNT(FF_2026!$AS$3:$AS$176)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="119">
+      <c r="C22" s="168">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D22" s="122">
+      <c r="D22" s="165">
         <f>IFERROR(B22/C22,0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="154"/>
-      <c r="G22" s="155"/>
-      <c r="H22" s="155"/>
-      <c r="I22" s="155"/>
-      <c r="J22" s="155"/>
-      <c r="K22" s="155"/>
-      <c r="L22" s="155"/>
-      <c r="M22" s="155"/>
-      <c r="N22" s="155"/>
-      <c r="O22" s="155"/>
-      <c r="P22" s="155"/>
-      <c r="Q22" s="155"/>
-      <c r="R22" s="156"/>
-    </row>
-    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="126"/>
-      <c r="B23" s="120"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="123"/>
-      <c r="F23" s="154"/>
-      <c r="G23" s="155"/>
-      <c r="H23" s="155"/>
-      <c r="I23" s="155"/>
-      <c r="J23" s="155"/>
-      <c r="K23" s="155"/>
-      <c r="L23" s="155"/>
-      <c r="M23" s="155"/>
-      <c r="N23" s="155"/>
-      <c r="O23" s="155"/>
-      <c r="P23" s="155"/>
-      <c r="Q23" s="155"/>
-      <c r="R23" s="156"/>
-    </row>
-    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="125" t="s">
+      <c r="F22" s="133"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="134"/>
+      <c r="I22" s="134"/>
+      <c r="J22" s="134"/>
+      <c r="K22" s="134"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="134"/>
+      <c r="N22" s="134"/>
+      <c r="O22" s="134"/>
+      <c r="P22" s="134"/>
+      <c r="Q22" s="134"/>
+      <c r="R22" s="135"/>
+    </row>
+    <row r="23" spans="1:18" ht="14.45">
+      <c r="A23" s="140"/>
+      <c r="B23" s="142"/>
+      <c r="C23" s="142"/>
+      <c r="D23" s="166"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="134"/>
+      <c r="L23" s="134"/>
+      <c r="M23" s="134"/>
+      <c r="N23" s="134"/>
+      <c r="O23" s="134"/>
+      <c r="P23" s="134"/>
+      <c r="Q23" s="134"/>
+      <c r="R23" s="135"/>
+    </row>
+    <row r="24" spans="1:18" ht="14.45">
+      <c r="A24" s="167" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="119">
+      <c r="B24" s="168">
         <f>COUNT(FF_2026!$BC$3:$BC$176)</f>
         <v>0</v>
       </c>
-      <c r="C24" s="119">
+      <c r="C24" s="168">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D24" s="122">
+      <c r="D24" s="165">
         <f>IFERROR(B24/C24,0)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="154"/>
-      <c r="G24" s="155"/>
-      <c r="H24" s="155"/>
-      <c r="I24" s="155"/>
-      <c r="J24" s="155"/>
-      <c r="K24" s="155"/>
-      <c r="L24" s="155"/>
-      <c r="M24" s="155"/>
-      <c r="N24" s="155"/>
-      <c r="O24" s="155"/>
-      <c r="P24" s="155"/>
-      <c r="Q24" s="155"/>
-      <c r="R24" s="156"/>
-    </row>
-    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="127"/>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="124"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="155"/>
-      <c r="I25" s="155"/>
-      <c r="J25" s="155"/>
-      <c r="K25" s="155"/>
-      <c r="L25" s="155"/>
-      <c r="M25" s="155"/>
-      <c r="N25" s="155"/>
-      <c r="O25" s="155"/>
-      <c r="P25" s="155"/>
-      <c r="Q25" s="155"/>
-      <c r="R25" s="156"/>
-    </row>
-    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F24" s="133"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="134"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="134"/>
+      <c r="N24" s="134"/>
+      <c r="O24" s="134"/>
+      <c r="P24" s="134"/>
+      <c r="Q24" s="134"/>
+      <c r="R24" s="135"/>
+    </row>
+    <row r="25" spans="1:18" ht="14.45">
+      <c r="A25" s="169"/>
+      <c r="B25" s="170"/>
+      <c r="C25" s="170"/>
+      <c r="D25" s="171"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="134"/>
+      <c r="L25" s="134"/>
+      <c r="M25" s="134"/>
+      <c r="N25" s="134"/>
+      <c r="O25" s="134"/>
+      <c r="P25" s="134"/>
+      <c r="Q25" s="134"/>
+      <c r="R25" s="135"/>
+    </row>
+    <row r="26" spans="1:18" ht="14.45">
       <c r="A26" s="66"/>
-      <c r="F26" s="154"/>
-      <c r="G26" s="155"/>
-      <c r="H26" s="155"/>
-      <c r="I26" s="155"/>
-      <c r="J26" s="155"/>
-      <c r="K26" s="155"/>
-      <c r="L26" s="155"/>
-      <c r="M26" s="155"/>
-      <c r="N26" s="155"/>
-      <c r="O26" s="155"/>
-      <c r="P26" s="155"/>
-      <c r="Q26" s="155"/>
-      <c r="R26" s="156"/>
-    </row>
-    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F26" s="133"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="134"/>
+      <c r="I26" s="134"/>
+      <c r="J26" s="134"/>
+      <c r="K26" s="134"/>
+      <c r="L26" s="134"/>
+      <c r="M26" s="134"/>
+      <c r="N26" s="134"/>
+      <c r="O26" s="134"/>
+      <c r="P26" s="134"/>
+      <c r="Q26" s="134"/>
+      <c r="R26" s="135"/>
+    </row>
+    <row r="27" spans="1:18" ht="14.45">
       <c r="A27" s="66"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="152"/>
-      <c r="K27" s="152"/>
-      <c r="L27" s="152"/>
-      <c r="M27" s="152"/>
-      <c r="N27" s="152"/>
-      <c r="O27" s="152"/>
-      <c r="P27" s="152"/>
-      <c r="Q27" s="152"/>
-      <c r="R27" s="153"/>
-    </row>
-    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="157" t="s">
+      <c r="F27" s="136"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="137"/>
+      <c r="I27" s="137"/>
+      <c r="J27" s="137"/>
+      <c r="K27" s="137"/>
+      <c r="L27" s="137"/>
+      <c r="M27" s="137"/>
+      <c r="N27" s="137"/>
+      <c r="O27" s="137"/>
+      <c r="P27" s="137"/>
+      <c r="Q27" s="137"/>
+      <c r="R27" s="138"/>
+    </row>
+    <row r="28" spans="1:18" ht="14.45">
+      <c r="A28" s="162" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="158"/>
-      <c r="C28" s="158"/>
-      <c r="D28" s="159"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="171"/>
-      <c r="I28" s="171"/>
-      <c r="J28" s="171"/>
-      <c r="K28" s="171"/>
-      <c r="L28" s="171"/>
-      <c r="M28" s="171"/>
-      <c r="N28" s="171"/>
-      <c r="O28" s="171"/>
-      <c r="P28" s="171"/>
-      <c r="Q28" s="171"/>
-      <c r="R28" s="172"/>
-    </row>
-    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B28" s="163"/>
+      <c r="C28" s="163"/>
+      <c r="D28" s="164"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="131"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
+      <c r="M28" s="131"/>
+      <c r="N28" s="131"/>
+      <c r="O28" s="131"/>
+      <c r="P28" s="131"/>
+      <c r="Q28" s="131"/>
+      <c r="R28" s="132"/>
+    </row>
+    <row r="29" spans="1:18" ht="14.45">
       <c r="A29" s="75" t="s">
         <v>34</v>
       </c>
@@ -9212,21 +9212,21 @@
       <c r="D29" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="154"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="155"/>
-      <c r="I29" s="155"/>
-      <c r="J29" s="155"/>
-      <c r="K29" s="155"/>
-      <c r="L29" s="155"/>
-      <c r="M29" s="155"/>
-      <c r="N29" s="155"/>
-      <c r="O29" s="155"/>
-      <c r="P29" s="155"/>
-      <c r="Q29" s="155"/>
-      <c r="R29" s="156"/>
-    </row>
-    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F29" s="133"/>
+      <c r="G29" s="134"/>
+      <c r="H29" s="134"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="134"/>
+      <c r="L29" s="134"/>
+      <c r="M29" s="134"/>
+      <c r="N29" s="134"/>
+      <c r="O29" s="134"/>
+      <c r="P29" s="134"/>
+      <c r="Q29" s="134"/>
+      <c r="R29" s="135"/>
+    </row>
+    <row r="30" spans="1:18" ht="14.45">
       <c r="A30" s="76" t="s">
         <v>36</v>
       </c>
@@ -9242,21 +9242,21 @@
         <f>IFERROR(B30/C30,0)</f>
         <v>0.91509433962264153</v>
       </c>
-      <c r="F30" s="154"/>
-      <c r="G30" s="155"/>
-      <c r="H30" s="155"/>
-      <c r="I30" s="155"/>
-      <c r="J30" s="155"/>
-      <c r="K30" s="155"/>
-      <c r="L30" s="155"/>
-      <c r="M30" s="155"/>
-      <c r="N30" s="155"/>
-      <c r="O30" s="155"/>
-      <c r="P30" s="155"/>
-      <c r="Q30" s="155"/>
-      <c r="R30" s="156"/>
-    </row>
-    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F30" s="133"/>
+      <c r="G30" s="134"/>
+      <c r="H30" s="134"/>
+      <c r="I30" s="134"/>
+      <c r="J30" s="134"/>
+      <c r="K30" s="134"/>
+      <c r="L30" s="134"/>
+      <c r="M30" s="134"/>
+      <c r="N30" s="134"/>
+      <c r="O30" s="134"/>
+      <c r="P30" s="134"/>
+      <c r="Q30" s="134"/>
+      <c r="R30" s="135"/>
+    </row>
+    <row r="31" spans="1:18" ht="14.45">
       <c r="A31" s="77" t="s">
         <v>37</v>
       </c>
@@ -9272,21 +9272,21 @@
         <f>IFERROR(B31/C31,0)</f>
         <v>0.73529411764705888</v>
       </c>
-      <c r="F31" s="154"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="155"/>
-      <c r="I31" s="155"/>
-      <c r="J31" s="155"/>
-      <c r="K31" s="155"/>
-      <c r="L31" s="155"/>
-      <c r="M31" s="155"/>
-      <c r="N31" s="155"/>
-      <c r="O31" s="155"/>
-      <c r="P31" s="155"/>
-      <c r="Q31" s="155"/>
-      <c r="R31" s="156"/>
-    </row>
-    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F31" s="133"/>
+      <c r="G31" s="134"/>
+      <c r="H31" s="134"/>
+      <c r="I31" s="134"/>
+      <c r="J31" s="134"/>
+      <c r="K31" s="134"/>
+      <c r="L31" s="134"/>
+      <c r="M31" s="134"/>
+      <c r="N31" s="134"/>
+      <c r="O31" s="134"/>
+      <c r="P31" s="134"/>
+      <c r="Q31" s="134"/>
+      <c r="R31" s="135"/>
+    </row>
+    <row r="32" spans="1:18" ht="14.45">
       <c r="A32" s="77" t="s">
         <v>38</v>
       </c>
@@ -9302,21 +9302,21 @@
         <f>IFERROR(B32/C32,0)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="154"/>
-      <c r="G32" s="155"/>
-      <c r="H32" s="155"/>
-      <c r="I32" s="155"/>
-      <c r="J32" s="155"/>
-      <c r="K32" s="155"/>
-      <c r="L32" s="155"/>
-      <c r="M32" s="155"/>
-      <c r="N32" s="155"/>
-      <c r="O32" s="155"/>
-      <c r="P32" s="155"/>
-      <c r="Q32" s="155"/>
-      <c r="R32" s="156"/>
-    </row>
-    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F32" s="133"/>
+      <c r="G32" s="134"/>
+      <c r="H32" s="134"/>
+      <c r="I32" s="134"/>
+      <c r="J32" s="134"/>
+      <c r="K32" s="134"/>
+      <c r="L32" s="134"/>
+      <c r="M32" s="134"/>
+      <c r="N32" s="134"/>
+      <c r="O32" s="134"/>
+      <c r="P32" s="134"/>
+      <c r="Q32" s="134"/>
+      <c r="R32" s="135"/>
+    </row>
+    <row r="33" spans="1:18" ht="14.45">
       <c r="A33" s="77" t="s">
         <v>39</v>
       </c>
@@ -9332,21 +9332,21 @@
         <f t="shared" ref="D33" si="0">IFERROR(B33/C33,0)</f>
         <v>1</v>
       </c>
-      <c r="F33" s="154"/>
-      <c r="G33" s="155"/>
-      <c r="H33" s="155"/>
-      <c r="I33" s="155"/>
-      <c r="J33" s="155"/>
-      <c r="K33" s="155"/>
-      <c r="L33" s="155"/>
-      <c r="M33" s="155"/>
-      <c r="N33" s="155"/>
-      <c r="O33" s="155"/>
-      <c r="P33" s="155"/>
-      <c r="Q33" s="155"/>
-      <c r="R33" s="156"/>
-    </row>
-    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F33" s="133"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="134"/>
+      <c r="I33" s="134"/>
+      <c r="J33" s="134"/>
+      <c r="K33" s="134"/>
+      <c r="L33" s="134"/>
+      <c r="M33" s="134"/>
+      <c r="N33" s="134"/>
+      <c r="O33" s="134"/>
+      <c r="P33" s="134"/>
+      <c r="Q33" s="134"/>
+      <c r="R33" s="135"/>
+    </row>
+    <row r="34" spans="1:18" ht="14.45">
       <c r="A34" s="77" t="s">
         <v>40</v>
       </c>
@@ -9362,21 +9362,21 @@
         <f t="shared" ref="D34:D40" si="1">IFERROR(B34/C34,0)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="154"/>
-      <c r="G34" s="155"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="155"/>
-      <c r="J34" s="155"/>
-      <c r="K34" s="155"/>
-      <c r="L34" s="155"/>
-      <c r="M34" s="155"/>
-      <c r="N34" s="155"/>
-      <c r="O34" s="155"/>
-      <c r="P34" s="155"/>
-      <c r="Q34" s="155"/>
-      <c r="R34" s="156"/>
-    </row>
-    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F34" s="133"/>
+      <c r="G34" s="134"/>
+      <c r="H34" s="134"/>
+      <c r="I34" s="134"/>
+      <c r="J34" s="134"/>
+      <c r="K34" s="134"/>
+      <c r="L34" s="134"/>
+      <c r="M34" s="134"/>
+      <c r="N34" s="134"/>
+      <c r="O34" s="134"/>
+      <c r="P34" s="134"/>
+      <c r="Q34" s="134"/>
+      <c r="R34" s="135"/>
+    </row>
+    <row r="35" spans="1:18" ht="14.45">
       <c r="A35" s="77" t="s">
         <v>41</v>
       </c>
@@ -9392,21 +9392,21 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F35" s="154"/>
-      <c r="G35" s="155"/>
-      <c r="H35" s="155"/>
-      <c r="I35" s="155"/>
-      <c r="J35" s="155"/>
-      <c r="K35" s="155"/>
-      <c r="L35" s="155"/>
-      <c r="M35" s="155"/>
-      <c r="N35" s="155"/>
-      <c r="O35" s="155"/>
-      <c r="P35" s="155"/>
-      <c r="Q35" s="155"/>
-      <c r="R35" s="156"/>
-    </row>
-    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F35" s="133"/>
+      <c r="G35" s="134"/>
+      <c r="H35" s="134"/>
+      <c r="I35" s="134"/>
+      <c r="J35" s="134"/>
+      <c r="K35" s="134"/>
+      <c r="L35" s="134"/>
+      <c r="M35" s="134"/>
+      <c r="N35" s="134"/>
+      <c r="O35" s="134"/>
+      <c r="P35" s="134"/>
+      <c r="Q35" s="134"/>
+      <c r="R35" s="135"/>
+    </row>
+    <row r="36" spans="1:18" ht="14.45">
       <c r="A36" s="78" t="s">
         <v>42</v>
       </c>
@@ -9422,21 +9422,21 @@
         <f t="shared" si="1"/>
         <v>0.98780487804878048</v>
       </c>
-      <c r="F36" s="154"/>
-      <c r="G36" s="155"/>
-      <c r="H36" s="155"/>
-      <c r="I36" s="155"/>
-      <c r="J36" s="155"/>
-      <c r="K36" s="155"/>
-      <c r="L36" s="155"/>
-      <c r="M36" s="155"/>
-      <c r="N36" s="155"/>
-      <c r="O36" s="155"/>
-      <c r="P36" s="155"/>
-      <c r="Q36" s="155"/>
-      <c r="R36" s="156"/>
-    </row>
-    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F36" s="133"/>
+      <c r="G36" s="134"/>
+      <c r="H36" s="134"/>
+      <c r="I36" s="134"/>
+      <c r="J36" s="134"/>
+      <c r="K36" s="134"/>
+      <c r="L36" s="134"/>
+      <c r="M36" s="134"/>
+      <c r="N36" s="134"/>
+      <c r="O36" s="134"/>
+      <c r="P36" s="134"/>
+      <c r="Q36" s="134"/>
+      <c r="R36" s="135"/>
+    </row>
+    <row r="37" spans="1:18" ht="14.45">
       <c r="A37" s="79" t="s">
         <v>37</v>
       </c>
@@ -9452,21 +9452,21 @@
         <f t="shared" si="1"/>
         <v>0.95652173913043481</v>
       </c>
-      <c r="F37" s="154"/>
-      <c r="G37" s="155"/>
-      <c r="H37" s="155"/>
-      <c r="I37" s="155"/>
-      <c r="J37" s="155"/>
-      <c r="K37" s="155"/>
-      <c r="L37" s="155"/>
-      <c r="M37" s="155"/>
-      <c r="N37" s="155"/>
-      <c r="O37" s="155"/>
-      <c r="P37" s="155"/>
-      <c r="Q37" s="155"/>
-      <c r="R37" s="156"/>
-    </row>
-    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F37" s="133"/>
+      <c r="G37" s="134"/>
+      <c r="H37" s="134"/>
+      <c r="I37" s="134"/>
+      <c r="J37" s="134"/>
+      <c r="K37" s="134"/>
+      <c r="L37" s="134"/>
+      <c r="M37" s="134"/>
+      <c r="N37" s="134"/>
+      <c r="O37" s="134"/>
+      <c r="P37" s="134"/>
+      <c r="Q37" s="134"/>
+      <c r="R37" s="135"/>
+    </row>
+    <row r="38" spans="1:18" ht="14.45">
       <c r="A38" s="79" t="s">
         <v>38</v>
       </c>
@@ -9482,21 +9482,21 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F38" s="154"/>
-      <c r="G38" s="155"/>
-      <c r="H38" s="155"/>
-      <c r="I38" s="155"/>
-      <c r="J38" s="155"/>
-      <c r="K38" s="155"/>
-      <c r="L38" s="155"/>
-      <c r="M38" s="155"/>
-      <c r="N38" s="155"/>
-      <c r="O38" s="155"/>
-      <c r="P38" s="155"/>
-      <c r="Q38" s="155"/>
-      <c r="R38" s="156"/>
-    </row>
-    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F38" s="133"/>
+      <c r="G38" s="134"/>
+      <c r="H38" s="134"/>
+      <c r="I38" s="134"/>
+      <c r="J38" s="134"/>
+      <c r="K38" s="134"/>
+      <c r="L38" s="134"/>
+      <c r="M38" s="134"/>
+      <c r="N38" s="134"/>
+      <c r="O38" s="134"/>
+      <c r="P38" s="134"/>
+      <c r="Q38" s="134"/>
+      <c r="R38" s="135"/>
+    </row>
+    <row r="39" spans="1:18" ht="14.45">
       <c r="A39" s="79" t="s">
         <v>39</v>
       </c>
@@ -9512,21 +9512,21 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F39" s="154"/>
-      <c r="G39" s="155"/>
-      <c r="H39" s="155"/>
-      <c r="I39" s="155"/>
-      <c r="J39" s="155"/>
-      <c r="K39" s="155"/>
-      <c r="L39" s="155"/>
-      <c r="M39" s="155"/>
-      <c r="N39" s="155"/>
-      <c r="O39" s="155"/>
-      <c r="P39" s="155"/>
-      <c r="Q39" s="155"/>
-      <c r="R39" s="156"/>
-    </row>
-    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F39" s="133"/>
+      <c r="G39" s="134"/>
+      <c r="H39" s="134"/>
+      <c r="I39" s="134"/>
+      <c r="J39" s="134"/>
+      <c r="K39" s="134"/>
+      <c r="L39" s="134"/>
+      <c r="M39" s="134"/>
+      <c r="N39" s="134"/>
+      <c r="O39" s="134"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="135"/>
+    </row>
+    <row r="40" spans="1:18" ht="14.45">
       <c r="A40" s="79" t="s">
         <v>40</v>
       </c>
@@ -9542,21 +9542,21 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F40" s="154"/>
-      <c r="G40" s="155"/>
-      <c r="H40" s="155"/>
-      <c r="I40" s="155"/>
-      <c r="J40" s="155"/>
-      <c r="K40" s="155"/>
-      <c r="L40" s="155"/>
-      <c r="M40" s="155"/>
-      <c r="N40" s="155"/>
-      <c r="O40" s="155"/>
-      <c r="P40" s="155"/>
-      <c r="Q40" s="155"/>
-      <c r="R40" s="156"/>
-    </row>
-    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F40" s="133"/>
+      <c r="G40" s="134"/>
+      <c r="H40" s="134"/>
+      <c r="I40" s="134"/>
+      <c r="J40" s="134"/>
+      <c r="K40" s="134"/>
+      <c r="L40" s="134"/>
+      <c r="M40" s="134"/>
+      <c r="N40" s="134"/>
+      <c r="O40" s="134"/>
+      <c r="P40" s="134"/>
+      <c r="Q40" s="134"/>
+      <c r="R40" s="135"/>
+    </row>
+    <row r="41" spans="1:18" ht="14.45">
       <c r="A41" s="79" t="s">
         <v>41</v>
       </c>
@@ -9572,21 +9572,21 @@
         <f t="shared" ref="D41:D42" si="2">IFERROR(B41/C41,0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="154"/>
-      <c r="G41" s="155"/>
-      <c r="H41" s="155"/>
-      <c r="I41" s="155"/>
-      <c r="J41" s="155"/>
-      <c r="K41" s="155"/>
-      <c r="L41" s="155"/>
-      <c r="M41" s="155"/>
-      <c r="N41" s="155"/>
-      <c r="O41" s="155"/>
-      <c r="P41" s="155"/>
-      <c r="Q41" s="155"/>
-      <c r="R41" s="156"/>
-    </row>
-    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F41" s="133"/>
+      <c r="G41" s="134"/>
+      <c r="H41" s="134"/>
+      <c r="I41" s="134"/>
+      <c r="J41" s="134"/>
+      <c r="K41" s="134"/>
+      <c r="L41" s="134"/>
+      <c r="M41" s="134"/>
+      <c r="N41" s="134"/>
+      <c r="O41" s="134"/>
+      <c r="P41" s="134"/>
+      <c r="Q41" s="134"/>
+      <c r="R41" s="135"/>
+    </row>
+    <row r="42" spans="1:18" ht="14.45">
       <c r="A42" s="78" t="s">
         <v>43</v>
       </c>
@@ -9602,21 +9602,21 @@
         <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="F42" s="154"/>
-      <c r="G42" s="155"/>
-      <c r="H42" s="155"/>
-      <c r="I42" s="155"/>
-      <c r="J42" s="155"/>
-      <c r="K42" s="155"/>
-      <c r="L42" s="155"/>
-      <c r="M42" s="155"/>
-      <c r="N42" s="155"/>
-      <c r="O42" s="155"/>
-      <c r="P42" s="155"/>
-      <c r="Q42" s="155"/>
-      <c r="R42" s="156"/>
-    </row>
-    <row r="43" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F42" s="133"/>
+      <c r="G42" s="134"/>
+      <c r="H42" s="134"/>
+      <c r="I42" s="134"/>
+      <c r="J42" s="134"/>
+      <c r="K42" s="134"/>
+      <c r="L42" s="134"/>
+      <c r="M42" s="134"/>
+      <c r="N42" s="134"/>
+      <c r="O42" s="134"/>
+      <c r="P42" s="134"/>
+      <c r="Q42" s="134"/>
+      <c r="R42" s="135"/>
+    </row>
+    <row r="43" spans="1:18" ht="14.45">
       <c r="A43" s="79" t="s">
         <v>37</v>
       </c>
@@ -9632,21 +9632,21 @@
         <f>IFERROR(B43/C43,0)</f>
         <v>0.27272727272727271</v>
       </c>
-      <c r="F43" s="154"/>
-      <c r="G43" s="155"/>
-      <c r="H43" s="155"/>
-      <c r="I43" s="155"/>
-      <c r="J43" s="155"/>
-      <c r="K43" s="155"/>
-      <c r="L43" s="155"/>
-      <c r="M43" s="155"/>
-      <c r="N43" s="155"/>
-      <c r="O43" s="155"/>
-      <c r="P43" s="155"/>
-      <c r="Q43" s="155"/>
-      <c r="R43" s="156"/>
-    </row>
-    <row r="44" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F43" s="133"/>
+      <c r="G43" s="134"/>
+      <c r="H43" s="134"/>
+      <c r="I43" s="134"/>
+      <c r="J43" s="134"/>
+      <c r="K43" s="134"/>
+      <c r="L43" s="134"/>
+      <c r="M43" s="134"/>
+      <c r="N43" s="134"/>
+      <c r="O43" s="134"/>
+      <c r="P43" s="134"/>
+      <c r="Q43" s="134"/>
+      <c r="R43" s="135"/>
+    </row>
+    <row r="44" spans="1:18" ht="14.45">
       <c r="A44" s="79" t="s">
         <v>38</v>
       </c>
@@ -9662,21 +9662,21 @@
         <f t="shared" ref="D44" si="3">IFERROR(B44/C44,0)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="154"/>
-      <c r="G44" s="155"/>
-      <c r="H44" s="155"/>
-      <c r="I44" s="155"/>
-      <c r="J44" s="155"/>
-      <c r="K44" s="155"/>
-      <c r="L44" s="155"/>
-      <c r="M44" s="155"/>
-      <c r="N44" s="155"/>
-      <c r="O44" s="155"/>
-      <c r="P44" s="155"/>
-      <c r="Q44" s="155"/>
-      <c r="R44" s="156"/>
-    </row>
-    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F44" s="133"/>
+      <c r="G44" s="134"/>
+      <c r="H44" s="134"/>
+      <c r="I44" s="134"/>
+      <c r="J44" s="134"/>
+      <c r="K44" s="134"/>
+      <c r="L44" s="134"/>
+      <c r="M44" s="134"/>
+      <c r="N44" s="134"/>
+      <c r="O44" s="134"/>
+      <c r="P44" s="134"/>
+      <c r="Q44" s="134"/>
+      <c r="R44" s="135"/>
+    </row>
+    <row r="45" spans="1:18" ht="14.45">
       <c r="A45" s="79" t="s">
         <v>39</v>
       </c>
@@ -9692,21 +9692,21 @@
         <f>IFERROR(B45/C45,0)</f>
         <v>1</v>
       </c>
-      <c r="F45" s="154"/>
-      <c r="G45" s="155"/>
-      <c r="H45" s="155"/>
-      <c r="I45" s="155"/>
-      <c r="J45" s="155"/>
-      <c r="K45" s="155"/>
-      <c r="L45" s="155"/>
-      <c r="M45" s="155"/>
-      <c r="N45" s="155"/>
-      <c r="O45" s="155"/>
-      <c r="P45" s="155"/>
-      <c r="Q45" s="155"/>
-      <c r="R45" s="156"/>
-    </row>
-    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F45" s="133"/>
+      <c r="G45" s="134"/>
+      <c r="H45" s="134"/>
+      <c r="I45" s="134"/>
+      <c r="J45" s="134"/>
+      <c r="K45" s="134"/>
+      <c r="L45" s="134"/>
+      <c r="M45" s="134"/>
+      <c r="N45" s="134"/>
+      <c r="O45" s="134"/>
+      <c r="P45" s="134"/>
+      <c r="Q45" s="134"/>
+      <c r="R45" s="135"/>
+    </row>
+    <row r="46" spans="1:18" ht="14.45">
       <c r="A46" s="79" t="s">
         <v>40</v>
       </c>
@@ -9722,21 +9722,21 @@
         <f>IFERROR(B46/C46,0)</f>
         <v>1</v>
       </c>
-      <c r="F46" s="154"/>
-      <c r="G46" s="155"/>
-      <c r="H46" s="155"/>
-      <c r="I46" s="155"/>
-      <c r="J46" s="155"/>
-      <c r="K46" s="155"/>
-      <c r="L46" s="155"/>
-      <c r="M46" s="155"/>
-      <c r="N46" s="155"/>
-      <c r="O46" s="155"/>
-      <c r="P46" s="155"/>
-      <c r="Q46" s="155"/>
-      <c r="R46" s="156"/>
-    </row>
-    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F46" s="133"/>
+      <c r="G46" s="134"/>
+      <c r="H46" s="134"/>
+      <c r="I46" s="134"/>
+      <c r="J46" s="134"/>
+      <c r="K46" s="134"/>
+      <c r="L46" s="134"/>
+      <c r="M46" s="134"/>
+      <c r="N46" s="134"/>
+      <c r="O46" s="134"/>
+      <c r="P46" s="134"/>
+      <c r="Q46" s="134"/>
+      <c r="R46" s="135"/>
+    </row>
+    <row r="47" spans="1:18" ht="14.45">
       <c r="A47" s="79" t="s">
         <v>41</v>
       </c>
@@ -9752,21 +9752,21 @@
         <f t="shared" ref="D47:D48" si="4">IFERROR(B47/C47,0)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="154"/>
-      <c r="G47" s="155"/>
-      <c r="H47" s="155"/>
-      <c r="I47" s="155"/>
-      <c r="J47" s="155"/>
-      <c r="K47" s="155"/>
-      <c r="L47" s="155"/>
-      <c r="M47" s="155"/>
-      <c r="N47" s="155"/>
-      <c r="O47" s="155"/>
-      <c r="P47" s="155"/>
-      <c r="Q47" s="155"/>
-      <c r="R47" s="156"/>
-    </row>
-    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F47" s="133"/>
+      <c r="G47" s="134"/>
+      <c r="H47" s="134"/>
+      <c r="I47" s="134"/>
+      <c r="J47" s="134"/>
+      <c r="K47" s="134"/>
+      <c r="L47" s="134"/>
+      <c r="M47" s="134"/>
+      <c r="N47" s="134"/>
+      <c r="O47" s="134"/>
+      <c r="P47" s="134"/>
+      <c r="Q47" s="134"/>
+      <c r="R47" s="135"/>
+    </row>
+    <row r="48" spans="1:18" ht="14.45">
       <c r="A48" s="81" t="s">
         <v>44</v>
       </c>
@@ -9782,99 +9782,99 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F48" s="154"/>
-      <c r="G48" s="155"/>
-      <c r="H48" s="155"/>
-      <c r="I48" s="155"/>
-      <c r="J48" s="155"/>
-      <c r="K48" s="155"/>
-      <c r="L48" s="155"/>
-      <c r="M48" s="155"/>
-      <c r="N48" s="155"/>
-      <c r="O48" s="155"/>
-      <c r="P48" s="155"/>
-      <c r="Q48" s="155"/>
-      <c r="R48" s="156"/>
-    </row>
-    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="F48" s="133"/>
+      <c r="G48" s="134"/>
+      <c r="H48" s="134"/>
+      <c r="I48" s="134"/>
+      <c r="J48" s="134"/>
+      <c r="K48" s="134"/>
+      <c r="L48" s="134"/>
+      <c r="M48" s="134"/>
+      <c r="N48" s="134"/>
+      <c r="O48" s="134"/>
+      <c r="P48" s="134"/>
+      <c r="Q48" s="134"/>
+      <c r="R48" s="135"/>
+    </row>
+    <row r="49" spans="1:18" ht="14.45">
       <c r="A49" s="66"/>
-      <c r="F49" s="151"/>
-      <c r="G49" s="152"/>
-      <c r="H49" s="152"/>
-      <c r="I49" s="152"/>
-      <c r="J49" s="152"/>
-      <c r="K49" s="152"/>
-      <c r="L49" s="152"/>
-      <c r="M49" s="152"/>
-      <c r="N49" s="152"/>
-      <c r="O49" s="152"/>
-      <c r="P49" s="152"/>
-      <c r="Q49" s="152"/>
-      <c r="R49" s="153"/>
-    </row>
-    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="154"/>
-      <c r="B50" s="155"/>
-      <c r="C50" s="155"/>
-      <c r="D50" s="155"/>
-      <c r="E50" s="155"/>
-      <c r="F50" s="155"/>
-      <c r="G50" s="155"/>
-      <c r="H50" s="155"/>
-      <c r="I50" s="155"/>
-      <c r="J50" s="155"/>
-      <c r="K50" s="155"/>
-      <c r="L50" s="155"/>
-      <c r="M50" s="155"/>
-      <c r="N50" s="155"/>
-      <c r="O50" s="155"/>
-      <c r="P50" s="155"/>
-      <c r="Q50" s="155"/>
-      <c r="R50" s="156"/>
-    </row>
-    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="154"/>
-      <c r="B51" s="155"/>
-      <c r="C51" s="155"/>
-      <c r="D51" s="155"/>
-      <c r="E51" s="155"/>
-      <c r="F51" s="155"/>
-      <c r="G51" s="155"/>
-      <c r="H51" s="155"/>
-      <c r="I51" s="155"/>
-      <c r="J51" s="155"/>
-      <c r="K51" s="155"/>
-      <c r="L51" s="155"/>
-      <c r="M51" s="155"/>
-      <c r="N51" s="155"/>
-      <c r="O51" s="155"/>
-      <c r="P51" s="155"/>
-      <c r="Q51" s="155"/>
-      <c r="R51" s="156"/>
-    </row>
-    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="139" t="s">
+      <c r="F49" s="136"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="137"/>
+      <c r="I49" s="137"/>
+      <c r="J49" s="137"/>
+      <c r="K49" s="137"/>
+      <c r="L49" s="137"/>
+      <c r="M49" s="137"/>
+      <c r="N49" s="137"/>
+      <c r="O49" s="137"/>
+      <c r="P49" s="137"/>
+      <c r="Q49" s="137"/>
+      <c r="R49" s="138"/>
+    </row>
+    <row r="50" spans="1:18" ht="14.45">
+      <c r="A50" s="133"/>
+      <c r="B50" s="134"/>
+      <c r="C50" s="134"/>
+      <c r="D50" s="134"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="134"/>
+      <c r="H50" s="134"/>
+      <c r="I50" s="134"/>
+      <c r="J50" s="134"/>
+      <c r="K50" s="134"/>
+      <c r="L50" s="134"/>
+      <c r="M50" s="134"/>
+      <c r="N50" s="134"/>
+      <c r="O50" s="134"/>
+      <c r="P50" s="134"/>
+      <c r="Q50" s="134"/>
+      <c r="R50" s="135"/>
+    </row>
+    <row r="51" spans="1:18" ht="14.45">
+      <c r="A51" s="133"/>
+      <c r="B51" s="134"/>
+      <c r="C51" s="134"/>
+      <c r="D51" s="134"/>
+      <c r="E51" s="134"/>
+      <c r="F51" s="134"/>
+      <c r="G51" s="134"/>
+      <c r="H51" s="134"/>
+      <c r="I51" s="134"/>
+      <c r="J51" s="134"/>
+      <c r="K51" s="134"/>
+      <c r="L51" s="134"/>
+      <c r="M51" s="134"/>
+      <c r="N51" s="134"/>
+      <c r="O51" s="134"/>
+      <c r="P51" s="134"/>
+      <c r="Q51" s="134"/>
+      <c r="R51" s="135"/>
+    </row>
+    <row r="52" spans="1:18" ht="14.45">
+      <c r="A52" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="140"/>
-      <c r="C52" s="140"/>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="140"/>
-      <c r="H52" s="140"/>
-      <c r="I52" s="140"/>
-      <c r="J52" s="140"/>
-      <c r="K52" s="140"/>
-      <c r="L52" s="140"/>
-      <c r="M52" s="140"/>
-      <c r="N52" s="140"/>
-      <c r="O52" s="140"/>
-      <c r="P52" s="140"/>
-      <c r="Q52" s="140"/>
-      <c r="R52" s="141"/>
-    </row>
-    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B52" s="151"/>
+      <c r="C52" s="151"/>
+      <c r="D52" s="151"/>
+      <c r="E52" s="151"/>
+      <c r="F52" s="151"/>
+      <c r="G52" s="151"/>
+      <c r="H52" s="151"/>
+      <c r="I52" s="151"/>
+      <c r="J52" s="151"/>
+      <c r="K52" s="151"/>
+      <c r="L52" s="151"/>
+      <c r="M52" s="151"/>
+      <c r="N52" s="151"/>
+      <c r="O52" s="151"/>
+      <c r="P52" s="151"/>
+      <c r="Q52" s="151"/>
+      <c r="R52" s="152"/>
+    </row>
+    <row r="53" spans="1:18" ht="14.45">
       <c r="A53" s="83" t="s">
         <v>46</v>
       </c>
@@ -9883,106 +9883,144 @@
       </c>
       <c r="R53" s="67"/>
     </row>
-    <row r="54" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" ht="32.25" customHeight="1">
       <c r="A54" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="129" t="s">
+      <c r="B54" s="117" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="130"/>
-      <c r="D54" s="130"/>
-      <c r="E54" s="130"/>
-      <c r="F54" s="130"/>
-      <c r="G54" s="130"/>
-      <c r="H54" s="130"/>
-      <c r="I54" s="130"/>
-      <c r="J54" s="130"/>
-      <c r="K54" s="130"/>
-      <c r="L54" s="130"/>
-      <c r="M54" s="130"/>
-      <c r="N54" s="130"/>
-      <c r="O54" s="130"/>
-      <c r="P54" s="130"/>
-      <c r="Q54" s="130"/>
-      <c r="R54" s="131"/>
-    </row>
-    <row r="55" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C54" s="118"/>
+      <c r="D54" s="118"/>
+      <c r="E54" s="118"/>
+      <c r="F54" s="118"/>
+      <c r="G54" s="118"/>
+      <c r="H54" s="118"/>
+      <c r="I54" s="118"/>
+      <c r="J54" s="118"/>
+      <c r="K54" s="118"/>
+      <c r="L54" s="118"/>
+      <c r="M54" s="118"/>
+      <c r="N54" s="118"/>
+      <c r="O54" s="118"/>
+      <c r="P54" s="118"/>
+      <c r="Q54" s="118"/>
+      <c r="R54" s="119"/>
+    </row>
+    <row r="55" spans="1:18" ht="32.25" customHeight="1">
       <c r="A55" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="129" t="s">
+      <c r="B55" s="117" t="s">
         <v>51</v>
       </c>
-      <c r="C55" s="130"/>
-      <c r="D55" s="130"/>
-      <c r="E55" s="130"/>
-      <c r="F55" s="130"/>
-      <c r="G55" s="130"/>
-      <c r="H55" s="130"/>
-      <c r="I55" s="130"/>
-      <c r="J55" s="130"/>
-      <c r="K55" s="130"/>
-      <c r="L55" s="130"/>
-      <c r="M55" s="130"/>
-      <c r="N55" s="130"/>
-      <c r="O55" s="130"/>
-      <c r="P55" s="130"/>
-      <c r="Q55" s="130"/>
-      <c r="R55" s="131"/>
-    </row>
-    <row r="56" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C55" s="118"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="118"/>
+      <c r="G55" s="118"/>
+      <c r="H55" s="118"/>
+      <c r="I55" s="118"/>
+      <c r="J55" s="118"/>
+      <c r="K55" s="118"/>
+      <c r="L55" s="118"/>
+      <c r="M55" s="118"/>
+      <c r="N55" s="118"/>
+      <c r="O55" s="118"/>
+      <c r="P55" s="118"/>
+      <c r="Q55" s="118"/>
+      <c r="R55" s="119"/>
+    </row>
+    <row r="56" spans="1:18" ht="32.25" customHeight="1">
       <c r="A56" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="129" t="s">
+      <c r="B56" s="117" t="s">
         <v>53</v>
       </c>
-      <c r="C56" s="130"/>
-      <c r="D56" s="130"/>
-      <c r="E56" s="130"/>
-      <c r="F56" s="130"/>
-      <c r="G56" s="130"/>
-      <c r="H56" s="130"/>
-      <c r="I56" s="130"/>
-      <c r="J56" s="130"/>
-      <c r="K56" s="130"/>
-      <c r="L56" s="130"/>
-      <c r="M56" s="130"/>
-      <c r="N56" s="130"/>
-      <c r="O56" s="130"/>
-      <c r="P56" s="130"/>
-      <c r="Q56" s="130"/>
-      <c r="R56" s="131"/>
-    </row>
-    <row r="57" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C56" s="118"/>
+      <c r="D56" s="118"/>
+      <c r="E56" s="118"/>
+      <c r="F56" s="118"/>
+      <c r="G56" s="118"/>
+      <c r="H56" s="118"/>
+      <c r="I56" s="118"/>
+      <c r="J56" s="118"/>
+      <c r="K56" s="118"/>
+      <c r="L56" s="118"/>
+      <c r="M56" s="118"/>
+      <c r="N56" s="118"/>
+      <c r="O56" s="118"/>
+      <c r="P56" s="118"/>
+      <c r="Q56" s="118"/>
+      <c r="R56" s="119"/>
+    </row>
+    <row r="57" spans="1:18" ht="32.25" customHeight="1">
       <c r="A57" s="90" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="132" t="s">
+      <c r="B57" s="143" t="s">
         <v>55</v>
       </c>
-      <c r="C57" s="133"/>
-      <c r="D57" s="133"/>
-      <c r="E57" s="133"/>
-      <c r="F57" s="133"/>
-      <c r="G57" s="133"/>
-      <c r="H57" s="133"/>
-      <c r="I57" s="133"/>
-      <c r="J57" s="133"/>
-      <c r="K57" s="133"/>
-      <c r="L57" s="133"/>
-      <c r="M57" s="133"/>
-      <c r="N57" s="133"/>
-      <c r="O57" s="133"/>
-      <c r="P57" s="133"/>
-      <c r="Q57" s="133"/>
-      <c r="R57" s="134"/>
-    </row>
-    <row r="58" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="C57" s="144"/>
+      <c r="D57" s="144"/>
+      <c r="E57" s="144"/>
+      <c r="F57" s="144"/>
+      <c r="G57" s="144"/>
+      <c r="H57" s="144"/>
+      <c r="I57" s="144"/>
+      <c r="J57" s="144"/>
+      <c r="K57" s="144"/>
+      <c r="L57" s="144"/>
+      <c r="M57" s="144"/>
+      <c r="N57" s="144"/>
+      <c r="O57" s="144"/>
+      <c r="P57" s="144"/>
+      <c r="Q57" s="144"/>
+      <c r="R57" s="145"/>
+    </row>
+    <row r="58" spans="1:18" ht="15" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="54">
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B56:R56"/>
+    <mergeCell ref="B57:R57"/>
+    <mergeCell ref="G5:I6"/>
+    <mergeCell ref="J5:L6"/>
+    <mergeCell ref="A12:R12"/>
+    <mergeCell ref="A52:R52"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="D5:F6"/>
+    <mergeCell ref="M5:O6"/>
+    <mergeCell ref="P5:R6"/>
+    <mergeCell ref="A8:R8"/>
+    <mergeCell ref="A9:R10"/>
+    <mergeCell ref="A7:R7"/>
+    <mergeCell ref="A51:R51"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A28:D28"/>
     <mergeCell ref="B54:R54"/>
     <mergeCell ref="B55:R55"/>
     <mergeCell ref="G4:I4"/>
@@ -9999,44 +10037,6 @@
     <mergeCell ref="A50:R50"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B56:R56"/>
-    <mergeCell ref="B57:R57"/>
-    <mergeCell ref="G5:I6"/>
-    <mergeCell ref="J5:L6"/>
-    <mergeCell ref="A12:R12"/>
-    <mergeCell ref="A52:R52"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="D5:F6"/>
-    <mergeCell ref="M5:O6"/>
-    <mergeCell ref="P5:R6"/>
-    <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A9:R10"/>
-    <mergeCell ref="A7:R7"/>
-    <mergeCell ref="A51:R51"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="D24:D25"/>
   </mergeCells>
   <conditionalFormatting sqref="D14:D25">
     <cfRule type="dataBar" priority="1">
@@ -10237,13 +10237,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1877BE-C3D3-4865-8DAD-D82CCF22B69D}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="30.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="30.28515625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.95">
       <c r="A1" s="43" t="s">
         <v>56</v>
       </c>
@@ -10251,7 +10251,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" s="44" t="s">
         <v>58</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" s="44" t="s">
         <v>60</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" s="44" t="s">
         <v>43</v>
       </c>
@@ -10275,7 +10275,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" s="44" t="s">
         <v>63</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" s="44" t="s">
         <v>65</v>
       </c>
@@ -10291,7 +10291,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" s="44" t="s">
         <v>67</v>
       </c>
@@ -10299,7 +10299,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" s="44" t="s">
         <v>69</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" s="44" t="s">
         <v>71</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" s="44" t="s">
         <v>73</v>
       </c>
@@ -10332,64 +10332,64 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3218EFE-4B56-464B-9411-92BE99F13E89}">
   <dimension ref="A1:BB33"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="42" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="57" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.26953125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="5.1796875" style="36" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" style="36" customWidth="1"/>
-    <col min="7" max="7" width="8.54296875" style="36" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.26953125" style="36" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.26953125" style="36" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.1796875" style="36" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" style="35" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1796875" style="47" customWidth="1"/>
-    <col min="14" max="14" width="5.7265625" style="36" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.1796875" style="36" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.54296875" style="35" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.26953125" style="37" customWidth="1"/>
-    <col min="19" max="19" width="6.26953125" style="36" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.26953125" style="35" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.81640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.26953125" style="60" customWidth="1"/>
-    <col min="23" max="23" width="9.26953125" style="35" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.26953125" style="35" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.26953125" style="35" customWidth="1"/>
-    <col min="26" max="27" width="10.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.1796875" style="35" customWidth="1"/>
-    <col min="29" max="29" width="10.54296875" style="35" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="7.1796875" style="36" customWidth="1"/>
-    <col min="31" max="31" width="9.54296875" style="36" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="12.453125" style="35" customWidth="1"/>
-    <col min="34" max="34" width="8.81640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.1796875" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="36" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" style="35" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="35" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="47" customWidth="1"/>
+    <col min="14" max="14" width="5.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" style="37" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" style="35" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" style="60" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.28515625" style="35" customWidth="1"/>
+    <col min="26" max="27" width="10.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.140625" style="35" customWidth="1"/>
+    <col min="29" max="29" width="10.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="7.140625" style="36" customWidth="1"/>
+    <col min="31" max="31" width="9.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="12.42578125" style="35" customWidth="1"/>
+    <col min="34" max="34" width="8.85546875" style="35" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6.140625" style="37" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="18" style="69" customWidth="1"/>
     <col min="37" max="37" width="11" style="35" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="10.7265625" style="35" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="8.26953125" style="35" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.26953125" style="35" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="16.1796875" style="2" customWidth="1"/>
+    <col min="38" max="38" width="10.7109375" style="35" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="8.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="16.140625" style="2" customWidth="1"/>
     <col min="42" max="42" width="8" style="35" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="7.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="5.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="9.453125" style="35" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="10.1796875" style="36" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="7.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="5.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.42578125" style="35" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10.140625" style="36" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="11" style="36" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="7" style="36" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="6" style="36" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="8" style="36" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="7.7265625" style="36" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="11.7265625" style="36" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="8.453125" style="36" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="10.1796875" style="41" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="11.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="8.42578125" style="36" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.140625" style="41" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="63" style="13" customWidth="1"/>
     <col min="56" max="16384" width="0" style="13" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="30" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:54" s="30" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="99" t="s">
         <v>27</v>
       </c>
@@ -10432,32 +10432,32 @@
       <c r="AH1" s="103"/>
       <c r="AI1" s="103"/>
       <c r="AJ1" s="104"/>
-      <c r="AK1" s="176" t="s">
+      <c r="AK1" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="AL1" s="176"/>
-      <c r="AM1" s="176"/>
-      <c r="AN1" s="176"/>
-      <c r="AO1" s="176"/>
-      <c r="AP1" s="177" t="s">
+      <c r="AL1" s="174"/>
+      <c r="AM1" s="174"/>
+      <c r="AN1" s="174"/>
+      <c r="AO1" s="174"/>
+      <c r="AP1" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="AQ1" s="177"/>
-      <c r="AR1" s="177"/>
-      <c r="AS1" s="177"/>
-      <c r="AT1" s="177"/>
-      <c r="AU1" s="174" t="s">
+      <c r="AQ1" s="175"/>
+      <c r="AR1" s="175"/>
+      <c r="AS1" s="175"/>
+      <c r="AT1" s="175"/>
+      <c r="AU1" s="172" t="s">
         <v>77</v>
       </c>
-      <c r="AV1" s="174"/>
-      <c r="AW1" s="174"/>
-      <c r="AX1" s="174"/>
-      <c r="AY1" s="174"/>
-      <c r="AZ1" s="174"/>
-      <c r="BA1" s="174"/>
-      <c r="BB1" s="175"/>
-    </row>
-    <row r="2" spans="1:54" s="1" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AV1" s="172"/>
+      <c r="AW1" s="172"/>
+      <c r="AX1" s="172"/>
+      <c r="AY1" s="172"/>
+      <c r="AZ1" s="172"/>
+      <c r="BA1" s="172"/>
+      <c r="BB1" s="173"/>
+    </row>
+    <row r="2" spans="1:54" s="1" customFormat="1" ht="50.25" customHeight="1">
       <c r="A2" s="52" t="s">
         <v>78</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:54" ht="30" customHeight="1">
       <c r="A3" s="40">
         <v>1</v>
       </c>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="AQ3" s="33"/>
     </row>
-    <row r="4" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:54" ht="30" customHeight="1">
       <c r="A4" s="40">
         <v>2</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:54" ht="30" customHeight="1">
       <c r="A5" s="40">
         <v>3</v>
       </c>
@@ -10939,7 +10939,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:54" ht="30" customHeight="1">
       <c r="A6" s="40">
         <v>4</v>
       </c>
@@ -11045,7 +11045,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:54" ht="30" customHeight="1">
       <c r="A7" s="40">
         <v>5</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:54" ht="30" customHeight="1">
       <c r="A8" s="40">
         <v>6</v>
       </c>
@@ -11257,7 +11257,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:54" ht="30" customHeight="1">
       <c r="A9" s="40">
         <v>7</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="10" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:54" ht="30" customHeight="1">
       <c r="A10" s="40">
         <v>8</v>
       </c>
@@ -11467,7 +11467,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="11" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:54" ht="30" customHeight="1">
       <c r="A11" s="40">
         <v>9</v>
       </c>
@@ -11572,7 +11572,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="12" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:54" ht="30" customHeight="1">
       <c r="A12" s="40">
         <v>10</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="13" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:54" ht="30" customHeight="1">
       <c r="A13" s="40">
         <v>11</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="14" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:54" ht="30" customHeight="1">
       <c r="A14" s="40">
         <v>12</v>
       </c>
@@ -11887,7 +11887,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="15" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:54" ht="30" customHeight="1">
       <c r="A15" s="40">
         <v>13</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="16" spans="1:54" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:54" ht="30" customHeight="1">
       <c r="A16" s="40">
         <v>14</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" ht="30" customHeight="1">
       <c r="A17" s="40">
         <v>15</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" ht="30" customHeight="1">
       <c r="A18" s="40">
         <v>16</v>
       </c>
@@ -12287,7 +12287,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" ht="30" customHeight="1">
       <c r="A19" s="40">
         <v>17</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" ht="30" customHeight="1">
       <c r="A20" s="40">
         <v>18</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" ht="30" customHeight="1">
       <c r="A21" s="40">
         <v>19</v>
       </c>
@@ -12581,32 +12581,32 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" ht="30" customHeight="1">
       <c r="V22" s="59"/>
     </row>
-    <row r="23" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="1:36" ht="30" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:36" ht="14.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" ht="30" customHeight="1"/>
+    <row r="24" spans="1:36" ht="30" customHeight="1"/>
+    <row r="25" spans="1:36" ht="30" customHeight="1"/>
+    <row r="26" spans="1:36" ht="30" customHeight="1"/>
+    <row r="27" spans="1:36" ht="30" customHeight="1"/>
+    <row r="28" spans="1:36" ht="30" customHeight="1"/>
+    <row r="29" spans="1:36" ht="30" customHeight="1"/>
+    <row r="30" spans="1:36" ht="14.45" hidden="1">
       <c r="D30" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" ht="0" hidden="1" customHeight="1">
       <c r="D31" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" ht="0" hidden="1" customHeight="1">
       <c r="D32" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="33" spans="4:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="4:4" ht="0" hidden="1" customHeight="1">
       <c r="D33" s="2" t="s">
         <v>166</v>
       </c>
@@ -12684,67 +12684,67 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:BD179"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" outlineLevelCol="3" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="5.7265625" style="42" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" style="42" customWidth="1"/>
     <col min="2" max="2" width="8" style="57" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" style="36" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.81640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="36" customWidth="1"/>
-    <col min="6" max="6" width="8.453125" style="36" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="36" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="36" customWidth="1"/>
     <col min="7" max="7" width="17" style="36" customWidth="1"/>
-    <col min="8" max="8" width="8.26953125" style="36" customWidth="1"/>
-    <col min="9" max="9" width="7.26953125" style="36" customWidth="1"/>
-    <col min="10" max="10" width="4.26953125" style="36" customWidth="1"/>
-    <col min="11" max="11" width="4.1796875" style="36" customWidth="1"/>
-    <col min="12" max="12" width="9.453125" style="35" customWidth="1"/>
-    <col min="13" max="13" width="9.7265625" style="35" customWidth="1"/>
-    <col min="14" max="14" width="9.1796875" style="47" customWidth="1"/>
-    <col min="15" max="15" width="5.7265625" style="36" customWidth="1"/>
-    <col min="16" max="16" width="8.54296875" style="36" customWidth="1"/>
-    <col min="17" max="18" width="10.54296875" style="35" customWidth="1" outlineLevel="3"/>
-    <col min="19" max="19" width="7.26953125" style="37" customWidth="1" outlineLevel="3"/>
-    <col min="20" max="20" width="6.26953125" style="36" customWidth="1" outlineLevel="3"/>
-    <col min="21" max="21" width="9.26953125" style="35" customWidth="1" outlineLevel="3"/>
-    <col min="22" max="22" width="9.81640625" style="35" customWidth="1" outlineLevel="3"/>
-    <col min="23" max="23" width="17.26953125" style="60" customWidth="1" outlineLevel="3"/>
-    <col min="24" max="24" width="9.26953125" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="25" max="25" width="10.1796875" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="26" max="26" width="12.26953125" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="27" max="27" width="10.1796875" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="28" max="28" width="12.26953125" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="29" max="29" width="11.1796875" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="30" max="30" width="10.54296875" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="31" max="31" width="33.7265625" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="32" max="32" width="7.1796875" style="36" customWidth="1" outlineLevel="2"/>
-    <col min="33" max="33" width="9.453125" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="34" max="34" width="9.54296875" style="36" customWidth="1" outlineLevel="2"/>
-    <col min="35" max="36" width="12.453125" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="8" max="8" width="8.28515625" style="36" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" style="36" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" style="36" customWidth="1"/>
+    <col min="11" max="11" width="4.140625" style="36" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="35" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="35" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="47" customWidth="1"/>
+    <col min="15" max="15" width="5.7109375" style="36" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" style="36" customWidth="1"/>
+    <col min="17" max="18" width="10.5703125" style="35" customWidth="1" outlineLevel="3"/>
+    <col min="19" max="19" width="7.28515625" style="37" customWidth="1" outlineLevel="3"/>
+    <col min="20" max="20" width="6.28515625" style="36" customWidth="1" outlineLevel="3"/>
+    <col min="21" max="21" width="9.28515625" style="35" customWidth="1" outlineLevel="3"/>
+    <col min="22" max="22" width="9.85546875" style="35" customWidth="1" outlineLevel="3"/>
+    <col min="23" max="23" width="17.28515625" style="60" customWidth="1" outlineLevel="3"/>
+    <col min="24" max="24" width="9.28515625" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="25" max="25" width="10.140625" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="26" max="26" width="12.28515625" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="27" max="27" width="10.140625" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="28" max="28" width="12.28515625" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="29" max="29" width="11.140625" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="30" max="30" width="10.5703125" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="31" max="31" width="33.7109375" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="32" max="32" width="7.140625" style="36" customWidth="1" outlineLevel="2"/>
+    <col min="33" max="33" width="9.42578125" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="34" max="34" width="9.5703125" style="36" customWidth="1" outlineLevel="2"/>
+    <col min="35" max="36" width="12.42578125" style="35" customWidth="1" outlineLevel="2"/>
     <col min="37" max="37" width="8" style="37" customWidth="1" outlineLevel="2"/>
-    <col min="38" max="38" width="33.7265625" style="69" customWidth="1" outlineLevel="2"/>
+    <col min="38" max="38" width="33.7109375" style="69" customWidth="1" outlineLevel="2"/>
     <col min="39" max="39" width="11" style="35" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.7265625" style="35" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.26953125" style="35" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.26953125" style="35" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.26953125" style="2" customWidth="1"/>
+    <col min="40" max="40" width="10.7109375" style="35" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.28515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.28515625" style="2" customWidth="1"/>
     <col min="44" max="44" width="8" style="35" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="7.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="5.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="9.453125" style="35" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.1796875" style="36" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="7.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="5.140625" style="35" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="9.42578125" style="35" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.140625" style="36" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="11" style="36" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" style="36" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="6" style="36" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="8" style="36" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="7.7265625" style="36" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="11.7265625" style="36" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="8.453125" style="36" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="10.1796875" style="41" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="7.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="11.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="8.42578125" style="36" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="10.140625" style="41" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="63" style="13" customWidth="1"/>
     <col min="58" max="16384" width="0" style="13" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" s="30" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:56" s="30" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="99" t="s">
         <v>27</v>
       </c>
@@ -12814,7 +12814,7 @@
       <c r="BC1" s="106"/>
       <c r="BD1" s="107"/>
     </row>
-    <row r="2" spans="1:56" s="1" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:56" s="1" customFormat="1" ht="50.25" customHeight="1">
       <c r="A2" s="52" t="s">
         <v>78</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:56" ht="30" customHeight="1">
       <c r="A3" s="40">
         <v>1</v>
       </c>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="AL3" s="58"/>
     </row>
-    <row r="4" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:56" ht="30" customHeight="1">
       <c r="A4" s="40">
         <v>2</v>
       </c>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="AL4" s="58"/>
     </row>
-    <row r="5" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:56" ht="30" customHeight="1">
       <c r="A5" s="40">
         <v>3</v>
       </c>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="AL5" s="58"/>
     </row>
-    <row r="6" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:56" ht="30" customHeight="1">
       <c r="A6" s="40">
         <v>4</v>
       </c>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="AL6" s="58"/>
     </row>
-    <row r="7" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:56" ht="30" customHeight="1">
       <c r="A7" s="40">
         <v>5</v>
       </c>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="AL7" s="58"/>
     </row>
-    <row r="8" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:56" ht="30" customHeight="1">
       <c r="A8" s="40">
         <v>6</v>
       </c>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="AL8" s="58"/>
     </row>
-    <row r="9" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:56" ht="30" customHeight="1">
       <c r="A9" s="40">
         <v>7</v>
       </c>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="AL9" s="58"/>
     </row>
-    <row r="10" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:56" ht="30" customHeight="1">
       <c r="A10" s="40">
         <v>8</v>
       </c>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="AL10" s="58"/>
     </row>
-    <row r="11" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:56" ht="30" customHeight="1">
       <c r="A11" s="40">
         <v>9</v>
       </c>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="AL11" s="58"/>
     </row>
-    <row r="12" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:56" ht="30" customHeight="1">
       <c r="A12" s="40">
         <v>10</v>
       </c>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AL12" s="58"/>
     </row>
-    <row r="13" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:56" ht="30" customHeight="1">
       <c r="A13" s="40">
         <v>11</v>
       </c>
@@ -13745,7 +13745,7 @@
       </c>
       <c r="AL13" s="58"/>
     </row>
-    <row r="14" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:56" ht="30" customHeight="1">
       <c r="A14" s="40">
         <v>12</v>
       </c>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="AL14" s="58"/>
     </row>
-    <row r="15" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:56" ht="30" customHeight="1">
       <c r="A15" s="40">
         <v>13</v>
       </c>
@@ -13883,7 +13883,7 @@
       </c>
       <c r="AL15" s="58"/>
     </row>
-    <row r="16" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:56" ht="30" customHeight="1">
       <c r="A16" s="40">
         <v>14</v>
       </c>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="AL16" s="58"/>
     </row>
-    <row r="17" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:45" ht="30" customHeight="1">
       <c r="A17" s="40">
         <v>15</v>
       </c>
@@ -14021,7 +14021,7 @@
       </c>
       <c r="AL17" s="58"/>
     </row>
-    <row r="18" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:45" ht="30" customHeight="1">
       <c r="A18" s="40">
         <v>16</v>
       </c>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="AL18" s="58"/>
     </row>
-    <row r="19" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:45" ht="30" customHeight="1">
       <c r="A19" s="40">
         <v>17</v>
       </c>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="AL19" s="58"/>
     </row>
-    <row r="20" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:45" ht="30" customHeight="1">
       <c r="A20" s="40">
         <v>18</v>
       </c>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="AL20" s="58"/>
     </row>
-    <row r="21" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:45" ht="30" customHeight="1">
       <c r="A21" s="40">
         <v>19</v>
       </c>
@@ -14297,7 +14297,7 @@
       </c>
       <c r="AL21" s="58"/>
     </row>
-    <row r="22" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:45" ht="30" customHeight="1">
       <c r="A22" s="40">
         <v>20</v>
       </c>
@@ -14367,7 +14367,7 @@
       </c>
       <c r="AL22" s="58"/>
     </row>
-    <row r="23" spans="1:45" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:45" ht="30" hidden="1" customHeight="1">
       <c r="A23" s="40">
         <v>21</v>
       </c>
@@ -14488,7 +14488,7 @@
       <c r="AL23" s="58"/>
       <c r="AS23" s="33"/>
     </row>
-    <row r="24" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:45" ht="30" customHeight="1">
       <c r="A24" s="40">
         <v>22</v>
       </c>
@@ -14557,7 +14557,7 @@
       </c>
       <c r="AL24" s="58"/>
     </row>
-    <row r="25" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:45" ht="30" customHeight="1">
       <c r="A25" s="40">
         <v>23</v>
       </c>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="AL25" s="58"/>
     </row>
-    <row r="26" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:45" ht="30" customHeight="1">
       <c r="A26" s="40">
         <v>24</v>
       </c>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="AL26" s="58"/>
     </row>
-    <row r="27" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:45" ht="30" customHeight="1">
       <c r="A27" s="40">
         <v>25</v>
       </c>
@@ -14764,7 +14764,7 @@
       </c>
       <c r="AL27" s="58"/>
     </row>
-    <row r="28" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:45" ht="30" customHeight="1">
       <c r="A28" s="40">
         <v>26</v>
       </c>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="AL28" s="58"/>
     </row>
-    <row r="29" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:45" ht="30" customHeight="1">
       <c r="A29" s="40">
         <v>27</v>
       </c>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="AL29" s="58"/>
     </row>
-    <row r="30" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:45" ht="30" customHeight="1">
       <c r="A30" s="40">
         <v>28</v>
       </c>
@@ -14971,7 +14971,7 @@
       </c>
       <c r="AL30" s="58"/>
     </row>
-    <row r="31" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:45" ht="30" customHeight="1">
       <c r="A31" s="40">
         <v>29</v>
       </c>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="AL31" s="58"/>
     </row>
-    <row r="32" spans="1:45" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:45" ht="30" customHeight="1">
       <c r="A32" s="40">
         <v>30</v>
       </c>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="AL32" s="58"/>
     </row>
-    <row r="33" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" ht="30" customHeight="1">
       <c r="A33" s="40">
         <v>31</v>
       </c>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="AL33" s="58"/>
     </row>
-    <row r="34" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" ht="30" customHeight="1">
       <c r="A34" s="40">
         <v>32</v>
       </c>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="AL34" s="58"/>
     </row>
-    <row r="35" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" ht="30" customHeight="1">
       <c r="A35" s="40">
         <v>33</v>
       </c>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="AL35" s="58"/>
     </row>
-    <row r="36" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" ht="30" customHeight="1">
       <c r="A36" s="40">
         <v>34</v>
       </c>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="AL36" s="58"/>
     </row>
-    <row r="37" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" ht="30" customHeight="1">
       <c r="A37" s="40">
         <v>35</v>
       </c>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="AL37" s="58"/>
     </row>
-    <row r="38" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" ht="30" customHeight="1">
       <c r="A38" s="40">
         <v>36</v>
       </c>
@@ -15525,7 +15525,7 @@
       </c>
       <c r="AL38" s="58"/>
     </row>
-    <row r="39" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" ht="30" customHeight="1">
       <c r="A39" s="40">
         <v>37</v>
       </c>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="AL39" s="58"/>
     </row>
-    <row r="40" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" ht="30" customHeight="1">
       <c r="A40" s="40">
         <v>38</v>
       </c>
@@ -15663,7 +15663,7 @@
       </c>
       <c r="AL40" s="58"/>
     </row>
-    <row r="41" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" ht="30" customHeight="1">
       <c r="A41" s="40">
         <v>39</v>
       </c>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="AL41" s="58"/>
     </row>
-    <row r="42" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A42" s="40">
         <v>40</v>
       </c>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="AL42" s="58"/>
     </row>
-    <row r="43" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A43" s="40">
         <v>41</v>
       </c>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="AL43" s="58"/>
     </row>
-    <row r="44" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A44" s="40">
         <v>42</v>
       </c>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="AL44" s="58"/>
     </row>
-    <row r="45" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A45" s="40">
         <v>43</v>
       </c>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="AL45" s="58"/>
     </row>
-    <row r="46" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A46" s="40">
         <v>44</v>
       </c>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="AL46" s="58"/>
     </row>
-    <row r="47" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" ht="30" customHeight="1">
       <c r="A47" s="40">
         <v>45</v>
       </c>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="AL47" s="58"/>
     </row>
-    <row r="48" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A48" s="40">
         <v>46</v>
       </c>
@@ -16412,7 +16412,7 @@
       </c>
       <c r="AL48" s="58"/>
     </row>
-    <row r="49" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:43" ht="30" customHeight="1">
       <c r="A49" s="40">
         <v>47</v>
       </c>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="AL49" s="58"/>
     </row>
-    <row r="50" spans="1:43" ht="36.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:43" ht="36.6" hidden="1" customHeight="1">
       <c r="A50" s="40">
         <v>48</v>
       </c>
@@ -16585,7 +16585,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:43" ht="30" customHeight="1">
       <c r="A51" s="40">
         <v>49</v>
       </c>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="AL51" s="58"/>
     </row>
-    <row r="52" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:43" ht="30" customHeight="1">
       <c r="A52" s="40">
         <v>50</v>
       </c>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AL52" s="58"/>
     </row>
-    <row r="53" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A53" s="40">
         <v>51</v>
       </c>
@@ -16840,7 +16840,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="54" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A54" s="40">
         <v>52</v>
       </c>
@@ -16956,7 +16956,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="55" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A55" s="40">
         <v>53</v>
       </c>
@@ -17072,7 +17072,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="56" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A56" s="40">
         <v>54</v>
       </c>
@@ -17188,7 +17188,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="57" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A57" s="40">
         <v>55</v>
       </c>
@@ -17304,7 +17304,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="58" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A58" s="40">
         <v>56</v>
       </c>
@@ -17420,7 +17420,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="59" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A59" s="40">
         <v>57</v>
       </c>
@@ -17536,7 +17536,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="60" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A60" s="40">
         <v>58</v>
       </c>
@@ -17652,7 +17652,7 @@
         <v>46286</v>
       </c>
     </row>
-    <row r="61" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A61" s="40">
         <v>59</v>
       </c>
@@ -17768,7 +17768,7 @@
       </c>
       <c r="AL61" s="58"/>
     </row>
-    <row r="62" spans="1:43" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:43" ht="30" hidden="1" customHeight="1">
       <c r="A62" s="40">
         <v>60</v>
       </c>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AL62" s="58"/>
     </row>
-    <row r="63" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:43" ht="30" customHeight="1">
       <c r="A63" s="40">
         <v>61</v>
       </c>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="AL63" s="58"/>
     </row>
-    <row r="64" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:43" ht="30" customHeight="1">
       <c r="A64" s="40">
         <v>62</v>
       </c>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AL64" s="58"/>
     </row>
-    <row r="65" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:38" ht="30" customHeight="1">
       <c r="A65" s="40">
         <v>63</v>
       </c>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="AL65" s="58"/>
     </row>
-    <row r="66" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A66" s="40">
         <v>64</v>
       </c>
@@ -18188,7 +18188,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="67" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A67" s="40">
         <v>65</v>
       </c>
@@ -18302,7 +18302,7 @@
       </c>
       <c r="AL67" s="58"/>
     </row>
-    <row r="68" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:38" ht="30" customHeight="1">
       <c r="A68" s="40">
         <v>66</v>
       </c>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="AL68" s="58"/>
     </row>
-    <row r="69" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:38" ht="30" customHeight="1">
       <c r="A69" s="40">
         <v>67</v>
       </c>
@@ -18436,7 +18436,7 @@
       </c>
       <c r="AL69" s="58"/>
     </row>
-    <row r="70" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:38" ht="30" customHeight="1">
       <c r="A70" s="40">
         <v>68</v>
       </c>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="AL70" s="58"/>
     </row>
-    <row r="71" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:38" ht="30" customHeight="1">
       <c r="A71" s="40">
         <v>70</v>
       </c>
@@ -18570,7 +18570,7 @@
       </c>
       <c r="AL71" s="58"/>
     </row>
-    <row r="72" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:38" ht="30" hidden="1" customHeight="1">
       <c r="A72" s="40">
         <v>69</v>
       </c>
@@ -18688,7 +18688,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="73" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:38" ht="30" customHeight="1">
       <c r="A73" s="40">
         <v>71</v>
       </c>
@@ -18755,7 +18755,7 @@
       </c>
       <c r="AL73" s="58"/>
     </row>
-    <row r="74" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:38" ht="30" customHeight="1">
       <c r="A74" s="40">
         <v>72</v>
       </c>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AL74" s="58"/>
     </row>
-    <row r="75" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:38" ht="30" customHeight="1">
       <c r="A75" s="40">
         <v>73</v>
       </c>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="AL75" s="58"/>
     </row>
-    <row r="76" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:38" ht="30" customHeight="1">
       <c r="A76" s="40">
         <v>74</v>
       </c>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="AL76" s="58"/>
     </row>
-    <row r="77" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:38" ht="30" customHeight="1">
       <c r="A77" s="40">
         <v>75</v>
       </c>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AL77" s="58"/>
     </row>
-    <row r="78" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:38" ht="30" customHeight="1">
       <c r="A78" s="40">
         <v>76</v>
       </c>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="AL78" s="58"/>
     </row>
-    <row r="79" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:38" ht="30" customHeight="1">
       <c r="A79" s="40">
         <v>77</v>
       </c>
@@ -19167,7 +19167,7 @@
       </c>
       <c r="AL79" s="58"/>
     </row>
-    <row r="80" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:38" ht="30" customHeight="1">
       <c r="A80" s="40">
         <v>78</v>
       </c>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="AL80" s="58"/>
     </row>
-    <row r="81" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:38" ht="30" customHeight="1">
       <c r="A81" s="40">
         <v>79</v>
       </c>
@@ -19305,7 +19305,7 @@
       </c>
       <c r="AL81" s="58"/>
     </row>
-    <row r="82" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:38" ht="30" customHeight="1">
       <c r="A82" s="40">
         <v>80</v>
       </c>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="AL82" s="58"/>
     </row>
-    <row r="83" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:38" ht="30" customHeight="1">
       <c r="A83" s="40">
         <v>81</v>
       </c>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="AL83" s="58"/>
     </row>
-    <row r="84" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:38" ht="30" customHeight="1">
       <c r="A84" s="40">
         <v>82</v>
       </c>
@@ -19512,7 +19512,7 @@
       </c>
       <c r="AL84" s="58"/>
     </row>
-    <row r="85" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:38" ht="30" customHeight="1">
       <c r="A85" s="40">
         <v>83</v>
       </c>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="AL85" s="58"/>
     </row>
-    <row r="86" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:38" ht="30" customHeight="1">
       <c r="A86" s="40">
         <v>84</v>
       </c>
@@ -19650,7 +19650,7 @@
       </c>
       <c r="AL86" s="58"/>
     </row>
-    <row r="87" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:38" ht="30" customHeight="1">
       <c r="A87" s="40">
         <v>85</v>
       </c>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="AL87" s="58"/>
     </row>
-    <row r="88" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:38" ht="30" customHeight="1">
       <c r="A88" s="40">
         <v>86</v>
       </c>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="AL88" s="58"/>
     </row>
-    <row r="89" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:38" ht="30" customHeight="1">
       <c r="A89" s="40">
         <v>87</v>
       </c>
@@ -19857,7 +19857,7 @@
       </c>
       <c r="AL89" s="58"/>
     </row>
-    <row r="90" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:38" ht="30" customHeight="1">
       <c r="A90" s="40">
         <v>88</v>
       </c>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="AL90" s="58"/>
     </row>
-    <row r="91" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:38" ht="30" customHeight="1">
       <c r="A91" s="40">
         <v>89</v>
       </c>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="AL91" s="58"/>
     </row>
-    <row r="92" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:38" ht="30" customHeight="1">
       <c r="A92" s="40">
         <v>90</v>
       </c>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="AL92" s="58"/>
     </row>
-    <row r="93" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:38" ht="30" customHeight="1">
       <c r="A93" s="40">
         <v>91</v>
       </c>
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AL93" s="58"/>
     </row>
-    <row r="94" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:38" ht="30" customHeight="1">
       <c r="A94" s="40">
         <v>92</v>
       </c>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="AL94" s="58"/>
     </row>
-    <row r="95" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:38" ht="30" customHeight="1">
       <c r="A95" s="40">
         <v>93</v>
       </c>
@@ -20271,7 +20271,7 @@
       </c>
       <c r="AL95" s="58"/>
     </row>
-    <row r="96" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:38" ht="30" customHeight="1">
       <c r="A96" s="40">
         <v>94</v>
       </c>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="AL96" s="58"/>
     </row>
-    <row r="97" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:38" ht="30" customHeight="1">
       <c r="A97" s="40">
         <v>95</v>
       </c>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="AL97" s="58"/>
     </row>
-    <row r="98" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:38" ht="30" customHeight="1">
       <c r="A98" s="40">
         <v>96</v>
       </c>
@@ -20472,7 +20472,7 @@
       </c>
       <c r="AL98" s="58"/>
     </row>
-    <row r="99" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:38" ht="30" customHeight="1">
       <c r="A99" s="40">
         <v>97</v>
       </c>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AL99" s="58"/>
     </row>
-    <row r="100" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:38" ht="30" customHeight="1">
       <c r="A100" s="40">
         <v>98</v>
       </c>
@@ -20608,7 +20608,7 @@
       </c>
       <c r="AL100" s="58"/>
     </row>
-    <row r="101" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:38" ht="30" customHeight="1">
       <c r="A101" s="40">
         <v>99</v>
       </c>
@@ -20677,7 +20677,7 @@
       </c>
       <c r="AL101" s="58"/>
     </row>
-    <row r="102" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:38" ht="30" customHeight="1">
       <c r="A102" s="40">
         <v>100</v>
       </c>
@@ -20746,7 +20746,7 @@
       </c>
       <c r="AL102" s="58"/>
     </row>
-    <row r="103" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:38" ht="30" customHeight="1">
       <c r="A103" s="40">
         <v>101</v>
       </c>
@@ -20815,7 +20815,7 @@
       </c>
       <c r="AL103" s="58"/>
     </row>
-    <row r="104" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:38" ht="30" customHeight="1">
       <c r="A104" s="40">
         <v>102</v>
       </c>
@@ -20884,7 +20884,7 @@
       </c>
       <c r="AL104" s="58"/>
     </row>
-    <row r="105" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:38" ht="30" customHeight="1">
       <c r="A105" s="40">
         <v>103</v>
       </c>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="AL105" s="58"/>
     </row>
-    <row r="106" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:38" ht="30" customHeight="1">
       <c r="A106" s="40">
         <v>104</v>
       </c>
@@ -21017,7 +21017,7 @@
       </c>
       <c r="AL106" s="58"/>
     </row>
-    <row r="107" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:38" ht="30" customHeight="1">
       <c r="A107" s="40">
         <v>105</v>
       </c>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="AL107" s="58"/>
     </row>
-    <row r="108" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:38" ht="30" customHeight="1">
       <c r="A108" s="40">
         <v>106</v>
       </c>
@@ -21143,91 +21143,91 @@
       </c>
       <c r="AL108" s="58"/>
     </row>
-    <row r="109" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:38" ht="30" customHeight="1">
       <c r="B109" s="33"/>
     </row>
-    <row r="110" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" spans="1:38" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="120" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="121" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="122" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="126" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="127" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" spans="4:4" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" spans="4:4" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:38" ht="30" hidden="1" customHeight="1"/>
+    <row r="111" spans="1:38" ht="30" hidden="1" customHeight="1"/>
+    <row r="112" spans="1:38" ht="30" hidden="1" customHeight="1"/>
+    <row r="113" ht="30" hidden="1" customHeight="1"/>
+    <row r="114" ht="30" hidden="1" customHeight="1"/>
+    <row r="115" ht="30" hidden="1" customHeight="1"/>
+    <row r="116" ht="30" hidden="1" customHeight="1"/>
+    <row r="117" ht="30" hidden="1" customHeight="1"/>
+    <row r="118" ht="30" hidden="1" customHeight="1"/>
+    <row r="119" ht="30" hidden="1" customHeight="1"/>
+    <row r="120" ht="30" hidden="1" customHeight="1"/>
+    <row r="121" ht="30" hidden="1" customHeight="1"/>
+    <row r="122" ht="30" hidden="1" customHeight="1"/>
+    <row r="123" ht="30" hidden="1" customHeight="1"/>
+    <row r="124" ht="30" hidden="1" customHeight="1"/>
+    <row r="125" ht="30" hidden="1" customHeight="1"/>
+    <row r="126" ht="30" hidden="1" customHeight="1"/>
+    <row r="127" ht="30" hidden="1" customHeight="1"/>
+    <row r="128" ht="30" hidden="1" customHeight="1"/>
+    <row r="129" ht="30" hidden="1" customHeight="1"/>
+    <row r="130" ht="30" hidden="1" customHeight="1"/>
+    <row r="131" ht="30" hidden="1" customHeight="1"/>
+    <row r="132" ht="30" hidden="1" customHeight="1"/>
+    <row r="133" ht="30" hidden="1" customHeight="1"/>
+    <row r="134" ht="30" hidden="1" customHeight="1"/>
+    <row r="135" ht="30" hidden="1" customHeight="1"/>
+    <row r="136" ht="30" hidden="1" customHeight="1"/>
+    <row r="137" ht="30" hidden="1" customHeight="1"/>
+    <row r="138" ht="30" hidden="1" customHeight="1"/>
+    <row r="139" ht="30" hidden="1" customHeight="1"/>
+    <row r="140" ht="30" hidden="1" customHeight="1"/>
+    <row r="141" ht="30" hidden="1" customHeight="1"/>
+    <row r="142" ht="30" hidden="1" customHeight="1"/>
+    <row r="143" ht="30" hidden="1" customHeight="1"/>
+    <row r="144" ht="30" hidden="1" customHeight="1"/>
+    <row r="145" ht="30" hidden="1" customHeight="1"/>
+    <row r="146" ht="30" hidden="1" customHeight="1"/>
+    <row r="147" ht="30" hidden="1" customHeight="1"/>
+    <row r="148" ht="30" hidden="1" customHeight="1"/>
+    <row r="149" ht="30" hidden="1" customHeight="1"/>
+    <row r="150" ht="30" hidden="1" customHeight="1"/>
+    <row r="151" ht="30" hidden="1" customHeight="1"/>
+    <row r="152" ht="30" hidden="1" customHeight="1"/>
+    <row r="153" ht="30" hidden="1" customHeight="1"/>
+    <row r="154" ht="30" hidden="1" customHeight="1"/>
+    <row r="155" ht="30" hidden="1" customHeight="1"/>
+    <row r="156" ht="30" hidden="1" customHeight="1"/>
+    <row r="157" ht="30" hidden="1" customHeight="1"/>
+    <row r="158" ht="30" hidden="1" customHeight="1"/>
+    <row r="159" ht="30" hidden="1" customHeight="1"/>
+    <row r="160" ht="30" hidden="1" customHeight="1"/>
+    <row r="161" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="162" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="163" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="164" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="165" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="166" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="167" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="168" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="169" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="170" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="171" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="172" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="173" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="174" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="175" spans="4:4" ht="30" hidden="1" customHeight="1"/>
+    <row r="176" spans="4:4" ht="15" hidden="1" customHeight="1">
       <c r="D176" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="177" spans="4:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="4:4" ht="0" hidden="1" customHeight="1">
       <c r="D177" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="178" spans="4:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="4:4" ht="0" hidden="1" customHeight="1">
       <c r="D178" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="179" spans="4:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="4:4" ht="0" hidden="1" customHeight="1">
       <c r="D179" s="2" t="s">
         <v>166</v>
       </c>
@@ -21324,20 +21324,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60BC4B6-37BA-4A83-A06A-ACBCD4185354}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.95"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="6" customWidth="1"/>
-    <col min="4" max="4" width="17.54296875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="12.7265625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="13.54296875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="9.1796875" style="6"/>
+    <col min="4" max="4" width="17.5703125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" style="6" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="26.1">
       <c r="A1" s="3" t="s">
         <v>56</v>
       </c>
@@ -21363,7 +21363,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="7" t="s">
         <v>58</v>
       </c>
@@ -21389,7 +21389,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="7" t="s">
         <v>60</v>
       </c>
@@ -21415,7 +21415,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="7" t="s">
         <v>43</v>
       </c>
@@ -21441,7 +21441,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="7" t="s">
         <v>63</v>
       </c>
@@ -21467,7 +21467,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="7" t="s">
         <v>65</v>
       </c>
@@ -21493,7 +21493,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="7" t="s">
         <v>67</v>
       </c>
@@ -21519,7 +21519,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="7" t="s">
         <v>69</v>
       </c>
@@ -21545,7 +21545,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="7" t="s">
         <v>71</v>
       </c>
@@ -21571,7 +21571,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="8" t="s">
         <v>73</v>
       </c>
@@ -21597,29 +21597,29 @@
         <v>342</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="181"/>
-      <c r="B11" s="181"/>
-      <c r="C11" s="181"/>
-      <c r="D11" s="181"/>
-      <c r="E11" s="181"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="181"/>
-      <c r="H11" s="181"/>
-    </row>
-    <row r="12" spans="1:8" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="178" t="s">
+    <row r="11" spans="1:8">
+      <c r="A11" s="179"/>
+      <c r="B11" s="179"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="179"/>
+      <c r="E11" s="179"/>
+      <c r="F11" s="179"/>
+      <c r="G11" s="179"/>
+      <c r="H11" s="179"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.45">
+      <c r="A12" s="176" t="s">
         <v>346</v>
       </c>
-      <c r="B12" s="179"/>
-      <c r="C12" s="179"/>
-      <c r="D12" s="179"/>
-      <c r="E12" s="179"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="179"/>
-      <c r="H12" s="180"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B12" s="177"/>
+      <c r="C12" s="177"/>
+      <c r="D12" s="177"/>
+      <c r="E12" s="177"/>
+      <c r="F12" s="177"/>
+      <c r="G12" s="177"/>
+      <c r="H12" s="178"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="14" t="s">
         <v>347</v>
       </c>
@@ -21639,25 +21639,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F7F5A8-702B-4F09-8932-57A6A0E2716C}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="49" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="49" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="3.453125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.54296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.81640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" style="23" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="23" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="23" customWidth="1"/>
     <col min="6" max="6" width="9" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" style="23" customWidth="1"/>
-    <col min="11" max="11" width="9.81640625" style="23" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="23" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="23" customWidth="1"/>
     <col min="12" max="12" width="9" style="15" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="15" customWidth="1"/>
     <col min="14" max="14" width="15" style="15" customWidth="1"/>
     <col min="15" max="16384" width="49" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="29" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="29" customFormat="1" ht="29.1">
       <c r="A1" s="26" t="s">
         <v>349</v>
       </c>
@@ -21701,7 +21701,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="29.1">
       <c r="A2" s="25">
         <v>1</v>
       </c>
@@ -21729,7 +21729,7 @@
       </c>
       <c r="K2" s="25">
         <f ca="1">IF(H2&lt;&gt;"","",IF(G2="","",G2-TODAY()))</f>
-        <v>-46</v>
+        <v>-43</v>
       </c>
       <c r="L2" s="18" t="str">
         <f ca="1">IF(I2&lt;&gt;"","Completed",IF(G2&lt;TODAY(),"Delayed",IF(G2-TODAY()&lt;=7,"At Risk","On Track")))</f>
@@ -21738,7 +21738,7 @@
       <c r="M2" s="16"/>
       <c r="N2" s="16"/>
     </row>
-    <row r="3" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="29.1">
       <c r="A3" s="25">
         <v>2</v>
       </c>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="K3" s="25">
         <f t="shared" ref="K3:K7" ca="1" si="1">IF(H3&lt;&gt;"","",IF(G3="","",G3-TODAY()))</f>
-        <v>-44</v>
+        <v>-41</v>
       </c>
       <c r="L3" s="18" t="str">
         <f t="shared" ref="L3:L7" ca="1" si="2">IF(I3&lt;&gt;"","Completed",IF(G3&lt;TODAY(),"Delayed",IF(G3-TODAY()&lt;=7,"At Risk","On Track")))</f>
@@ -21778,7 +21778,7 @@
       <c r="M3" s="16"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="29.1">
       <c r="A4" s="25">
         <v>3</v>
       </c>
@@ -21808,7 +21808,7 @@
       </c>
       <c r="K4" s="25">
         <f t="shared" ca="1" si="1"/>
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="L4" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21817,7 +21817,7 @@
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
     </row>
-    <row r="5" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="29.1">
       <c r="A5" s="25">
         <v>4</v>
       </c>
@@ -21852,7 +21852,7 @@
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="29.1">
       <c r="A6" s="25">
         <v>5</v>
       </c>
@@ -21887,7 +21887,7 @@
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="29.1">
       <c r="A7" s="25">
         <v>6</v>
       </c>
@@ -21922,7 +21922,7 @@
       <c r="M7" s="16"/>
       <c r="N7" s="16"/>
     </row>
-    <row r="9" spans="1:14" ht="21" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:14" ht="21">
       <c r="B9" s="19" t="s">
         <v>374</v>
       </c>
@@ -21931,37 +21931,37 @@
       </c>
       <c r="D9" s="27"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14">
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="28"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14">
       <c r="B11" s="21"/>
       <c r="C11" s="20"/>
       <c r="D11" s="28"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14">
       <c r="B12" s="21"/>
       <c r="C12" s="20"/>
       <c r="D12" s="28"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14">
       <c r="B13" s="21"/>
       <c r="C13" s="20"/>
       <c r="D13" s="28"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14">
       <c r="B14" s="21"/>
       <c r="C14" s="20"/>
       <c r="D14" s="28"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14">
       <c r="B15" s="21"/>
       <c r="C15" s="20"/>
       <c r="D15" s="28"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14">
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
       <c r="D16" s="28"/>
@@ -22209,6 +22209,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="edc11825-568b-413a-84d5-4a9f1ca45e23" xsi:nil="true"/>
@@ -22223,49 +22232,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16C960B7-FFC1-4DD5-9675-AA2B14844178}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5257c0a4-1430-449d-83fe-5487a44f74a9"/>
-    <ds:schemaRef ds:uri="edc11825-568b-413a-84d5-4a9f1ca45e23"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16C960B7-FFC1-4DD5-9675-AA2B14844178}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E33095DF-5488-4606-9391-81B68F99522C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="edc11825-568b-413a-84d5-4a9f1ca45e23"/>
-    <ds:schemaRef ds:uri="5257c0a4-1430-449d-83fe-5487a44f74a9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FDABFEE-ABC0-4726-8B0A-8CC6F28E08C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FDABFEE-ABC0-4726-8B0A-8CC6F28E08C9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E33095DF-5488-4606-9391-81B68F99522C}"/>
 </file>
--- a/excel files/Part_Qualification_FF_Tracker_2026.xlsx
+++ b/excel files/Part_Qualification_FF_Tracker_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nutreco1.sharepoint.com/sites/ProductDesign/Shared Documents/Product Engineering/PE_Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70FBDE81-E981-4D6F-A42E-7D28A214AADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35D687F2-FFD6-463A-B4AC-2A8C5657B33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-2760" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,8 +22,8 @@
     <sheet name="Timeline" sheetId="3" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FF_2026_Ref_Backup!$A$2:$BC$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">FF_2026!$A$2:$BE$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FF_2026_Ref_Backup!$A$2:$BC$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="378">
   <si>
     <t>Fish Feeder 2026 Readiness Tracker</t>
   </si>
@@ -769,6 +769,9 @@
     <t>Scope</t>
   </si>
   <si>
+    <t>Draw. Rev. No</t>
+  </si>
+  <si>
     <t>Shortlisted Supplier Name</t>
   </si>
   <si>
@@ -778,7 +781,7 @@
     <t>Eruvaka</t>
   </si>
   <si>
-    <t>r1</t>
+    <t>rB</t>
   </si>
   <si>
     <t>ERLPM04</t>
@@ -895,7 +898,7 @@
     <t>PG11 (Gland + Lock nut+O ring)</t>
   </si>
   <si>
-    <t>r0</t>
+    <t>rA</t>
   </si>
   <si>
     <t>G Industries</t>
@@ -1040,10 +1043,47 @@
     <t>M4x16 CSK Philips head screw</t>
   </si>
   <si>
-    <t>EXOUSIA AUTOMOTIVE PRIVATE LIMITED</t>
+    <t>Exousia Automotive Private Limited</t>
   </si>
   <si>
     <t>Trails completed, samples ready and dispatch before 05th Oct</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Visit Plan:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> 21–23 Sep;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Tool Dev. Reports: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Ravindra Namburi to provide.</t>
+    </r>
   </si>
   <si>
     <t>Pacific Bearings Pvt Ltd</t>
@@ -1490,7 +1530,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1779,6 +1819,17 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="20">
@@ -2512,7 +2563,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2786,7 +2837,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2802,6 +2856,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3043,7 +3100,12 @@
     <cellStyle name="Accent6" xfId="6" builtinId="49"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3430,7 +3492,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0.87735849056603776</c:v>
+                  <c:v>0.85849056603773588</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.17924528301886791</c:v>
@@ -3904,10 +3966,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.91509433962264153</c:v>
+                  <c:v>0.86792452830188682</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.73529411764705888</c:v>
+                  <c:v>0.58823529411764708</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4304,10 +4366,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.98780487804878048</c:v>
+                  <c:v>0.95121951219512191</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.95652173913043481</c:v>
+                  <c:v>0.82608695652173914</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -4704,10 +4766,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.66666666666666663</c:v>
+                  <c:v>0.58333333333333337</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.27272727272727271</c:v>
+                  <c:v>9.0909090909090912E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -8459,16 +8521,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="48" customHeight="1">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="182" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="180"/>
+      <c r="B1" s="182"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="181"/>
+      <c r="B2" s="183"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="61" t="s">
@@ -8544,286 +8606,286 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="48" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="123"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="125"/>
     </row>
     <row r="2" spans="1:18" ht="14.45">
-      <c r="A2" s="124" t="str">
+      <c r="A2" s="126" t="str">
         <f ca="1">"Live view from FF_2026 • Updated "&amp;TEXT(NOW(),"dd-mmm-yyyy hh:mm")</f>
-        <v>Live view from FF_2026 • Updated 25-Sep-2026 15:14</v>
-      </c>
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-      <c r="O2" s="125"/>
-      <c r="P2" s="125"/>
-      <c r="Q2" s="125"/>
-      <c r="R2" s="126"/>
+        <v>Live view from FF_2026 • Updated 06-Oct-2026 17:35</v>
+      </c>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="127"/>
+      <c r="J2" s="127"/>
+      <c r="K2" s="127"/>
+      <c r="L2" s="127"/>
+      <c r="M2" s="127"/>
+      <c r="N2" s="127"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="127"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="128"/>
     </row>
     <row r="3" spans="1:18" ht="14.45">
-      <c r="A3" s="130"/>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="131"/>
-      <c r="M3" s="131"/>
-      <c r="N3" s="131"/>
-      <c r="O3" s="131"/>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="131"/>
-      <c r="R3" s="132"/>
+      <c r="A3" s="132"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="133"/>
+      <c r="Q3" s="133"/>
+      <c r="R3" s="134"/>
     </row>
     <row r="4" spans="1:18" ht="14.45">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="129" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="128"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128" t="s">
+      <c r="B4" s="130"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="120" t="s">
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="122" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120" t="s">
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
-      <c r="M4" s="128" t="s">
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128" t="s">
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="129"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="131"/>
     </row>
     <row r="5" spans="1:18" ht="32.25" customHeight="1">
-      <c r="A5" s="153">
+      <c r="A5" s="155">
         <f>SUM(B14:B24)/SUM(C14:C24)</f>
-        <v>0.20283018867924529</v>
-      </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="154">
+        <v>0.19968553459119498</v>
+      </c>
+      <c r="B5" s="149"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="156">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="146">
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="148">
         <f>COUNTIF(FF_2026!H3:H1145,"Mech")</f>
         <v>82</v>
       </c>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="146">
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="148">
         <f>COUNTIF(FF_2026!H3:H1145,"HW")</f>
         <v>24</v>
       </c>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="155">
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="157">
         <f>COUNTIFS(FF_2026!$A$3:$A$176,"&lt;&gt;",FF_2026!$P$3:$P$176,"&gt;0")+COUNTIFS(FF_2026!$A$3:$A$176,"&lt;&gt;",FF_2026!$S$3:$S$176,"&gt;0")-COUNTIFS(FF_2026!$A$3:$A$176,"&lt;&gt;",FF_2026!$P$3:$P$176,"&gt;0",FF_2026!$S$3:$S$176,"&gt;0")</f>
         <v>4</v>
       </c>
-      <c r="N5" s="147"/>
-      <c r="O5" s="147"/>
-      <c r="P5" s="156">
+      <c r="N5" s="149"/>
+      <c r="O5" s="149"/>
+      <c r="P5" s="158">
         <f>IFERROR(MIN(FF_2026!$V$3:$V$176),"")</f>
         <v>46280</v>
       </c>
-      <c r="Q5" s="147"/>
-      <c r="R5" s="157"/>
+      <c r="Q5" s="149"/>
+      <c r="R5" s="159"/>
     </row>
     <row r="6" spans="1:18" ht="32.25" customHeight="1">
-      <c r="A6" s="148"/>
-      <c r="B6" s="149"/>
-      <c r="C6" s="149"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="149"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="149"/>
-      <c r="L6" s="149"/>
-      <c r="M6" s="148"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="149"/>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="149"/>
-      <c r="R6" s="158"/>
+      <c r="A6" s="150"/>
+      <c r="B6" s="151"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="150"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="151"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="151"/>
+      <c r="M6" s="150"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="150"/>
+      <c r="Q6" s="151"/>
+      <c r="R6" s="160"/>
     </row>
     <row r="7" spans="1:18" ht="14.45">
-      <c r="A7" s="136"/>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="137"/>
-      <c r="H7" s="137"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="137"/>
-      <c r="K7" s="137"/>
-      <c r="L7" s="137"/>
-      <c r="M7" s="137"/>
-      <c r="N7" s="137"/>
-      <c r="O7" s="137"/>
-      <c r="P7" s="137"/>
-      <c r="Q7" s="137"/>
-      <c r="R7" s="138"/>
+      <c r="A7" s="138"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
+      <c r="M7" s="139"/>
+      <c r="N7" s="139"/>
+      <c r="O7" s="139"/>
+      <c r="P7" s="139"/>
+      <c r="Q7" s="139"/>
+      <c r="R7" s="140"/>
     </row>
     <row r="8" spans="1:18" ht="14.45">
-      <c r="A8" s="150" t="s">
+      <c r="A8" s="152" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="151"/>
-      <c r="C8" s="151"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="151"/>
-      <c r="G8" s="151"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="151"/>
-      <c r="J8" s="151"/>
-      <c r="K8" s="151"/>
-      <c r="L8" s="151"/>
-      <c r="M8" s="151"/>
-      <c r="N8" s="151"/>
-      <c r="O8" s="151"/>
-      <c r="P8" s="151"/>
-      <c r="Q8" s="151"/>
-      <c r="R8" s="152"/>
+      <c r="B8" s="153"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
+      <c r="I8" s="153"/>
+      <c r="J8" s="153"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="153"/>
+      <c r="M8" s="153"/>
+      <c r="N8" s="153"/>
+      <c r="O8" s="153"/>
+      <c r="P8" s="153"/>
+      <c r="Q8" s="153"/>
+      <c r="R8" s="154"/>
     </row>
     <row r="9" spans="1:18" ht="27.75" customHeight="1">
-      <c r="A9" s="159" t="str">
+      <c r="A9" s="161" t="str">
         <f>"Overall gate progress is "&amp;TEXT(A5,"0%")&amp;" across "&amp;TEXT(D5,"0")&amp;" tracked parts. Design and part qualification are complete; sourcing is at "&amp;TEXT(D18,"0%")&amp;". Supplier qualification, sample procurement and factory handover remain at 0%, making downstream execution the critical path. "&amp;TEXT(M5,"0")&amp;" parts currently show a positive design or qualification delay."</f>
         <v>Overall gate progress is 20% across 106 tracked parts. Design and part qualification are complete; sourcing is at 16%. Supplier qualification, sample procurement and factory handover remain at 0%, making downstream execution the critical path. 4 parts currently show a positive design or qualification delay.</v>
       </c>
-      <c r="B9" s="160"/>
-      <c r="C9" s="160"/>
-      <c r="D9" s="160"/>
-      <c r="E9" s="160"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="160"/>
-      <c r="I9" s="160"/>
-      <c r="J9" s="160"/>
-      <c r="K9" s="160"/>
-      <c r="L9" s="160"/>
-      <c r="M9" s="160"/>
-      <c r="N9" s="160"/>
-      <c r="O9" s="160"/>
-      <c r="P9" s="160"/>
-      <c r="Q9" s="160"/>
-      <c r="R9" s="161"/>
+      <c r="B9" s="162"/>
+      <c r="C9" s="162"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="162"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="162"/>
+      <c r="K9" s="162"/>
+      <c r="L9" s="162"/>
+      <c r="M9" s="162"/>
+      <c r="N9" s="162"/>
+      <c r="O9" s="162"/>
+      <c r="P9" s="162"/>
+      <c r="Q9" s="162"/>
+      <c r="R9" s="163"/>
     </row>
     <row r="10" spans="1:18" ht="27.75" customHeight="1">
-      <c r="A10" s="159"/>
-      <c r="B10" s="160"/>
-      <c r="C10" s="160"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="160"/>
-      <c r="G10" s="160"/>
-      <c r="H10" s="160"/>
-      <c r="I10" s="160"/>
-      <c r="J10" s="160"/>
-      <c r="K10" s="160"/>
-      <c r="L10" s="160"/>
-      <c r="M10" s="160"/>
-      <c r="N10" s="160"/>
-      <c r="O10" s="160"/>
-      <c r="P10" s="160"/>
-      <c r="Q10" s="160"/>
-      <c r="R10" s="161"/>
+      <c r="A10" s="161"/>
+      <c r="B10" s="162"/>
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="162"/>
+      <c r="K10" s="162"/>
+      <c r="L10" s="162"/>
+      <c r="M10" s="162"/>
+      <c r="N10" s="162"/>
+      <c r="O10" s="162"/>
+      <c r="P10" s="162"/>
+      <c r="Q10" s="162"/>
+      <c r="R10" s="163"/>
     </row>
     <row r="11" spans="1:18" ht="14.45">
-      <c r="A11" s="133"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="134"/>
-      <c r="D11" s="134"/>
-      <c r="E11" s="134"/>
-      <c r="F11" s="134"/>
-      <c r="G11" s="134"/>
-      <c r="H11" s="134"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
-      <c r="N11" s="134"/>
-      <c r="O11" s="134"/>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="135"/>
+      <c r="A11" s="135"/>
+      <c r="B11" s="136"/>
+      <c r="C11" s="136"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="136"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="136"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
+      <c r="N11" s="136"/>
+      <c r="O11" s="136"/>
+      <c r="P11" s="136"/>
+      <c r="Q11" s="136"/>
+      <c r="R11" s="137"/>
     </row>
     <row r="12" spans="1:18" ht="14.45">
-      <c r="A12" s="150" t="s">
+      <c r="A12" s="152" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="151"/>
-      <c r="C12" s="151"/>
-      <c r="D12" s="151"/>
-      <c r="E12" s="151"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="151"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="151"/>
-      <c r="J12" s="151"/>
-      <c r="K12" s="151"/>
-      <c r="L12" s="151"/>
-      <c r="M12" s="151"/>
-      <c r="N12" s="151"/>
-      <c r="O12" s="151"/>
-      <c r="P12" s="151"/>
-      <c r="Q12" s="151"/>
-      <c r="R12" s="152"/>
+      <c r="B12" s="153"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="153"/>
+      <c r="O12" s="153"/>
+      <c r="P12" s="153"/>
+      <c r="Q12" s="153"/>
+      <c r="R12" s="154"/>
     </row>
     <row r="13" spans="1:18" ht="14.45">
       <c r="A13" s="93" t="s">
@@ -8838,366 +8900,366 @@
       <c r="D13" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="130"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="131"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="131"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="131"/>
-      <c r="R13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="133"/>
+      <c r="P13" s="133"/>
+      <c r="Q13" s="133"/>
+      <c r="R13" s="134"/>
     </row>
     <row r="14" spans="1:18" ht="14.45">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="141">
+      <c r="B14" s="143">
         <f>COUNT(FF_2026!$M$3:$M$176)</f>
-        <v>93</v>
-      </c>
-      <c r="C14" s="141">
+        <v>91</v>
+      </c>
+      <c r="C14" s="143">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D14" s="165">
+      <c r="D14" s="167">
         <f>IFERROR(B14/C14,0)</f>
-        <v>0.87735849056603776</v>
-      </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="134"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
-      <c r="N14" s="134"/>
-      <c r="O14" s="134"/>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="135"/>
+        <v>0.85849056603773588</v>
+      </c>
+      <c r="F14" s="135"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="136"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="136"/>
+      <c r="Q14" s="136"/>
+      <c r="R14" s="137"/>
     </row>
     <row r="15" spans="1:18" ht="14.45">
-      <c r="A15" s="140"/>
-      <c r="B15" s="142"/>
-      <c r="C15" s="142"/>
-      <c r="D15" s="166"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="134"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
-      <c r="L15" s="134"/>
-      <c r="M15" s="134"/>
-      <c r="N15" s="134"/>
-      <c r="O15" s="134"/>
-      <c r="P15" s="134"/>
-      <c r="Q15" s="134"/>
-      <c r="R15" s="135"/>
+      <c r="A15" s="142"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="168"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="136"/>
+      <c r="J15" s="136"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="136"/>
+      <c r="M15" s="136"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="136"/>
+      <c r="P15" s="136"/>
+      <c r="Q15" s="136"/>
+      <c r="R15" s="137"/>
     </row>
     <row r="16" spans="1:18" ht="14.45">
-      <c r="A16" s="167" t="s">
+      <c r="A16" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="168">
+      <c r="B16" s="170">
         <f>COUNT(FF_2026!$R$3:$R$176)</f>
         <v>19</v>
       </c>
-      <c r="C16" s="168">
+      <c r="C16" s="170">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D16" s="165">
+      <c r="D16" s="167">
         <f>IFERROR(B16/C16,0)</f>
         <v>0.17924528301886791</v>
       </c>
-      <c r="F16" s="133"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="134"/>
-      <c r="M16" s="134"/>
-      <c r="N16" s="134"/>
-      <c r="O16" s="134"/>
-      <c r="P16" s="134"/>
-      <c r="Q16" s="134"/>
-      <c r="R16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="136"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="136"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="136"/>
+      <c r="O16" s="136"/>
+      <c r="P16" s="136"/>
+      <c r="Q16" s="136"/>
+      <c r="R16" s="137"/>
     </row>
     <row r="17" spans="1:18" ht="14.45">
-      <c r="A17" s="140"/>
-      <c r="B17" s="142"/>
-      <c r="C17" s="142"/>
-      <c r="D17" s="166"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="134"/>
-      <c r="H17" s="134"/>
-      <c r="I17" s="134"/>
-      <c r="J17" s="134"/>
-      <c r="K17" s="134"/>
-      <c r="L17" s="134"/>
-      <c r="M17" s="134"/>
-      <c r="N17" s="134"/>
-      <c r="O17" s="134"/>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="135"/>
+      <c r="A17" s="142"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="168"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="136"/>
+      <c r="P17" s="136"/>
+      <c r="Q17" s="136"/>
+      <c r="R17" s="137"/>
     </row>
     <row r="18" spans="1:18" ht="14.45">
-      <c r="A18" s="167" t="s">
+      <c r="A18" s="169" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="168">
+      <c r="B18" s="170">
         <f>COUNT(FF_2026!$AD$3:$AD$176)</f>
         <v>17</v>
       </c>
-      <c r="C18" s="168">
+      <c r="C18" s="170">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D18" s="165">
+      <c r="D18" s="167">
         <f>IFERROR(B18/C18,0)</f>
         <v>0.16037735849056603</v>
       </c>
-      <c r="F18" s="133"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="134"/>
-      <c r="N18" s="134"/>
-      <c r="O18" s="134"/>
-      <c r="P18" s="134"/>
-      <c r="Q18" s="134"/>
-      <c r="R18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
+      <c r="H18" s="136"/>
+      <c r="I18" s="136"/>
+      <c r="J18" s="136"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="136"/>
+      <c r="N18" s="136"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="136"/>
+      <c r="R18" s="137"/>
     </row>
     <row r="19" spans="1:18" ht="14.45">
-      <c r="A19" s="140"/>
-      <c r="B19" s="142"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="166"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="134"/>
-      <c r="J19" s="134"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="134"/>
-      <c r="N19" s="134"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="134"/>
-      <c r="Q19" s="134"/>
-      <c r="R19" s="135"/>
+      <c r="A19" s="142"/>
+      <c r="B19" s="144"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="168"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="136"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="136"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="136"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="136"/>
+      <c r="R19" s="137"/>
     </row>
     <row r="20" spans="1:18" ht="14.45">
-      <c r="A20" s="167" t="s">
+      <c r="A20" s="169" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="168">
+      <c r="B20" s="170">
         <f>COUNT(FF_2026!$AO$3:$AO$176)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="168">
+      <c r="C20" s="170">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D20" s="165">
+      <c r="D20" s="167">
         <f>IFERROR(B20/C20,0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="134"/>
-      <c r="I20" s="134"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="134"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="134"/>
-      <c r="N20" s="134"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="136"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="136"/>
+      <c r="Q20" s="136"/>
+      <c r="R20" s="137"/>
     </row>
     <row r="21" spans="1:18" ht="14.45">
-      <c r="A21" s="140"/>
-      <c r="B21" s="142"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="166"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="134"/>
-      <c r="N21" s="134"/>
-      <c r="O21" s="134"/>
-      <c r="P21" s="134"/>
-      <c r="Q21" s="134"/>
-      <c r="R21" s="135"/>
+      <c r="A21" s="142"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="168"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="136"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="136"/>
+      <c r="N21" s="136"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="136"/>
+      <c r="Q21" s="136"/>
+      <c r="R21" s="137"/>
     </row>
     <row r="22" spans="1:18" ht="14.45">
-      <c r="A22" s="167" t="s">
+      <c r="A22" s="169" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="168">
+      <c r="B22" s="170">
         <f>COUNT(FF_2026!$AS$3:$AS$176)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="168">
+      <c r="C22" s="170">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D22" s="165">
+      <c r="D22" s="167">
         <f>IFERROR(B22/C22,0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="133"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="134"/>
-      <c r="N22" s="134"/>
-      <c r="O22" s="134"/>
-      <c r="P22" s="134"/>
-      <c r="Q22" s="134"/>
-      <c r="R22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="136"/>
+      <c r="O22" s="136"/>
+      <c r="P22" s="136"/>
+      <c r="Q22" s="136"/>
+      <c r="R22" s="137"/>
     </row>
     <row r="23" spans="1:18" ht="14.45">
-      <c r="A23" s="140"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="166"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="134"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="134"/>
-      <c r="L23" s="134"/>
-      <c r="M23" s="134"/>
-      <c r="N23" s="134"/>
-      <c r="O23" s="134"/>
-      <c r="P23" s="134"/>
-      <c r="Q23" s="134"/>
-      <c r="R23" s="135"/>
+      <c r="A23" s="142"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="168"/>
+      <c r="F23" s="135"/>
+      <c r="G23" s="136"/>
+      <c r="H23" s="136"/>
+      <c r="I23" s="136"/>
+      <c r="J23" s="136"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="136"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="136"/>
+      <c r="Q23" s="136"/>
+      <c r="R23" s="137"/>
     </row>
     <row r="24" spans="1:18" ht="14.45">
-      <c r="A24" s="167" t="s">
+      <c r="A24" s="169" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="168">
+      <c r="B24" s="170">
         <f>COUNT(FF_2026!$BC$3:$BC$176)</f>
         <v>0</v>
       </c>
-      <c r="C24" s="168">
+      <c r="C24" s="170">
         <f>COUNT(FF_2026!$A$3:$A$176)</f>
         <v>106</v>
       </c>
-      <c r="D24" s="165">
+      <c r="D24" s="167">
         <f>IFERROR(B24/C24,0)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="133"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="134"/>
-      <c r="I24" s="134"/>
-      <c r="J24" s="134"/>
-      <c r="K24" s="134"/>
-      <c r="L24" s="134"/>
-      <c r="M24" s="134"/>
-      <c r="N24" s="134"/>
-      <c r="O24" s="134"/>
-      <c r="P24" s="134"/>
-      <c r="Q24" s="134"/>
-      <c r="R24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136"/>
+      <c r="H24" s="136"/>
+      <c r="I24" s="136"/>
+      <c r="J24" s="136"/>
+      <c r="K24" s="136"/>
+      <c r="L24" s="136"/>
+      <c r="M24" s="136"/>
+      <c r="N24" s="136"/>
+      <c r="O24" s="136"/>
+      <c r="P24" s="136"/>
+      <c r="Q24" s="136"/>
+      <c r="R24" s="137"/>
     </row>
     <row r="25" spans="1:18" ht="14.45">
-      <c r="A25" s="169"/>
-      <c r="B25" s="170"/>
-      <c r="C25" s="170"/>
-      <c r="D25" s="171"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="134"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="134"/>
-      <c r="L25" s="134"/>
-      <c r="M25" s="134"/>
-      <c r="N25" s="134"/>
-      <c r="O25" s="134"/>
-      <c r="P25" s="134"/>
-      <c r="Q25" s="134"/>
-      <c r="R25" s="135"/>
+      <c r="A25" s="171"/>
+      <c r="B25" s="172"/>
+      <c r="C25" s="172"/>
+      <c r="D25" s="173"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="136"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="136"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+      <c r="N25" s="136"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="136"/>
+      <c r="Q25" s="136"/>
+      <c r="R25" s="137"/>
     </row>
     <row r="26" spans="1:18" ht="14.45">
       <c r="A26" s="66"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="134"/>
-      <c r="I26" s="134"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="134"/>
-      <c r="L26" s="134"/>
-      <c r="M26" s="134"/>
-      <c r="N26" s="134"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="134"/>
-      <c r="Q26" s="134"/>
-      <c r="R26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="136"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="136"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="136"/>
+      <c r="Q26" s="136"/>
+      <c r="R26" s="137"/>
     </row>
     <row r="27" spans="1:18" ht="14.45">
       <c r="A27" s="66"/>
-      <c r="F27" s="136"/>
-      <c r="G27" s="137"/>
-      <c r="H27" s="137"/>
-      <c r="I27" s="137"/>
-      <c r="J27" s="137"/>
-      <c r="K27" s="137"/>
-      <c r="L27" s="137"/>
-      <c r="M27" s="137"/>
-      <c r="N27" s="137"/>
-      <c r="O27" s="137"/>
-      <c r="P27" s="137"/>
-      <c r="Q27" s="137"/>
-      <c r="R27" s="138"/>
+      <c r="F27" s="138"/>
+      <c r="G27" s="139"/>
+      <c r="H27" s="139"/>
+      <c r="I27" s="139"/>
+      <c r="J27" s="139"/>
+      <c r="K27" s="139"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="139"/>
+      <c r="N27" s="139"/>
+      <c r="O27" s="139"/>
+      <c r="P27" s="139"/>
+      <c r="Q27" s="139"/>
+      <c r="R27" s="140"/>
     </row>
     <row r="28" spans="1:18" ht="14.45">
-      <c r="A28" s="162" t="s">
+      <c r="A28" s="164" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="163"/>
-      <c r="C28" s="163"/>
-      <c r="D28" s="164"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="131"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="131"/>
-      <c r="L28" s="131"/>
-      <c r="M28" s="131"/>
-      <c r="N28" s="131"/>
-      <c r="O28" s="131"/>
-      <c r="P28" s="131"/>
-      <c r="Q28" s="131"/>
-      <c r="R28" s="132"/>
+      <c r="B28" s="165"/>
+      <c r="C28" s="165"/>
+      <c r="D28" s="166"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="133"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="133"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
+      <c r="M28" s="133"/>
+      <c r="N28" s="133"/>
+      <c r="O28" s="133"/>
+      <c r="P28" s="133"/>
+      <c r="Q28" s="133"/>
+      <c r="R28" s="134"/>
     </row>
     <row r="29" spans="1:18" ht="14.45">
       <c r="A29" s="75" t="s">
@@ -9212,19 +9274,19 @@
       <c r="D29" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="133"/>
-      <c r="G29" s="134"/>
-      <c r="H29" s="134"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="134"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="134"/>
-      <c r="N29" s="134"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="134"/>
-      <c r="Q29" s="134"/>
-      <c r="R29" s="135"/>
+      <c r="F29" s="135"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="136"/>
+      <c r="I29" s="136"/>
+      <c r="J29" s="136"/>
+      <c r="K29" s="136"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="136"/>
+      <c r="N29" s="136"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="136"/>
+      <c r="Q29" s="136"/>
+      <c r="R29" s="137"/>
     </row>
     <row r="30" spans="1:18" ht="14.45">
       <c r="A30" s="76" t="s">
@@ -9232,7 +9294,7 @@
       </c>
       <c r="B30" s="70">
         <f>COUNTIFS(FF_2026!$A$3:$A$646,"&lt;&gt;",FF_2026!$N$3:$N$646,"&gt;=0.9")</f>
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C30" s="71">
         <f>$D$5</f>
@@ -9240,21 +9302,21 @@
       </c>
       <c r="D30" s="96">
         <f>IFERROR(B30/C30,0)</f>
-        <v>0.91509433962264153</v>
-      </c>
-      <c r="F30" s="133"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="134"/>
-      <c r="I30" s="134"/>
-      <c r="J30" s="134"/>
-      <c r="K30" s="134"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="134"/>
-      <c r="N30" s="134"/>
-      <c r="O30" s="134"/>
-      <c r="P30" s="134"/>
-      <c r="Q30" s="134"/>
-      <c r="R30" s="135"/>
+        <v>0.86792452830188682</v>
+      </c>
+      <c r="F30" s="135"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="136"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="136"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="136"/>
+      <c r="N30" s="136"/>
+      <c r="O30" s="136"/>
+      <c r="P30" s="136"/>
+      <c r="Q30" s="136"/>
+      <c r="R30" s="137"/>
     </row>
     <row r="31" spans="1:18" ht="14.45">
       <c r="A31" s="77" t="s">
@@ -9262,7 +9324,7 @@
       </c>
       <c r="B31" s="72">
         <f>COUNTIFS(FF_2026!$G$3:$G$646,"New - Critical",FF_2026!$N$3:$N$646,"&gt;=0.9")</f>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C31" s="72">
         <f>COUNTIF(FF_2026!$G$3:$G$645,"New - Critical")</f>
@@ -9270,21 +9332,21 @@
       </c>
       <c r="D31" s="94">
         <f>IFERROR(B31/C31,0)</f>
-        <v>0.73529411764705888</v>
-      </c>
-      <c r="F31" s="133"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="134"/>
-      <c r="J31" s="134"/>
-      <c r="K31" s="134"/>
-      <c r="L31" s="134"/>
-      <c r="M31" s="134"/>
-      <c r="N31" s="134"/>
-      <c r="O31" s="134"/>
-      <c r="P31" s="134"/>
-      <c r="Q31" s="134"/>
-      <c r="R31" s="135"/>
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="F31" s="135"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="136"/>
+      <c r="I31" s="136"/>
+      <c r="J31" s="136"/>
+      <c r="K31" s="136"/>
+      <c r="L31" s="136"/>
+      <c r="M31" s="136"/>
+      <c r="N31" s="136"/>
+      <c r="O31" s="136"/>
+      <c r="P31" s="136"/>
+      <c r="Q31" s="136"/>
+      <c r="R31" s="137"/>
     </row>
     <row r="32" spans="1:18" ht="14.45">
       <c r="A32" s="77" t="s">
@@ -9302,19 +9364,19 @@
         <f>IFERROR(B32/C32,0)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="133"/>
-      <c r="G32" s="134"/>
-      <c r="H32" s="134"/>
-      <c r="I32" s="134"/>
-      <c r="J32" s="134"/>
-      <c r="K32" s="134"/>
-      <c r="L32" s="134"/>
-      <c r="M32" s="134"/>
-      <c r="N32" s="134"/>
-      <c r="O32" s="134"/>
-      <c r="P32" s="134"/>
-      <c r="Q32" s="134"/>
-      <c r="R32" s="135"/>
+      <c r="F32" s="135"/>
+      <c r="G32" s="136"/>
+      <c r="H32" s="136"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="136"/>
+      <c r="K32" s="136"/>
+      <c r="L32" s="136"/>
+      <c r="M32" s="136"/>
+      <c r="N32" s="136"/>
+      <c r="O32" s="136"/>
+      <c r="P32" s="136"/>
+      <c r="Q32" s="136"/>
+      <c r="R32" s="137"/>
     </row>
     <row r="33" spans="1:18" ht="14.45">
       <c r="A33" s="77" t="s">
@@ -9332,19 +9394,19 @@
         <f t="shared" ref="D33" si="0">IFERROR(B33/C33,0)</f>
         <v>1</v>
       </c>
-      <c r="F33" s="133"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="134"/>
-      <c r="J33" s="134"/>
-      <c r="K33" s="134"/>
-      <c r="L33" s="134"/>
-      <c r="M33" s="134"/>
-      <c r="N33" s="134"/>
-      <c r="O33" s="134"/>
-      <c r="P33" s="134"/>
-      <c r="Q33" s="134"/>
-      <c r="R33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="136"/>
+      <c r="I33" s="136"/>
+      <c r="J33" s="136"/>
+      <c r="K33" s="136"/>
+      <c r="L33" s="136"/>
+      <c r="M33" s="136"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="136"/>
+      <c r="P33" s="136"/>
+      <c r="Q33" s="136"/>
+      <c r="R33" s="137"/>
     </row>
     <row r="34" spans="1:18" ht="14.45">
       <c r="A34" s="77" t="s">
@@ -9362,19 +9424,19 @@
         <f t="shared" ref="D34:D40" si="1">IFERROR(B34/C34,0)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="133"/>
-      <c r="G34" s="134"/>
-      <c r="H34" s="134"/>
-      <c r="I34" s="134"/>
-      <c r="J34" s="134"/>
-      <c r="K34" s="134"/>
-      <c r="L34" s="134"/>
-      <c r="M34" s="134"/>
-      <c r="N34" s="134"/>
-      <c r="O34" s="134"/>
-      <c r="P34" s="134"/>
-      <c r="Q34" s="134"/>
-      <c r="R34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="136"/>
+      <c r="H34" s="136"/>
+      <c r="I34" s="136"/>
+      <c r="J34" s="136"/>
+      <c r="K34" s="136"/>
+      <c r="L34" s="136"/>
+      <c r="M34" s="136"/>
+      <c r="N34" s="136"/>
+      <c r="O34" s="136"/>
+      <c r="P34" s="136"/>
+      <c r="Q34" s="136"/>
+      <c r="R34" s="137"/>
     </row>
     <row r="35" spans="1:18" ht="14.45">
       <c r="A35" s="77" t="s">
@@ -9392,19 +9454,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F35" s="133"/>
-      <c r="G35" s="134"/>
-      <c r="H35" s="134"/>
-      <c r="I35" s="134"/>
-      <c r="J35" s="134"/>
-      <c r="K35" s="134"/>
-      <c r="L35" s="134"/>
-      <c r="M35" s="134"/>
-      <c r="N35" s="134"/>
-      <c r="O35" s="134"/>
-      <c r="P35" s="134"/>
-      <c r="Q35" s="134"/>
-      <c r="R35" s="135"/>
+      <c r="F35" s="135"/>
+      <c r="G35" s="136"/>
+      <c r="H35" s="136"/>
+      <c r="I35" s="136"/>
+      <c r="J35" s="136"/>
+      <c r="K35" s="136"/>
+      <c r="L35" s="136"/>
+      <c r="M35" s="136"/>
+      <c r="N35" s="136"/>
+      <c r="O35" s="136"/>
+      <c r="P35" s="136"/>
+      <c r="Q35" s="136"/>
+      <c r="R35" s="137"/>
     </row>
     <row r="36" spans="1:18" ht="14.45">
       <c r="A36" s="78" t="s">
@@ -9412,7 +9474,7 @@
       </c>
       <c r="B36" s="70">
         <f>COUNTIFS(FF_2026!$H$3:$H$646,"Mech",FF_2026!$N$3:$N$646,"&gt;=0.9")</f>
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C36" s="70">
         <f>COUNTIF(FF_2026!$H$3:$H$646,"Mech")</f>
@@ -9420,21 +9482,21 @@
       </c>
       <c r="D36" s="96">
         <f t="shared" si="1"/>
-        <v>0.98780487804878048</v>
-      </c>
-      <c r="F36" s="133"/>
-      <c r="G36" s="134"/>
-      <c r="H36" s="134"/>
-      <c r="I36" s="134"/>
-      <c r="J36" s="134"/>
-      <c r="K36" s="134"/>
-      <c r="L36" s="134"/>
-      <c r="M36" s="134"/>
-      <c r="N36" s="134"/>
-      <c r="O36" s="134"/>
-      <c r="P36" s="134"/>
-      <c r="Q36" s="134"/>
-      <c r="R36" s="135"/>
+        <v>0.95121951219512191</v>
+      </c>
+      <c r="F36" s="135"/>
+      <c r="G36" s="136"/>
+      <c r="H36" s="136"/>
+      <c r="I36" s="136"/>
+      <c r="J36" s="136"/>
+      <c r="K36" s="136"/>
+      <c r="L36" s="136"/>
+      <c r="M36" s="136"/>
+      <c r="N36" s="136"/>
+      <c r="O36" s="136"/>
+      <c r="P36" s="136"/>
+      <c r="Q36" s="136"/>
+      <c r="R36" s="137"/>
     </row>
     <row r="37" spans="1:18" ht="14.45">
       <c r="A37" s="79" t="s">
@@ -9442,7 +9504,7 @@
       </c>
       <c r="B37" s="74">
         <f>COUNTIFS(FF_2026!$G$3:$G$646,"New - Critical",FF_2026!$H$3:$H$646,"Mech",FF_2026!$N$3:$N$646,"&gt;=0.9")</f>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C37" s="74">
         <f>COUNTIFS(FF_2026!$G$3:$G$646,"New - Critical",FF_2026!$H$3:$H$646,"Mech")</f>
@@ -9450,21 +9512,21 @@
       </c>
       <c r="D37" s="96">
         <f t="shared" si="1"/>
-        <v>0.95652173913043481</v>
-      </c>
-      <c r="F37" s="133"/>
-      <c r="G37" s="134"/>
-      <c r="H37" s="134"/>
-      <c r="I37" s="134"/>
-      <c r="J37" s="134"/>
-      <c r="K37" s="134"/>
-      <c r="L37" s="134"/>
-      <c r="M37" s="134"/>
-      <c r="N37" s="134"/>
-      <c r="O37" s="134"/>
-      <c r="P37" s="134"/>
-      <c r="Q37" s="134"/>
-      <c r="R37" s="135"/>
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="F37" s="135"/>
+      <c r="G37" s="136"/>
+      <c r="H37" s="136"/>
+      <c r="I37" s="136"/>
+      <c r="J37" s="136"/>
+      <c r="K37" s="136"/>
+      <c r="L37" s="136"/>
+      <c r="M37" s="136"/>
+      <c r="N37" s="136"/>
+      <c r="O37" s="136"/>
+      <c r="P37" s="136"/>
+      <c r="Q37" s="136"/>
+      <c r="R37" s="137"/>
     </row>
     <row r="38" spans="1:18" ht="14.45">
       <c r="A38" s="79" t="s">
@@ -9482,19 +9544,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F38" s="133"/>
-      <c r="G38" s="134"/>
-      <c r="H38" s="134"/>
-      <c r="I38" s="134"/>
-      <c r="J38" s="134"/>
-      <c r="K38" s="134"/>
-      <c r="L38" s="134"/>
-      <c r="M38" s="134"/>
-      <c r="N38" s="134"/>
-      <c r="O38" s="134"/>
-      <c r="P38" s="134"/>
-      <c r="Q38" s="134"/>
-      <c r="R38" s="135"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="136"/>
+      <c r="I38" s="136"/>
+      <c r="J38" s="136"/>
+      <c r="K38" s="136"/>
+      <c r="L38" s="136"/>
+      <c r="M38" s="136"/>
+      <c r="N38" s="136"/>
+      <c r="O38" s="136"/>
+      <c r="P38" s="136"/>
+      <c r="Q38" s="136"/>
+      <c r="R38" s="137"/>
     </row>
     <row r="39" spans="1:18" ht="14.45">
       <c r="A39" s="79" t="s">
@@ -9512,19 +9574,19 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F39" s="133"/>
-      <c r="G39" s="134"/>
-      <c r="H39" s="134"/>
-      <c r="I39" s="134"/>
-      <c r="J39" s="134"/>
-      <c r="K39" s="134"/>
-      <c r="L39" s="134"/>
-      <c r="M39" s="134"/>
-      <c r="N39" s="134"/>
-      <c r="O39" s="134"/>
-      <c r="P39" s="134"/>
-      <c r="Q39" s="134"/>
-      <c r="R39" s="135"/>
+      <c r="F39" s="135"/>
+      <c r="G39" s="136"/>
+      <c r="H39" s="136"/>
+      <c r="I39" s="136"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="136"/>
+      <c r="L39" s="136"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="136"/>
+      <c r="O39" s="136"/>
+      <c r="P39" s="136"/>
+      <c r="Q39" s="136"/>
+      <c r="R39" s="137"/>
     </row>
     <row r="40" spans="1:18" ht="14.45">
       <c r="A40" s="79" t="s">
@@ -9542,19 +9604,19 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F40" s="133"/>
-      <c r="G40" s="134"/>
-      <c r="H40" s="134"/>
-      <c r="I40" s="134"/>
-      <c r="J40" s="134"/>
-      <c r="K40" s="134"/>
-      <c r="L40" s="134"/>
-      <c r="M40" s="134"/>
-      <c r="N40" s="134"/>
-      <c r="O40" s="134"/>
-      <c r="P40" s="134"/>
-      <c r="Q40" s="134"/>
-      <c r="R40" s="135"/>
+      <c r="F40" s="135"/>
+      <c r="G40" s="136"/>
+      <c r="H40" s="136"/>
+      <c r="I40" s="136"/>
+      <c r="J40" s="136"/>
+      <c r="K40" s="136"/>
+      <c r="L40" s="136"/>
+      <c r="M40" s="136"/>
+      <c r="N40" s="136"/>
+      <c r="O40" s="136"/>
+      <c r="P40" s="136"/>
+      <c r="Q40" s="136"/>
+      <c r="R40" s="137"/>
     </row>
     <row r="41" spans="1:18" ht="14.45">
       <c r="A41" s="79" t="s">
@@ -9572,19 +9634,19 @@
         <f t="shared" ref="D41:D42" si="2">IFERROR(B41/C41,0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="133"/>
-      <c r="G41" s="134"/>
-      <c r="H41" s="134"/>
-      <c r="I41" s="134"/>
-      <c r="J41" s="134"/>
-      <c r="K41" s="134"/>
-      <c r="L41" s="134"/>
-      <c r="M41" s="134"/>
-      <c r="N41" s="134"/>
-      <c r="O41" s="134"/>
-      <c r="P41" s="134"/>
-      <c r="Q41" s="134"/>
-      <c r="R41" s="135"/>
+      <c r="F41" s="135"/>
+      <c r="G41" s="136"/>
+      <c r="H41" s="136"/>
+      <c r="I41" s="136"/>
+      <c r="J41" s="136"/>
+      <c r="K41" s="136"/>
+      <c r="L41" s="136"/>
+      <c r="M41" s="136"/>
+      <c r="N41" s="136"/>
+      <c r="O41" s="136"/>
+      <c r="P41" s="136"/>
+      <c r="Q41" s="136"/>
+      <c r="R41" s="137"/>
     </row>
     <row r="42" spans="1:18" ht="14.45">
       <c r="A42" s="78" t="s">
@@ -9592,7 +9654,7 @@
       </c>
       <c r="B42" s="70">
         <f>COUNTIFS(FF_2026!$H$3:$H$646,"HW",FF_2026!$N$3:$N$646,"&gt;=0.9")</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C42" s="70">
         <f>COUNTIF(FF_2026!$H$3:$H$646,"HW")</f>
@@ -9600,21 +9662,21 @@
       </c>
       <c r="D42" s="96">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="F42" s="133"/>
-      <c r="G42" s="134"/>
-      <c r="H42" s="134"/>
-      <c r="I42" s="134"/>
-      <c r="J42" s="134"/>
-      <c r="K42" s="134"/>
-      <c r="L42" s="134"/>
-      <c r="M42" s="134"/>
-      <c r="N42" s="134"/>
-      <c r="O42" s="134"/>
-      <c r="P42" s="134"/>
-      <c r="Q42" s="134"/>
-      <c r="R42" s="135"/>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F42" s="135"/>
+      <c r="G42" s="136"/>
+      <c r="H42" s="136"/>
+      <c r="I42" s="136"/>
+      <c r="J42" s="136"/>
+      <c r="K42" s="136"/>
+      <c r="L42" s="136"/>
+      <c r="M42" s="136"/>
+      <c r="N42" s="136"/>
+      <c r="O42" s="136"/>
+      <c r="P42" s="136"/>
+      <c r="Q42" s="136"/>
+      <c r="R42" s="137"/>
     </row>
     <row r="43" spans="1:18" ht="14.45">
       <c r="A43" s="79" t="s">
@@ -9622,7 +9684,7 @@
       </c>
       <c r="B43" s="74">
         <f>COUNTIFS(FF_2026!$G$3:$G$646,"New - Critical",FF_2026!$H$3:$H$646,"HW",FF_2026!$N$3:$N$646,"&gt;=0.9")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" s="74">
         <f>COUNTIFS(FF_2026!$G$3:$G$646,"New - Critical",FF_2026!$H$3:$H$646,"HW")</f>
@@ -9630,21 +9692,21 @@
       </c>
       <c r="D43" s="96">
         <f>IFERROR(B43/C43,0)</f>
-        <v>0.27272727272727271</v>
-      </c>
-      <c r="F43" s="133"/>
-      <c r="G43" s="134"/>
-      <c r="H43" s="134"/>
-      <c r="I43" s="134"/>
-      <c r="J43" s="134"/>
-      <c r="K43" s="134"/>
-      <c r="L43" s="134"/>
-      <c r="M43" s="134"/>
-      <c r="N43" s="134"/>
-      <c r="O43" s="134"/>
-      <c r="P43" s="134"/>
-      <c r="Q43" s="134"/>
-      <c r="R43" s="135"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="F43" s="135"/>
+      <c r="G43" s="136"/>
+      <c r="H43" s="136"/>
+      <c r="I43" s="136"/>
+      <c r="J43" s="136"/>
+      <c r="K43" s="136"/>
+      <c r="L43" s="136"/>
+      <c r="M43" s="136"/>
+      <c r="N43" s="136"/>
+      <c r="O43" s="136"/>
+      <c r="P43" s="136"/>
+      <c r="Q43" s="136"/>
+      <c r="R43" s="137"/>
     </row>
     <row r="44" spans="1:18" ht="14.45">
       <c r="A44" s="79" t="s">
@@ -9662,19 +9724,19 @@
         <f t="shared" ref="D44" si="3">IFERROR(B44/C44,0)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="133"/>
-      <c r="G44" s="134"/>
-      <c r="H44" s="134"/>
-      <c r="I44" s="134"/>
-      <c r="J44" s="134"/>
-      <c r="K44" s="134"/>
-      <c r="L44" s="134"/>
-      <c r="M44" s="134"/>
-      <c r="N44" s="134"/>
-      <c r="O44" s="134"/>
-      <c r="P44" s="134"/>
-      <c r="Q44" s="134"/>
-      <c r="R44" s="135"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="136"/>
+      <c r="H44" s="136"/>
+      <c r="I44" s="136"/>
+      <c r="J44" s="136"/>
+      <c r="K44" s="136"/>
+      <c r="L44" s="136"/>
+      <c r="M44" s="136"/>
+      <c r="N44" s="136"/>
+      <c r="O44" s="136"/>
+      <c r="P44" s="136"/>
+      <c r="Q44" s="136"/>
+      <c r="R44" s="137"/>
     </row>
     <row r="45" spans="1:18" ht="14.45">
       <c r="A45" s="79" t="s">
@@ -9692,19 +9754,19 @@
         <f>IFERROR(B45/C45,0)</f>
         <v>1</v>
       </c>
-      <c r="F45" s="133"/>
-      <c r="G45" s="134"/>
-      <c r="H45" s="134"/>
-      <c r="I45" s="134"/>
-      <c r="J45" s="134"/>
-      <c r="K45" s="134"/>
-      <c r="L45" s="134"/>
-      <c r="M45" s="134"/>
-      <c r="N45" s="134"/>
-      <c r="O45" s="134"/>
-      <c r="P45" s="134"/>
-      <c r="Q45" s="134"/>
-      <c r="R45" s="135"/>
+      <c r="F45" s="135"/>
+      <c r="G45" s="136"/>
+      <c r="H45" s="136"/>
+      <c r="I45" s="136"/>
+      <c r="J45" s="136"/>
+      <c r="K45" s="136"/>
+      <c r="L45" s="136"/>
+      <c r="M45" s="136"/>
+      <c r="N45" s="136"/>
+      <c r="O45" s="136"/>
+      <c r="P45" s="136"/>
+      <c r="Q45" s="136"/>
+      <c r="R45" s="137"/>
     </row>
     <row r="46" spans="1:18" ht="14.45">
       <c r="A46" s="79" t="s">
@@ -9722,19 +9784,19 @@
         <f>IFERROR(B46/C46,0)</f>
         <v>1</v>
       </c>
-      <c r="F46" s="133"/>
-      <c r="G46" s="134"/>
-      <c r="H46" s="134"/>
-      <c r="I46" s="134"/>
-      <c r="J46" s="134"/>
-      <c r="K46" s="134"/>
-      <c r="L46" s="134"/>
-      <c r="M46" s="134"/>
-      <c r="N46" s="134"/>
-      <c r="O46" s="134"/>
-      <c r="P46" s="134"/>
-      <c r="Q46" s="134"/>
-      <c r="R46" s="135"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="136"/>
+      <c r="H46" s="136"/>
+      <c r="I46" s="136"/>
+      <c r="J46" s="136"/>
+      <c r="K46" s="136"/>
+      <c r="L46" s="136"/>
+      <c r="M46" s="136"/>
+      <c r="N46" s="136"/>
+      <c r="O46" s="136"/>
+      <c r="P46" s="136"/>
+      <c r="Q46" s="136"/>
+      <c r="R46" s="137"/>
     </row>
     <row r="47" spans="1:18" ht="14.45">
       <c r="A47" s="79" t="s">
@@ -9752,19 +9814,19 @@
         <f t="shared" ref="D47:D48" si="4">IFERROR(B47/C47,0)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="133"/>
-      <c r="G47" s="134"/>
-      <c r="H47" s="134"/>
-      <c r="I47" s="134"/>
-      <c r="J47" s="134"/>
-      <c r="K47" s="134"/>
-      <c r="L47" s="134"/>
-      <c r="M47" s="134"/>
-      <c r="N47" s="134"/>
-      <c r="O47" s="134"/>
-      <c r="P47" s="134"/>
-      <c r="Q47" s="134"/>
-      <c r="R47" s="135"/>
+      <c r="F47" s="135"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="136"/>
+      <c r="L47" s="136"/>
+      <c r="M47" s="136"/>
+      <c r="N47" s="136"/>
+      <c r="O47" s="136"/>
+      <c r="P47" s="136"/>
+      <c r="Q47" s="136"/>
+      <c r="R47" s="137"/>
     </row>
     <row r="48" spans="1:18" ht="14.45">
       <c r="A48" s="81" t="s">
@@ -9782,97 +9844,97 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F48" s="133"/>
-      <c r="G48" s="134"/>
-      <c r="H48" s="134"/>
-      <c r="I48" s="134"/>
-      <c r="J48" s="134"/>
-      <c r="K48" s="134"/>
-      <c r="L48" s="134"/>
-      <c r="M48" s="134"/>
-      <c r="N48" s="134"/>
-      <c r="O48" s="134"/>
-      <c r="P48" s="134"/>
-      <c r="Q48" s="134"/>
-      <c r="R48" s="135"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="136"/>
+      <c r="H48" s="136"/>
+      <c r="I48" s="136"/>
+      <c r="J48" s="136"/>
+      <c r="K48" s="136"/>
+      <c r="L48" s="136"/>
+      <c r="M48" s="136"/>
+      <c r="N48" s="136"/>
+      <c r="O48" s="136"/>
+      <c r="P48" s="136"/>
+      <c r="Q48" s="136"/>
+      <c r="R48" s="137"/>
     </row>
     <row r="49" spans="1:18" ht="14.45">
       <c r="A49" s="66"/>
-      <c r="F49" s="136"/>
-      <c r="G49" s="137"/>
-      <c r="H49" s="137"/>
-      <c r="I49" s="137"/>
-      <c r="J49" s="137"/>
-      <c r="K49" s="137"/>
-      <c r="L49" s="137"/>
-      <c r="M49" s="137"/>
-      <c r="N49" s="137"/>
-      <c r="O49" s="137"/>
-      <c r="P49" s="137"/>
-      <c r="Q49" s="137"/>
-      <c r="R49" s="138"/>
+      <c r="F49" s="138"/>
+      <c r="G49" s="139"/>
+      <c r="H49" s="139"/>
+      <c r="I49" s="139"/>
+      <c r="J49" s="139"/>
+      <c r="K49" s="139"/>
+      <c r="L49" s="139"/>
+      <c r="M49" s="139"/>
+      <c r="N49" s="139"/>
+      <c r="O49" s="139"/>
+      <c r="P49" s="139"/>
+      <c r="Q49" s="139"/>
+      <c r="R49" s="140"/>
     </row>
     <row r="50" spans="1:18" ht="14.45">
-      <c r="A50" s="133"/>
-      <c r="B50" s="134"/>
-      <c r="C50" s="134"/>
-      <c r="D50" s="134"/>
-      <c r="E50" s="134"/>
-      <c r="F50" s="134"/>
-      <c r="G50" s="134"/>
-      <c r="H50" s="134"/>
-      <c r="I50" s="134"/>
-      <c r="J50" s="134"/>
-      <c r="K50" s="134"/>
-      <c r="L50" s="134"/>
-      <c r="M50" s="134"/>
-      <c r="N50" s="134"/>
-      <c r="O50" s="134"/>
-      <c r="P50" s="134"/>
-      <c r="Q50" s="134"/>
-      <c r="R50" s="135"/>
+      <c r="A50" s="135"/>
+      <c r="B50" s="136"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="136"/>
+      <c r="E50" s="136"/>
+      <c r="F50" s="136"/>
+      <c r="G50" s="136"/>
+      <c r="H50" s="136"/>
+      <c r="I50" s="136"/>
+      <c r="J50" s="136"/>
+      <c r="K50" s="136"/>
+      <c r="L50" s="136"/>
+      <c r="M50" s="136"/>
+      <c r="N50" s="136"/>
+      <c r="O50" s="136"/>
+      <c r="P50" s="136"/>
+      <c r="Q50" s="136"/>
+      <c r="R50" s="137"/>
     </row>
     <row r="51" spans="1:18" ht="14.45">
-      <c r="A51" s="133"/>
-      <c r="B51" s="134"/>
-      <c r="C51" s="134"/>
-      <c r="D51" s="134"/>
-      <c r="E51" s="134"/>
-      <c r="F51" s="134"/>
-      <c r="G51" s="134"/>
-      <c r="H51" s="134"/>
-      <c r="I51" s="134"/>
-      <c r="J51" s="134"/>
-      <c r="K51" s="134"/>
-      <c r="L51" s="134"/>
-      <c r="M51" s="134"/>
-      <c r="N51" s="134"/>
-      <c r="O51" s="134"/>
-      <c r="P51" s="134"/>
-      <c r="Q51" s="134"/>
-      <c r="R51" s="135"/>
+      <c r="A51" s="135"/>
+      <c r="B51" s="136"/>
+      <c r="C51" s="136"/>
+      <c r="D51" s="136"/>
+      <c r="E51" s="136"/>
+      <c r="F51" s="136"/>
+      <c r="G51" s="136"/>
+      <c r="H51" s="136"/>
+      <c r="I51" s="136"/>
+      <c r="J51" s="136"/>
+      <c r="K51" s="136"/>
+      <c r="L51" s="136"/>
+      <c r="M51" s="136"/>
+      <c r="N51" s="136"/>
+      <c r="O51" s="136"/>
+      <c r="P51" s="136"/>
+      <c r="Q51" s="136"/>
+      <c r="R51" s="137"/>
     </row>
     <row r="52" spans="1:18" ht="14.45">
-      <c r="A52" s="150" t="s">
+      <c r="A52" s="152" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="151"/>
-      <c r="C52" s="151"/>
-      <c r="D52" s="151"/>
-      <c r="E52" s="151"/>
-      <c r="F52" s="151"/>
-      <c r="G52" s="151"/>
-      <c r="H52" s="151"/>
-      <c r="I52" s="151"/>
-      <c r="J52" s="151"/>
-      <c r="K52" s="151"/>
-      <c r="L52" s="151"/>
-      <c r="M52" s="151"/>
-      <c r="N52" s="151"/>
-      <c r="O52" s="151"/>
-      <c r="P52" s="151"/>
-      <c r="Q52" s="151"/>
-      <c r="R52" s="152"/>
+      <c r="B52" s="153"/>
+      <c r="C52" s="153"/>
+      <c r="D52" s="153"/>
+      <c r="E52" s="153"/>
+      <c r="F52" s="153"/>
+      <c r="G52" s="153"/>
+      <c r="H52" s="153"/>
+      <c r="I52" s="153"/>
+      <c r="J52" s="153"/>
+      <c r="K52" s="153"/>
+      <c r="L52" s="153"/>
+      <c r="M52" s="153"/>
+      <c r="N52" s="153"/>
+      <c r="O52" s="153"/>
+      <c r="P52" s="153"/>
+      <c r="Q52" s="153"/>
+      <c r="R52" s="154"/>
     </row>
     <row r="53" spans="1:18" ht="14.45">
       <c r="A53" s="83" t="s">
@@ -9887,97 +9949,97 @@
       <c r="A54" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="117" t="s">
+      <c r="B54" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="118"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="118"/>
-      <c r="G54" s="118"/>
-      <c r="H54" s="118"/>
-      <c r="I54" s="118"/>
-      <c r="J54" s="118"/>
-      <c r="K54" s="118"/>
-      <c r="L54" s="118"/>
-      <c r="M54" s="118"/>
-      <c r="N54" s="118"/>
-      <c r="O54" s="118"/>
-      <c r="P54" s="118"/>
-      <c r="Q54" s="118"/>
-      <c r="R54" s="119"/>
+      <c r="C54" s="120"/>
+      <c r="D54" s="120"/>
+      <c r="E54" s="120"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="120"/>
+      <c r="H54" s="120"/>
+      <c r="I54" s="120"/>
+      <c r="J54" s="120"/>
+      <c r="K54" s="120"/>
+      <c r="L54" s="120"/>
+      <c r="M54" s="120"/>
+      <c r="N54" s="120"/>
+      <c r="O54" s="120"/>
+      <c r="P54" s="120"/>
+      <c r="Q54" s="120"/>
+      <c r="R54" s="121"/>
     </row>
     <row r="55" spans="1:18" ht="32.25" customHeight="1">
       <c r="A55" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="117" t="s">
+      <c r="B55" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="C55" s="118"/>
-      <c r="D55" s="118"/>
-      <c r="E55" s="118"/>
-      <c r="F55" s="118"/>
-      <c r="G55" s="118"/>
-      <c r="H55" s="118"/>
-      <c r="I55" s="118"/>
-      <c r="J55" s="118"/>
-      <c r="K55" s="118"/>
-      <c r="L55" s="118"/>
-      <c r="M55" s="118"/>
-      <c r="N55" s="118"/>
-      <c r="O55" s="118"/>
-      <c r="P55" s="118"/>
-      <c r="Q55" s="118"/>
-      <c r="R55" s="119"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="120"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
+      <c r="H55" s="120"/>
+      <c r="I55" s="120"/>
+      <c r="J55" s="120"/>
+      <c r="K55" s="120"/>
+      <c r="L55" s="120"/>
+      <c r="M55" s="120"/>
+      <c r="N55" s="120"/>
+      <c r="O55" s="120"/>
+      <c r="P55" s="120"/>
+      <c r="Q55" s="120"/>
+      <c r="R55" s="121"/>
     </row>
     <row r="56" spans="1:18" ht="32.25" customHeight="1">
       <c r="A56" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="117" t="s">
+      <c r="B56" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="C56" s="118"/>
-      <c r="D56" s="118"/>
-      <c r="E56" s="118"/>
-      <c r="F56" s="118"/>
-      <c r="G56" s="118"/>
-      <c r="H56" s="118"/>
-      <c r="I56" s="118"/>
-      <c r="J56" s="118"/>
-      <c r="K56" s="118"/>
-      <c r="L56" s="118"/>
-      <c r="M56" s="118"/>
-      <c r="N56" s="118"/>
-      <c r="O56" s="118"/>
-      <c r="P56" s="118"/>
-      <c r="Q56" s="118"/>
-      <c r="R56" s="119"/>
+      <c r="C56" s="120"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="120"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="120"/>
+      <c r="H56" s="120"/>
+      <c r="I56" s="120"/>
+      <c r="J56" s="120"/>
+      <c r="K56" s="120"/>
+      <c r="L56" s="120"/>
+      <c r="M56" s="120"/>
+      <c r="N56" s="120"/>
+      <c r="O56" s="120"/>
+      <c r="P56" s="120"/>
+      <c r="Q56" s="120"/>
+      <c r="R56" s="121"/>
     </row>
     <row r="57" spans="1:18" ht="32.25" customHeight="1">
       <c r="A57" s="90" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="143" t="s">
+      <c r="B57" s="145" t="s">
         <v>55</v>
       </c>
-      <c r="C57" s="144"/>
-      <c r="D57" s="144"/>
-      <c r="E57" s="144"/>
-      <c r="F57" s="144"/>
-      <c r="G57" s="144"/>
-      <c r="H57" s="144"/>
-      <c r="I57" s="144"/>
-      <c r="J57" s="144"/>
-      <c r="K57" s="144"/>
-      <c r="L57" s="144"/>
-      <c r="M57" s="144"/>
-      <c r="N57" s="144"/>
-      <c r="O57" s="144"/>
-      <c r="P57" s="144"/>
-      <c r="Q57" s="144"/>
-      <c r="R57" s="145"/>
+      <c r="C57" s="146"/>
+      <c r="D57" s="146"/>
+      <c r="E57" s="146"/>
+      <c r="F57" s="146"/>
+      <c r="G57" s="146"/>
+      <c r="H57" s="146"/>
+      <c r="I57" s="146"/>
+      <c r="J57" s="146"/>
+      <c r="K57" s="146"/>
+      <c r="L57" s="146"/>
+      <c r="M57" s="146"/>
+      <c r="N57" s="146"/>
+      <c r="O57" s="146"/>
+      <c r="P57" s="146"/>
+      <c r="Q57" s="146"/>
+      <c r="R57" s="147"/>
     </row>
     <row r="58" spans="1:18" ht="15" customHeight="1"/>
   </sheetData>
@@ -10390,72 +10452,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" s="30" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="114" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="102" t="s">
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="103"/>
-      <c r="AA1" s="103"/>
-      <c r="AB1" s="103"/>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="103"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="103"/>
-      <c r="AH1" s="103"/>
-      <c r="AI1" s="103"/>
-      <c r="AJ1" s="104"/>
-      <c r="AK1" s="174" t="s">
+      <c r="X1" s="104"/>
+      <c r="Y1" s="104"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="104"/>
+      <c r="AB1" s="104"/>
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="104"/>
+      <c r="AF1" s="104"/>
+      <c r="AG1" s="104"/>
+      <c r="AH1" s="104"/>
+      <c r="AI1" s="104"/>
+      <c r="AJ1" s="106"/>
+      <c r="AK1" s="176" t="s">
         <v>30</v>
       </c>
-      <c r="AL1" s="174"/>
-      <c r="AM1" s="174"/>
-      <c r="AN1" s="174"/>
-      <c r="AO1" s="174"/>
-      <c r="AP1" s="175" t="s">
+      <c r="AL1" s="176"/>
+      <c r="AM1" s="176"/>
+      <c r="AN1" s="176"/>
+      <c r="AO1" s="176"/>
+      <c r="AP1" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="AQ1" s="175"/>
-      <c r="AR1" s="175"/>
-      <c r="AS1" s="175"/>
-      <c r="AT1" s="175"/>
-      <c r="AU1" s="172" t="s">
+      <c r="AQ1" s="177"/>
+      <c r="AR1" s="177"/>
+      <c r="AS1" s="177"/>
+      <c r="AT1" s="177"/>
+      <c r="AU1" s="174" t="s">
         <v>77</v>
       </c>
-      <c r="AV1" s="172"/>
-      <c r="AW1" s="172"/>
-      <c r="AX1" s="172"/>
-      <c r="AY1" s="172"/>
-      <c r="AZ1" s="172"/>
-      <c r="BA1" s="172"/>
-      <c r="BB1" s="173"/>
+      <c r="AV1" s="174"/>
+      <c r="AW1" s="174"/>
+      <c r="AX1" s="174"/>
+      <c r="AY1" s="174"/>
+      <c r="AZ1" s="174"/>
+      <c r="BA1" s="174"/>
+      <c r="BB1" s="175"/>
     </row>
     <row r="2" spans="1:54" s="1" customFormat="1" ht="50.25" customHeight="1">
       <c r="A2" s="52" t="s">
@@ -12626,39 +12688,39 @@
     <mergeCell ref="AP1:AT1"/>
   </mergeCells>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="21" priority="1" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="HW">
+    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="HW">
       <formula>NOT(ISERROR(SEARCH("HW",G1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Mech">
+    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="Mech">
       <formula>NOT(ISERROR(SEARCH("Mech",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1 O3:O1048576 R3:R1048576 AI3:AI1048576">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1 U2:U18 S2:T21 U20:U21 S22:U1048576">
-    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",P1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE1048576">
-    <cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",AE2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",AE2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",AE2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12682,7 +12744,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:BD179"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" outlineLevelCol="3"/>
   <cols>
@@ -12695,7 +12756,7 @@
     <col min="7" max="7" width="17" style="36" customWidth="1"/>
     <col min="8" max="8" width="8.28515625" style="36" customWidth="1"/>
     <col min="9" max="9" width="7.28515625" style="36" customWidth="1"/>
-    <col min="10" max="10" width="4.28515625" style="36" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" style="36" customWidth="1"/>
     <col min="11" max="11" width="4.140625" style="36" customWidth="1"/>
     <col min="12" max="12" width="9.42578125" style="35" customWidth="1"/>
     <col min="13" max="13" width="9.7109375" style="35" customWidth="1"/>
@@ -12715,7 +12776,7 @@
     <col min="28" max="28" width="12.28515625" style="35" customWidth="1" outlineLevel="2"/>
     <col min="29" max="29" width="11.140625" style="35" customWidth="1" outlineLevel="2"/>
     <col min="30" max="30" width="10.5703125" style="35" customWidth="1" outlineLevel="2"/>
-    <col min="31" max="31" width="33.7109375" style="35" customWidth="1" outlineLevel="2"/>
+    <col min="31" max="31" width="20.5703125" style="35" customWidth="1" outlineLevel="2"/>
     <col min="32" max="32" width="7.140625" style="36" customWidth="1" outlineLevel="2"/>
     <col min="33" max="33" width="9.42578125" style="35" customWidth="1" outlineLevel="2"/>
     <col min="34" max="34" width="9.5703125" style="36" customWidth="1" outlineLevel="2"/>
@@ -12726,7 +12787,7 @@
     <col min="40" max="40" width="10.7109375" style="35" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="8.28515625" style="35" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="12.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.28515625" style="2" customWidth="1"/>
+    <col min="43" max="43" width="22.7109375" style="2" customWidth="1"/>
     <col min="44" max="44" width="8" style="35" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="7.140625" style="35" bestFit="1" customWidth="1"/>
     <col min="46" max="46" width="5.140625" style="35" bestFit="1" customWidth="1"/>
@@ -12745,74 +12806,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" s="30" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="114" t="s">
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
-      <c r="V1" s="115"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="102" t="s">
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="103"/>
-      <c r="AA1" s="103"/>
-      <c r="AB1" s="103"/>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="103"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="103"/>
-      <c r="AH1" s="103"/>
-      <c r="AI1" s="103"/>
-      <c r="AJ1" s="103"/>
-      <c r="AK1" s="103"/>
-      <c r="AL1" s="104"/>
-      <c r="AM1" s="108" t="s">
+      <c r="Y1" s="104"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="104"/>
+      <c r="AB1" s="104"/>
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="105"/>
+      <c r="AF1" s="104"/>
+      <c r="AG1" s="104"/>
+      <c r="AH1" s="104"/>
+      <c r="AI1" s="104"/>
+      <c r="AJ1" s="104"/>
+      <c r="AK1" s="104"/>
+      <c r="AL1" s="106"/>
+      <c r="AM1" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="AN1" s="109"/>
-      <c r="AO1" s="109"/>
-      <c r="AP1" s="109"/>
-      <c r="AQ1" s="110"/>
-      <c r="AR1" s="111" t="s">
+      <c r="AN1" s="111"/>
+      <c r="AO1" s="111"/>
+      <c r="AP1" s="111"/>
+      <c r="AQ1" s="112"/>
+      <c r="AR1" s="113" t="s">
         <v>76</v>
       </c>
-      <c r="AS1" s="112"/>
-      <c r="AT1" s="112"/>
-      <c r="AU1" s="112"/>
-      <c r="AV1" s="113"/>
-      <c r="AW1" s="105" t="s">
+      <c r="AS1" s="114"/>
+      <c r="AT1" s="114"/>
+      <c r="AU1" s="114"/>
+      <c r="AV1" s="115"/>
+      <c r="AW1" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="AX1" s="106"/>
-      <c r="AY1" s="106"/>
-      <c r="AZ1" s="106"/>
-      <c r="BA1" s="106"/>
-      <c r="BB1" s="106"/>
-      <c r="BC1" s="106"/>
-      <c r="BD1" s="107"/>
+      <c r="AX1" s="108"/>
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="108"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="109"/>
     </row>
     <row r="2" spans="1:56" s="1" customFormat="1" ht="50.25" customHeight="1">
       <c r="A2" s="52" t="s">
@@ -12843,7 +12904,7 @@
         <v>85</v>
       </c>
       <c r="J2" s="51" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="K2" s="53" t="s">
         <v>87</v>
@@ -12906,7 +12967,7 @@
         <v>105</v>
       </c>
       <c r="AE2" s="32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AF2" s="31" t="s">
         <v>106</v>
@@ -12995,13 +13056,13 @@
         <v>127</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G3" s="68" t="s">
         <v>37</v>
@@ -13010,7 +13071,7 @@
         <v>130</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2">
@@ -13020,9 +13081,7 @@
         <v>46211</v>
       </c>
       <c r="M3" s="33"/>
-      <c r="N3" s="46">
-        <v>0.95</v>
-      </c>
+      <c r="N3" s="46"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="str">
         <f t="shared" ref="P3:P66" si="0">IF(OR(L3="",M3=""),"",SIGN(M3-L3)*(NETWORKDAYS(MIN(L3,M3),MAX(L3,M3))-1))</f>
@@ -13035,18 +13094,19 @@
         <v/>
       </c>
       <c r="T3" s="2" t="str">
-        <f t="shared" ref="T3:T66" si="2">IF(AND(N3&gt;=90%,N3&lt;=100%),"Yes","No")</f>
-        <v>Yes</v>
+        <f>IF(AND(N3&gt;=90%,N3&lt;=100%,M3&lt;&gt;""),"Yes","No")</f>
+        <v>No</v>
       </c>
       <c r="U3" s="33"/>
       <c r="V3" s="33"/>
       <c r="W3" s="58"/>
+      <c r="AE3" s="33"/>
       <c r="AF3" s="36">
         <v>10</v>
       </c>
       <c r="AH3" s="2"/>
       <c r="AK3" s="37" t="str">
-        <f t="shared" ref="AK3:AK67" si="3">IF(OR(AI3="",AJ3=""),"",SIGN(AJ3-AI3)*(NETWORKDAYS(MIN(AI3,AJ3),MAX(AI3,AJ3))-1))</f>
+        <f t="shared" ref="AK3:AK67" si="2">IF(OR(AI3="",AJ3=""),"",SIGN(AJ3-AI3)*(NETWORKDAYS(MIN(AI3,AJ3),MAX(AI3,AJ3))-1))</f>
         <v/>
       </c>
       <c r="AL3" s="58"/>
@@ -13059,16 +13119,16 @@
         <v>46210</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G4" s="68" t="s">
         <v>39</v>
@@ -13077,7 +13137,7 @@
         <v>130</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2">
@@ -13104,7 +13164,7 @@
         <v/>
       </c>
       <c r="T4" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="T4:T67" si="3">IF(AND(N4&gt;=90%,N4&lt;=100%,M4&lt;&gt;""),"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="U4" s="33"/>
@@ -13115,7 +13175,7 @@
       </c>
       <c r="AH4" s="2"/>
       <c r="AK4" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL4" s="58"/>
@@ -13128,16 +13188,16 @@
         <v>46210</v>
       </c>
       <c r="C5" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G5" s="68" t="s">
         <v>39</v>
@@ -13146,7 +13206,7 @@
         <v>130</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2">
@@ -13173,7 +13233,7 @@
         <v/>
       </c>
       <c r="T5" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U5" s="33"/>
@@ -13184,7 +13244,7 @@
       </c>
       <c r="AH5" s="2"/>
       <c r="AK5" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL5" s="58"/>
@@ -13197,16 +13257,16 @@
         <v>46210</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G6" s="68" t="s">
         <v>39</v>
@@ -13215,7 +13275,7 @@
         <v>130</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2">
@@ -13242,7 +13302,7 @@
         <v/>
       </c>
       <c r="T6" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U6" s="33"/>
@@ -13253,7 +13313,7 @@
       </c>
       <c r="AH6" s="2"/>
       <c r="AK6" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL6" s="58"/>
@@ -13266,16 +13326,16 @@
         <v>46210</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G7" s="68" t="s">
         <v>39</v>
@@ -13284,7 +13344,7 @@
         <v>130</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2">
@@ -13311,7 +13371,7 @@
         <v/>
       </c>
       <c r="T7" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U7" s="33"/>
@@ -13322,7 +13382,7 @@
       </c>
       <c r="AH7" s="2"/>
       <c r="AK7" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL7" s="58"/>
@@ -13335,16 +13395,16 @@
         <v>46210</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G8" s="68" t="s">
         <v>40</v>
@@ -13353,7 +13413,7 @@
         <v>130</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2">
@@ -13381,7 +13441,7 @@
         <v/>
       </c>
       <c r="T8" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U8" s="33"/>
@@ -13392,7 +13452,7 @@
       </c>
       <c r="AH8" s="2"/>
       <c r="AK8" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL8" s="58"/>
@@ -13405,16 +13465,16 @@
         <v>46210</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G9" s="68" t="s">
         <v>40</v>
@@ -13423,7 +13483,7 @@
         <v>130</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2">
@@ -13451,7 +13511,7 @@
         <v/>
       </c>
       <c r="T9" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U9" s="33"/>
@@ -13462,7 +13522,7 @@
       </c>
       <c r="AH9" s="2"/>
       <c r="AK9" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL9" s="58"/>
@@ -13475,16 +13535,16 @@
         <v>46210</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G10" s="68" t="s">
         <v>40</v>
@@ -13493,7 +13553,7 @@
         <v>130</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2">
@@ -13521,7 +13581,7 @@
         <v/>
       </c>
       <c r="T10" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U10" s="33"/>
@@ -13532,7 +13592,7 @@
       </c>
       <c r="AH10" s="2"/>
       <c r="AK10" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL10" s="58"/>
@@ -13545,16 +13605,16 @@
         <v>46210</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G11" s="68" t="s">
         <v>40</v>
@@ -13563,7 +13623,7 @@
         <v>130</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2">
@@ -13591,7 +13651,7 @@
         <v/>
       </c>
       <c r="T11" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U11" s="33"/>
@@ -13602,7 +13662,7 @@
       </c>
       <c r="AH11" s="2"/>
       <c r="AK11" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL11" s="58"/>
@@ -13615,16 +13675,16 @@
         <v>46210</v>
       </c>
       <c r="C12" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="25" t="s">
-        <v>188</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G12" s="68" t="s">
         <v>40</v>
@@ -13633,7 +13693,7 @@
         <v>130</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2">
@@ -13660,7 +13720,7 @@
         <v/>
       </c>
       <c r="T12" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U12" s="33"/>
@@ -13671,7 +13731,7 @@
       </c>
       <c r="AH12" s="2"/>
       <c r="AK12" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL12" s="58"/>
@@ -13684,16 +13744,16 @@
         <v>46210</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G13" s="68" t="s">
         <v>40</v>
@@ -13702,7 +13762,7 @@
         <v>130</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2">
@@ -13729,7 +13789,7 @@
         <v/>
       </c>
       <c r="T13" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U13" s="33"/>
@@ -13740,7 +13800,7 @@
       </c>
       <c r="AH13" s="2"/>
       <c r="AK13" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL13" s="58"/>
@@ -13753,16 +13813,16 @@
         <v>46210</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G14" s="68" t="s">
         <v>39</v>
@@ -13771,7 +13831,7 @@
         <v>130</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2">
@@ -13798,7 +13858,7 @@
         <v/>
       </c>
       <c r="T14" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U14" s="33"/>
@@ -13809,7 +13869,7 @@
       </c>
       <c r="AH14" s="2"/>
       <c r="AK14" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL14" s="58"/>
@@ -13822,16 +13882,16 @@
         <v>46210</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G15" s="68" t="s">
         <v>40</v>
@@ -13840,7 +13900,7 @@
         <v>130</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2">
@@ -13867,7 +13927,7 @@
         <v/>
       </c>
       <c r="T15" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U15" s="33"/>
@@ -13878,7 +13938,7 @@
       </c>
       <c r="AH15" s="2"/>
       <c r="AK15" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL15" s="58"/>
@@ -13891,16 +13951,16 @@
         <v>46210</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G16" s="68" t="s">
         <v>40</v>
@@ -13909,7 +13969,7 @@
         <v>130</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2">
@@ -13936,7 +13996,7 @@
         <v/>
       </c>
       <c r="T16" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U16" s="33"/>
@@ -13947,7 +14007,7 @@
       </c>
       <c r="AH16" s="2"/>
       <c r="AK16" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL16" s="58"/>
@@ -13960,16 +14020,16 @@
         <v>46210</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G17" s="68" t="s">
         <v>40</v>
@@ -13978,7 +14038,7 @@
         <v>130</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2">
@@ -14005,7 +14065,7 @@
         <v/>
       </c>
       <c r="T17" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U17" s="33"/>
@@ -14016,7 +14076,7 @@
       </c>
       <c r="AH17" s="2"/>
       <c r="AK17" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL17" s="58"/>
@@ -14029,16 +14089,16 @@
         <v>46210</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G18" s="68" t="s">
         <v>40</v>
@@ -14047,7 +14107,7 @@
         <v>130</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2">
@@ -14074,7 +14134,7 @@
         <v/>
       </c>
       <c r="T18" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U18" s="33"/>
@@ -14085,7 +14145,7 @@
       </c>
       <c r="AH18" s="2"/>
       <c r="AK18" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL18" s="58"/>
@@ -14098,16 +14158,16 @@
         <v>46210</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G19" s="68" t="s">
         <v>39</v>
@@ -14116,7 +14176,7 @@
         <v>130</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2">
@@ -14143,7 +14203,7 @@
         <v/>
       </c>
       <c r="T19" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U19" s="33"/>
@@ -14154,7 +14214,7 @@
       </c>
       <c r="AH19" s="2"/>
       <c r="AK19" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL19" s="58"/>
@@ -14167,16 +14227,16 @@
         <v>46210</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G20" s="68" t="s">
         <v>40</v>
@@ -14185,7 +14245,7 @@
         <v>130</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2">
@@ -14212,7 +14272,7 @@
         <v/>
       </c>
       <c r="T20" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U20" s="33"/>
@@ -14223,7 +14283,7 @@
       </c>
       <c r="AH20" s="2"/>
       <c r="AK20" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL20" s="58"/>
@@ -14236,16 +14296,16 @@
         <v>46210</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G21" s="68" t="s">
         <v>40</v>
@@ -14254,7 +14314,7 @@
         <v>130</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2">
@@ -14281,7 +14341,7 @@
         <v/>
       </c>
       <c r="T21" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U21" s="33"/>
@@ -14292,7 +14352,7 @@
       </c>
       <c r="AH21" s="2"/>
       <c r="AK21" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL21" s="58"/>
@@ -14305,16 +14365,16 @@
         <v>46210</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G22" s="68" t="s">
         <v>40</v>
@@ -14323,7 +14383,7 @@
         <v>130</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2">
@@ -14351,7 +14411,7 @@
         <v/>
       </c>
       <c r="T22" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U22" s="33"/>
@@ -14362,12 +14422,12 @@
       </c>
       <c r="AH22" s="2"/>
       <c r="AK22" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL22" s="58"/>
     </row>
-    <row r="23" spans="1:45" ht="30" hidden="1" customHeight="1">
+    <row r="23" spans="1:45" ht="30" customHeight="1">
       <c r="A23" s="40">
         <v>21</v>
       </c>
@@ -14384,7 +14444,7 @@
         <v>129</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G23" s="68" t="s">
         <v>37</v>
@@ -14393,7 +14453,7 @@
         <v>130</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J23" s="2">
         <v>0</v>
@@ -14428,7 +14488,7 @@
         <v>-11</v>
       </c>
       <c r="T23" s="2" t="str">
-        <f>IF(AND(N23&gt;=90%,N23&lt;=100%),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U23" s="33">
@@ -14463,7 +14523,7 @@
         <v>46262</v>
       </c>
       <c r="AE23" s="98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AF23" s="36">
         <v>10</v>
@@ -14496,16 +14556,16 @@
         <v>46210</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G24" s="68" t="s">
         <v>40</v>
@@ -14514,7 +14574,7 @@
         <v>130</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2">
@@ -14541,7 +14601,7 @@
         <v/>
       </c>
       <c r="T24" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U24" s="33"/>
@@ -14552,7 +14612,7 @@
       </c>
       <c r="AH24" s="2"/>
       <c r="AK24" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL24" s="58"/>
@@ -14565,16 +14625,16 @@
         <v>46210</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G25" s="68" t="s">
         <v>39</v>
@@ -14583,7 +14643,7 @@
         <v>130</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2">
@@ -14610,7 +14670,7 @@
         <v/>
       </c>
       <c r="T25" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U25" s="33"/>
@@ -14621,7 +14681,7 @@
       </c>
       <c r="AH25" s="2"/>
       <c r="AK25" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL25" s="58"/>
@@ -14634,16 +14694,16 @@
         <v>46210</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G26" s="68" t="s">
         <v>40</v>
@@ -14652,7 +14712,7 @@
         <v>130</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2">
@@ -14679,7 +14739,7 @@
         <v/>
       </c>
       <c r="T26" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U26" s="33"/>
@@ -14690,7 +14750,7 @@
       </c>
       <c r="AH26" s="2"/>
       <c r="AK26" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL26" s="58"/>
@@ -14703,16 +14763,16 @@
         <v>46210</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G27" s="68" t="s">
         <v>40</v>
@@ -14721,7 +14781,7 @@
         <v>130</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2">
@@ -14748,7 +14808,7 @@
         <v/>
       </c>
       <c r="T27" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U27" s="33"/>
@@ -14759,7 +14819,7 @@
       </c>
       <c r="AH27" s="2"/>
       <c r="AK27" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL27" s="58"/>
@@ -14772,16 +14832,16 @@
         <v>46210</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G28" s="68" t="s">
         <v>40</v>
@@ -14790,7 +14850,7 @@
         <v>130</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2">
@@ -14817,7 +14877,7 @@
         <v/>
       </c>
       <c r="T28" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U28" s="33"/>
@@ -14828,7 +14888,7 @@
       </c>
       <c r="AH28" s="2"/>
       <c r="AK28" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL28" s="58"/>
@@ -14841,16 +14901,16 @@
         <v>46210</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G29" s="68" t="s">
         <v>40</v>
@@ -14859,7 +14919,7 @@
         <v>130</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2">
@@ -14886,7 +14946,7 @@
         <v/>
       </c>
       <c r="T29" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U29" s="33"/>
@@ -14897,7 +14957,7 @@
       </c>
       <c r="AH29" s="2"/>
       <c r="AK29" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL29" s="58"/>
@@ -14910,16 +14970,16 @@
         <v>46210</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G30" s="68" t="s">
         <v>40</v>
@@ -14928,7 +14988,7 @@
         <v>130</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2">
@@ -14955,7 +15015,7 @@
         <v/>
       </c>
       <c r="T30" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U30" s="33"/>
@@ -14966,7 +15026,7 @@
       </c>
       <c r="AH30" s="2"/>
       <c r="AK30" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL30" s="58"/>
@@ -14979,16 +15039,16 @@
         <v>46210</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G31" s="68" t="s">
         <v>40</v>
@@ -14997,7 +15057,7 @@
         <v>130</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2">
@@ -15024,7 +15084,7 @@
         <v/>
       </c>
       <c r="T31" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U31" s="33"/>
@@ -15035,7 +15095,7 @@
       </c>
       <c r="AH31" s="2"/>
       <c r="AK31" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL31" s="58"/>
@@ -15048,16 +15108,16 @@
         <v>46210</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G32" s="68" t="s">
         <v>40</v>
@@ -15066,7 +15126,7 @@
         <v>130</v>
       </c>
       <c r="I32" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2">
@@ -15093,7 +15153,7 @@
         <v/>
       </c>
       <c r="T32" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U32" s="33"/>
@@ -15104,7 +15164,7 @@
       </c>
       <c r="AH32" s="2"/>
       <c r="AK32" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL32" s="58"/>
@@ -15117,16 +15177,16 @@
         <v>46210</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G33" s="68" t="s">
         <v>40</v>
@@ -15135,7 +15195,7 @@
         <v>130</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2">
@@ -15162,7 +15222,7 @@
         <v/>
       </c>
       <c r="T33" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U33" s="33"/>
@@ -15173,7 +15233,7 @@
       </c>
       <c r="AH33" s="2"/>
       <c r="AK33" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL33" s="58"/>
@@ -15186,16 +15246,16 @@
         <v>46210</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G34" s="68" t="s">
         <v>40</v>
@@ -15204,7 +15264,7 @@
         <v>130</v>
       </c>
       <c r="I34" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2">
@@ -15231,7 +15291,7 @@
         <v/>
       </c>
       <c r="T34" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U34" s="33"/>
@@ -15242,7 +15302,7 @@
       </c>
       <c r="AH34" s="2"/>
       <c r="AK34" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL34" s="58"/>
@@ -15255,16 +15315,16 @@
         <v>46210</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G35" s="68" t="s">
         <v>40</v>
@@ -15273,7 +15333,7 @@
         <v>130</v>
       </c>
       <c r="I35" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2">
@@ -15300,7 +15360,7 @@
         <v/>
       </c>
       <c r="T35" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U35" s="33"/>
@@ -15311,7 +15371,7 @@
       </c>
       <c r="AH35" s="2"/>
       <c r="AK35" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL35" s="58"/>
@@ -15324,16 +15384,16 @@
         <v>46210</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G36" s="68" t="s">
         <v>40</v>
@@ -15342,7 +15402,7 @@
         <v>43</v>
       </c>
       <c r="I36" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2">
@@ -15369,7 +15429,7 @@
         <v/>
       </c>
       <c r="T36" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U36" s="33"/>
@@ -15380,7 +15440,7 @@
       </c>
       <c r="AH36" s="2"/>
       <c r="AK36" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL36" s="58"/>
@@ -15393,16 +15453,16 @@
         <v>46210</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G37" s="68" t="s">
         <v>40</v>
@@ -15411,7 +15471,7 @@
         <v>130</v>
       </c>
       <c r="I37" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2">
@@ -15439,7 +15499,7 @@
         <v/>
       </c>
       <c r="T37" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U37" s="33"/>
@@ -15450,7 +15510,7 @@
       </c>
       <c r="AH37" s="2"/>
       <c r="AK37" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL37" s="58"/>
@@ -15463,16 +15523,16 @@
         <v>46210</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G38" s="68" t="s">
         <v>40</v>
@@ -15481,7 +15541,7 @@
         <v>130</v>
       </c>
       <c r="I38" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2">
@@ -15509,7 +15569,7 @@
         <v/>
       </c>
       <c r="T38" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U38" s="33"/>
@@ -15520,7 +15580,7 @@
       </c>
       <c r="AH38" s="2"/>
       <c r="AK38" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL38" s="58"/>
@@ -15533,16 +15593,16 @@
         <v>46210</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G39" s="68" t="s">
         <v>40</v>
@@ -15551,7 +15611,7 @@
         <v>130</v>
       </c>
       <c r="I39" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2">
@@ -15578,7 +15638,7 @@
         <v/>
       </c>
       <c r="T39" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U39" s="33"/>
@@ -15589,7 +15649,7 @@
       </c>
       <c r="AH39" s="2"/>
       <c r="AK39" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL39" s="58"/>
@@ -15602,16 +15662,16 @@
         <v>46210</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G40" s="68" t="s">
         <v>40</v>
@@ -15620,7 +15680,7 @@
         <v>130</v>
       </c>
       <c r="I40" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2">
@@ -15647,7 +15707,7 @@
         <v/>
       </c>
       <c r="T40" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U40" s="33"/>
@@ -15658,7 +15718,7 @@
       </c>
       <c r="AH40" s="2"/>
       <c r="AK40" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL40" s="58"/>
@@ -15671,16 +15731,16 @@
         <v>46210</v>
       </c>
       <c r="C41" s="25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G41" s="68" t="s">
         <v>40</v>
@@ -15689,7 +15749,7 @@
         <v>130</v>
       </c>
       <c r="I41" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2">
@@ -15716,7 +15776,7 @@
         <v/>
       </c>
       <c r="T41" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U41" s="33"/>
@@ -15727,12 +15787,12 @@
       </c>
       <c r="AH41" s="2"/>
       <c r="AK41" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL41" s="58"/>
     </row>
-    <row r="42" spans="1:38" ht="30" hidden="1" customHeight="1">
+    <row r="42" spans="1:38" ht="30" customHeight="1">
       <c r="A42" s="40">
         <v>40</v>
       </c>
@@ -15743,13 +15803,13 @@
         <v>127</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G42" s="68" t="s">
         <v>37</v>
@@ -15758,7 +15818,7 @@
         <v>130</v>
       </c>
       <c r="I42" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
@@ -15769,18 +15829,16 @@
       <c r="L42" s="33">
         <v>46211</v>
       </c>
-      <c r="M42" s="33">
-        <v>46211</v>
-      </c>
+      <c r="M42" s="33"/>
       <c r="N42" s="46">
         <v>0.95</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q42" s="33"/>
       <c r="R42" s="33"/>
@@ -15789,30 +15847,31 @@
         <v/>
       </c>
       <c r="T42" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Yes</v>
+        <f t="shared" si="3"/>
+        <v>No</v>
       </c>
       <c r="U42" s="33"/>
       <c r="V42" s="33"/>
       <c r="W42" s="58"/>
+      <c r="AE42" s="33"/>
       <c r="AF42" s="36">
         <v>10</v>
       </c>
       <c r="AH42" s="2"/>
       <c r="AK42" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL42" s="58"/>
     </row>
-    <row r="43" spans="1:38" ht="30" hidden="1" customHeight="1">
+    <row r="43" spans="1:38" ht="30" customHeight="1">
       <c r="A43" s="40">
         <v>41</v>
       </c>
       <c r="B43" s="33">
         <v>46210</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="25" t="s">
         <v>127</v>
       </c>
       <c r="D43" s="25" t="s">
@@ -15822,7 +15881,7 @@
         <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G43" s="68" t="s">
         <v>37</v>
@@ -15831,7 +15890,7 @@
         <v>130</v>
       </c>
       <c r="I43" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>136</v>
@@ -15852,7 +15911,7 @@
         <v>131</v>
       </c>
       <c r="P43" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="P43" si="4">IF(OR(L43="",M43=""),"",SIGN(M43-L43)*(NETWORKDAYS(MIN(L43,M43),MAX(L43,M43))-1))</f>
         <v>16</v>
       </c>
       <c r="Q43" s="33">
@@ -15862,11 +15921,11 @@
         <v>46233</v>
       </c>
       <c r="S43" s="34">
-        <f t="shared" si="1"/>
+        <f>IF(OR(Q43="",R43=""),"",SIGN(R43-Q43)*(NETWORKDAYS(MIN(Q43,R43),MAX(Q43,R43))-1))</f>
         <v>0</v>
       </c>
       <c r="T43" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="T43" si="5">IF(AND(N43&gt;=90%,N43&lt;=100%,M43&lt;&gt;""),"Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="U43" s="33">
@@ -15897,7 +15956,7 @@
         <v>46262</v>
       </c>
       <c r="AE43" s="98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AF43" s="36">
         <v>10</v>
@@ -15909,19 +15968,19 @@
         <v>133</v>
       </c>
       <c r="AI43" s="35">
-        <f t="shared" ref="AI43:AI46" si="4">IF(OR(AD43="",AH43=""),"",WORKDAY(AD43,IF(AH43="Low",30,IF(AH43="Medium",45,IF(AH43="High",60,"")))))</f>
+        <f t="shared" ref="AI43" si="6">IF(OR(AD43="",AH43=""),"",WORKDAY(AD43,IF(AH43="Low",30,IF(AH43="Medium",45,IF(AH43="High",60,"")))))</f>
         <v>46325</v>
       </c>
       <c r="AJ43" s="35">
         <v>46290</v>
       </c>
       <c r="AK43" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AK43" si="7">IF(OR(AI43="",AJ43=""),"",SIGN(AJ43-AI43)*(NETWORKDAYS(MIN(AI43,AJ43),MAX(AI43,AJ43))-1))</f>
         <v>-25</v>
       </c>
       <c r="AL43" s="58"/>
     </row>
-    <row r="44" spans="1:38" ht="30" hidden="1" customHeight="1">
+    <row r="44" spans="1:38" ht="30" customHeight="1">
       <c r="A44" s="40">
         <v>42</v>
       </c>
@@ -15938,7 +15997,7 @@
         <v>129</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G44" s="68" t="s">
         <v>37</v>
@@ -15947,7 +16006,7 @@
         <v>130</v>
       </c>
       <c r="I44" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J44" s="2">
         <v>0</v>
@@ -15982,7 +16041,7 @@
         <v>-11</v>
       </c>
       <c r="T44" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U44" s="33">
@@ -16013,7 +16072,7 @@
         <v>46262</v>
       </c>
       <c r="AE44" s="98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AF44" s="36">
         <v>10</v>
@@ -16025,19 +16084,19 @@
         <v>133</v>
       </c>
       <c r="AI44" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="AI44:AI46" si="8">IF(OR(AD44="",AH44=""),"",WORKDAY(AD44,IF(AH44="Low",30,IF(AH44="Medium",45,IF(AH44="High",60,"")))))</f>
         <v>46325</v>
       </c>
       <c r="AJ44" s="35">
         <v>46290</v>
       </c>
       <c r="AK44" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-25</v>
       </c>
       <c r="AL44" s="58"/>
     </row>
-    <row r="45" spans="1:38" ht="30" hidden="1" customHeight="1">
+    <row r="45" spans="1:38" ht="30" customHeight="1">
       <c r="A45" s="40">
         <v>43</v>
       </c>
@@ -16054,7 +16113,7 @@
         <v>129</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G45" s="68" t="s">
         <v>37</v>
@@ -16063,7 +16122,7 @@
         <v>130</v>
       </c>
       <c r="I45" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>136</v>
@@ -16098,7 +16157,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U45" s="33">
@@ -16129,7 +16188,7 @@
         <v>46262</v>
       </c>
       <c r="AE45" s="98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AF45" s="36">
         <v>10</v>
@@ -16141,19 +16200,19 @@
         <v>133</v>
       </c>
       <c r="AI45" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>46325</v>
       </c>
       <c r="AJ45" s="35">
         <v>46290</v>
       </c>
       <c r="AK45" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-25</v>
       </c>
       <c r="AL45" s="58"/>
     </row>
-    <row r="46" spans="1:38" ht="30" hidden="1" customHeight="1">
+    <row r="46" spans="1:38" ht="30" customHeight="1">
       <c r="A46" s="40">
         <v>44</v>
       </c>
@@ -16170,7 +16229,7 @@
         <v>129</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G46" s="68" t="s">
         <v>37</v>
@@ -16179,7 +16238,7 @@
         <v>130</v>
       </c>
       <c r="I46" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
@@ -16214,7 +16273,7 @@
         <v>-11</v>
       </c>
       <c r="T46" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U46" s="33">
@@ -16245,7 +16304,7 @@
         <v>46262</v>
       </c>
       <c r="AE46" s="98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AF46" s="36">
         <v>10</v>
@@ -16257,14 +16316,14 @@
         <v>133</v>
       </c>
       <c r="AI46" s="35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>46325</v>
       </c>
       <c r="AJ46" s="35">
         <v>46290</v>
       </c>
       <c r="AK46" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-25</v>
       </c>
       <c r="AL46" s="58"/>
@@ -16277,16 +16336,16 @@
         <v>46210</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G47" s="68" t="s">
         <v>40</v>
@@ -16295,7 +16354,7 @@
         <v>130</v>
       </c>
       <c r="I47" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2">
@@ -16323,7 +16382,7 @@
         <v/>
       </c>
       <c r="T47" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U47" s="33"/>
@@ -16334,12 +16393,12 @@
       </c>
       <c r="AH47" s="2"/>
       <c r="AK47" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL47" s="58"/>
     </row>
-    <row r="48" spans="1:38" ht="30" hidden="1" customHeight="1">
+    <row r="48" spans="1:38" ht="30" customHeight="1">
       <c r="A48" s="40">
         <v>46</v>
       </c>
@@ -16350,13 +16409,13 @@
         <v>127</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G48" s="68" t="s">
         <v>37</v>
@@ -16365,7 +16424,7 @@
         <v>130</v>
       </c>
       <c r="I48" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J48" s="2">
         <v>0</v>
@@ -16376,18 +16435,16 @@
       <c r="L48" s="33">
         <v>46211</v>
       </c>
-      <c r="M48" s="33">
-        <v>46211</v>
-      </c>
+      <c r="M48" s="33"/>
       <c r="N48" s="46">
         <v>0.95</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="P48" s="2">
+      <c r="P48" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q48" s="33"/>
       <c r="R48" s="33"/>
@@ -16396,18 +16453,19 @@
         <v/>
       </c>
       <c r="T48" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Yes</v>
+        <f t="shared" si="3"/>
+        <v>No</v>
       </c>
       <c r="U48" s="33"/>
       <c r="V48" s="33"/>
       <c r="W48" s="58"/>
+      <c r="AE48" s="33"/>
       <c r="AF48" s="36">
         <v>10</v>
       </c>
       <c r="AH48" s="2"/>
       <c r="AK48" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL48" s="58"/>
@@ -16423,13 +16481,13 @@
         <v>127</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G49" s="68" t="s">
         <v>37</v>
@@ -16438,7 +16496,7 @@
         <v>43</v>
       </c>
       <c r="I49" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2">
@@ -16448,9 +16506,7 @@
         <v>46211</v>
       </c>
       <c r="M49" s="33"/>
-      <c r="N49" s="46">
-        <v>0.95</v>
-      </c>
+      <c r="N49" s="46"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2" t="str">
         <f t="shared" si="0"/>
@@ -16463,8 +16519,8 @@
         <v/>
       </c>
       <c r="T49" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Yes</v>
+        <f t="shared" si="3"/>
+        <v>No</v>
       </c>
       <c r="U49" s="33"/>
       <c r="V49" s="33"/>
@@ -16474,12 +16530,12 @@
       </c>
       <c r="AH49" s="2"/>
       <c r="AK49" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL49" s="58"/>
     </row>
-    <row r="50" spans="1:43" ht="36.6" hidden="1" customHeight="1">
+    <row r="50" spans="1:43" ht="36.6" customHeight="1">
       <c r="A50" s="40">
         <v>48</v>
       </c>
@@ -16496,7 +16552,7 @@
         <v>129</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G50" s="68" t="s">
         <v>37</v>
@@ -16505,7 +16561,7 @@
         <v>43</v>
       </c>
       <c r="I50" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J50" s="2">
         <v>0</v>
@@ -16540,7 +16596,7 @@
         <v>-11</v>
       </c>
       <c r="T50" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="U50" s="33">
@@ -16562,7 +16618,7 @@
         <v>46244</v>
       </c>
       <c r="AE50" s="98" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AF50" s="36">
         <v>10</v>
@@ -16578,11 +16634,11 @@
         <v/>
       </c>
       <c r="AK50" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL50" s="58" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:43" ht="30" customHeight="1">
@@ -16596,13 +16652,13 @@
         <v>127</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G51" s="68" t="s">
         <v>37</v>
@@ -16611,9 +16667,11 @@
         <v>43</v>
       </c>
       <c r="I51" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="J51" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="K51" s="2">
         <v>1</v>
       </c>
@@ -16624,7 +16682,9 @@
       <c r="N51" s="46">
         <v>0</v>
       </c>
-      <c r="O51" s="2"/>
+      <c r="O51" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="P51" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16636,7 +16696,7 @@
         <v/>
       </c>
       <c r="T51" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>No</v>
       </c>
       <c r="U51" s="33"/>
@@ -16647,7 +16707,7 @@
       </c>
       <c r="AH51" s="2"/>
       <c r="AK51" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL51" s="58"/>
@@ -16660,16 +16720,16 @@
         <v>46210</v>
       </c>
       <c r="C52" s="25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G52" s="68" t="s">
         <v>40</v>
@@ -16678,7 +16738,7 @@
         <v>130</v>
       </c>
       <c r="I52" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2">
@@ -16705,7 +16765,7 @@
         <v/>
       </c>
       <c r="T52" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U52" s="33"/>
@@ -16716,12 +16776,12 @@
       </c>
       <c r="AH52" s="2"/>
       <c r="AK52" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL52" s="58"/>
     </row>
-    <row r="53" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="53" spans="1:43" ht="30" customHeight="1">
       <c r="A53" s="40">
         <v>51</v>
       </c>
@@ -16738,7 +16798,7 @@
         <v>129</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G53" s="68" t="s">
         <v>37</v>
@@ -16747,7 +16807,7 @@
         <v>130</v>
       </c>
       <c r="I53" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J53" s="2">
         <v>0</v>
@@ -16782,7 +16842,7 @@
         <v>-11</v>
       </c>
       <c r="T53" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U53" s="33">
@@ -16811,7 +16871,7 @@
         <v>46262</v>
       </c>
       <c r="AE53" s="98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF53" s="36">
         <v>10</v>
@@ -16823,24 +16883,24 @@
         <v>133</v>
       </c>
       <c r="AI53" s="35">
-        <f t="shared" ref="AI53:AI60" si="5">IF(OR(AD53="",AH53=""),"",WORKDAY(AD53,IF(AH53="Low",30,IF(AH53="Medium",45,IF(AH53="High",60,"")))))</f>
+        <f t="shared" ref="AI53:AI60" si="9">IF(OR(AD53="",AH53=""),"",WORKDAY(AD53,IF(AH53="Low",30,IF(AH53="Medium",45,IF(AH53="High",60,"")))))</f>
         <v>46325</v>
       </c>
       <c r="AK53" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL53" s="58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM53" s="35">
         <v>46286</v>
       </c>
-      <c r="AQ53" s="95" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" spans="1:43" ht="30" hidden="1" customHeight="1">
+      <c r="AQ53" s="99" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="54" spans="1:43" ht="30" customHeight="1">
       <c r="A54" s="40">
         <v>52</v>
       </c>
@@ -16857,7 +16917,7 @@
         <v>129</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G54" s="68" t="s">
         <v>37</v>
@@ -16866,7 +16926,7 @@
         <v>130</v>
       </c>
       <c r="I54" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J54" s="2">
         <v>0</v>
@@ -16901,7 +16961,7 @@
         <v>-11</v>
       </c>
       <c r="T54" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U54" s="33">
@@ -16930,7 +16990,7 @@
         <v>46262</v>
       </c>
       <c r="AE54" s="98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF54" s="36">
         <v>10</v>
@@ -16942,21 +17002,21 @@
         <v>133</v>
       </c>
       <c r="AI54" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>46325</v>
       </c>
       <c r="AK54" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL54" s="58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM54" s="35">
         <v>46286</v>
       </c>
     </row>
-    <row r="55" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="55" spans="1:43" ht="30" customHeight="1">
       <c r="A55" s="40">
         <v>53</v>
       </c>
@@ -16973,7 +17033,7 @@
         <v>129</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G55" s="68" t="s">
         <v>37</v>
@@ -16982,7 +17042,7 @@
         <v>130</v>
       </c>
       <c r="I55" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J55" s="2">
         <v>0</v>
@@ -17017,7 +17077,7 @@
         <v>-11</v>
       </c>
       <c r="T55" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U55" s="33">
@@ -17046,7 +17106,7 @@
         <v>46262</v>
       </c>
       <c r="AE55" s="98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF55" s="36">
         <v>10</v>
@@ -17058,21 +17118,21 @@
         <v>133</v>
       </c>
       <c r="AI55" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>46325</v>
       </c>
       <c r="AK55" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL55" s="58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM55" s="35">
         <v>46286</v>
       </c>
     </row>
-    <row r="56" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="56" spans="1:43" ht="30" customHeight="1">
       <c r="A56" s="40">
         <v>54</v>
       </c>
@@ -17089,7 +17149,7 @@
         <v>129</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G56" s="68" t="s">
         <v>37</v>
@@ -17098,7 +17158,7 @@
         <v>130</v>
       </c>
       <c r="I56" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J56" s="2">
         <v>0</v>
@@ -17133,7 +17193,7 @@
         <v>-11</v>
       </c>
       <c r="T56" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U56" s="33">
@@ -17162,7 +17222,7 @@
         <v>46262</v>
       </c>
       <c r="AE56" s="98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF56" s="36">
         <v>10</v>
@@ -17174,21 +17234,21 @@
         <v>133</v>
       </c>
       <c r="AI56" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>46325</v>
       </c>
       <c r="AK56" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL56" s="58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM56" s="35">
         <v>46286</v>
       </c>
     </row>
-    <row r="57" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="57" spans="1:43" ht="30" customHeight="1">
       <c r="A57" s="40">
         <v>55</v>
       </c>
@@ -17205,7 +17265,7 @@
         <v>129</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G57" s="68" t="s">
         <v>37</v>
@@ -17214,7 +17274,7 @@
         <v>130</v>
       </c>
       <c r="I57" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J57" s="2">
         <v>0</v>
@@ -17249,7 +17309,7 @@
         <v>-11</v>
       </c>
       <c r="T57" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U57" s="33">
@@ -17278,7 +17338,7 @@
         <v>46262</v>
       </c>
       <c r="AE57" s="98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF57" s="36">
         <v>10</v>
@@ -17290,21 +17350,21 @@
         <v>133</v>
       </c>
       <c r="AI57" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>46325</v>
       </c>
       <c r="AK57" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL57" s="58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM57" s="35">
         <v>46286</v>
       </c>
     </row>
-    <row r="58" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="58" spans="1:43" ht="30" customHeight="1">
       <c r="A58" s="40">
         <v>56</v>
       </c>
@@ -17321,7 +17381,7 @@
         <v>129</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G58" s="68" t="s">
         <v>37</v>
@@ -17330,7 +17390,7 @@
         <v>130</v>
       </c>
       <c r="I58" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J58" s="2">
         <v>0</v>
@@ -17365,7 +17425,7 @@
         <v>-11</v>
       </c>
       <c r="T58" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U58" s="33">
@@ -17394,7 +17454,7 @@
         <v>46262</v>
       </c>
       <c r="AE58" s="98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF58" s="36">
         <v>10</v>
@@ -17406,21 +17466,21 @@
         <v>133</v>
       </c>
       <c r="AI58" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>46325</v>
       </c>
       <c r="AK58" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL58" s="58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM58" s="35">
         <v>46286</v>
       </c>
     </row>
-    <row r="59" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="59" spans="1:43" ht="30" customHeight="1">
       <c r="A59" s="40">
         <v>57</v>
       </c>
@@ -17437,7 +17497,7 @@
         <v>129</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G59" s="68" t="s">
         <v>37</v>
@@ -17446,7 +17506,7 @@
         <v>130</v>
       </c>
       <c r="I59" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J59" s="2">
         <v>0</v>
@@ -17481,7 +17541,7 @@
         <v>-11</v>
       </c>
       <c r="T59" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U59" s="33">
@@ -17510,7 +17570,7 @@
         <v>46262</v>
       </c>
       <c r="AE59" s="98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF59" s="36">
         <v>10</v>
@@ -17522,21 +17582,21 @@
         <v>133</v>
       </c>
       <c r="AI59" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>46325</v>
       </c>
       <c r="AK59" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL59" s="58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM59" s="35">
         <v>46286</v>
       </c>
     </row>
-    <row r="60" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="60" spans="1:43" ht="30" customHeight="1">
       <c r="A60" s="40">
         <v>58</v>
       </c>
@@ -17553,7 +17613,7 @@
         <v>129</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G60" s="68" t="s">
         <v>37</v>
@@ -17562,7 +17622,7 @@
         <v>130</v>
       </c>
       <c r="I60" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J60" s="2">
         <v>0</v>
@@ -17597,7 +17657,7 @@
         <v>-11</v>
       </c>
       <c r="T60" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U60" s="33">
@@ -17626,7 +17686,7 @@
         <v>46262</v>
       </c>
       <c r="AE60" s="98" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AF60" s="36">
         <v>10</v>
@@ -17638,21 +17698,21 @@
         <v>133</v>
       </c>
       <c r="AI60" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>46325</v>
       </c>
       <c r="AK60" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL60" s="58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM60" s="35">
         <v>46286</v>
       </c>
     </row>
-    <row r="61" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="61" spans="1:43" ht="30" customHeight="1">
       <c r="A61" s="40">
         <v>59</v>
       </c>
@@ -17669,7 +17729,7 @@
         <v>129</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G61" s="68" t="s">
         <v>37</v>
@@ -17678,7 +17738,7 @@
         <v>130</v>
       </c>
       <c r="I61" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J61" s="2">
         <v>0</v>
@@ -17713,7 +17773,7 @@
         <v>-11</v>
       </c>
       <c r="T61" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U61" s="33">
@@ -17744,7 +17804,7 @@
         <v>46262</v>
       </c>
       <c r="AE61" s="98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AF61" s="36">
         <v>10</v>
@@ -17763,12 +17823,12 @@
         <v>46287</v>
       </c>
       <c r="AK61" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-13</v>
       </c>
       <c r="AL61" s="58"/>
     </row>
-    <row r="62" spans="1:43" ht="30" hidden="1" customHeight="1">
+    <row r="62" spans="1:43" ht="30" customHeight="1">
       <c r="A62" s="40">
         <v>60</v>
       </c>
@@ -17785,7 +17845,7 @@
         <v>129</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G62" s="68" t="s">
         <v>37</v>
@@ -17794,7 +17854,7 @@
         <v>130</v>
       </c>
       <c r="I62" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J62" s="2">
         <v>0</v>
@@ -17829,7 +17889,7 @@
         <v>-11</v>
       </c>
       <c r="T62" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U62" s="33">
@@ -17855,7 +17915,7 @@
         <v>46262</v>
       </c>
       <c r="AE62" s="98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AF62" s="36">
         <v>10</v>
@@ -17867,14 +17927,14 @@
         <v>141</v>
       </c>
       <c r="AI62" s="35">
-        <f t="shared" ref="AI62" si="6">IF(OR(AD62="",AH62=""),"",WORKDAY(AD62,IF(AH62="Low",30,IF(AH62="Medium",45,IF(AH62="High",60,"")))))</f>
+        <f t="shared" ref="AI62" si="10">IF(OR(AD62="",AH62=""),"",WORKDAY(AD62,IF(AH62="Low",30,IF(AH62="Medium",45,IF(AH62="High",60,"")))))</f>
         <v>46304</v>
       </c>
       <c r="AJ62" s="35">
         <v>46290</v>
       </c>
       <c r="AK62" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-10</v>
       </c>
       <c r="AL62" s="58"/>
@@ -17887,16 +17947,16 @@
         <v>46210</v>
       </c>
       <c r="C63" s="25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" s="25" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G63" s="68" t="s">
         <v>39</v>
@@ -17905,7 +17965,7 @@
         <v>43</v>
       </c>
       <c r="I63" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2">
@@ -17932,7 +17992,7 @@
         <v/>
       </c>
       <c r="T63" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U63" s="33"/>
@@ -17943,7 +18003,7 @@
       </c>
       <c r="AH63" s="2"/>
       <c r="AK63" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL63" s="58"/>
@@ -17956,16 +18016,16 @@
         <v>46210</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G64" s="68" t="s">
         <v>40</v>
@@ -17974,7 +18034,7 @@
         <v>130</v>
       </c>
       <c r="I64" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2">
@@ -18001,7 +18061,7 @@
         <v/>
       </c>
       <c r="T64" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U64" s="33"/>
@@ -18012,7 +18072,7 @@
       </c>
       <c r="AH64" s="2"/>
       <c r="AK64" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL64" s="58"/>
@@ -18025,16 +18085,16 @@
         <v>46210</v>
       </c>
       <c r="C65" s="25" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G65" s="68" t="s">
         <v>40</v>
@@ -18043,7 +18103,7 @@
         <v>130</v>
       </c>
       <c r="I65" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2">
@@ -18070,7 +18130,7 @@
         <v/>
       </c>
       <c r="T65" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U65" s="33"/>
@@ -18081,12 +18141,12 @@
       </c>
       <c r="AH65" s="2"/>
       <c r="AK65" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL65" s="58"/>
     </row>
-    <row r="66" spans="1:38" ht="30" hidden="1" customHeight="1">
+    <row r="66" spans="1:38" ht="30" customHeight="1">
       <c r="A66" s="40">
         <v>64</v>
       </c>
@@ -18097,13 +18157,13 @@
         <v>127</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G66" s="68" t="s">
         <v>37</v>
@@ -18112,7 +18172,7 @@
         <v>130</v>
       </c>
       <c r="I66" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>157</v>
@@ -18147,7 +18207,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U66" s="33">
@@ -18177,18 +18237,18 @@
         <v>154</v>
       </c>
       <c r="AI66" s="35" t="str">
-        <f t="shared" ref="AI66:AI67" si="7">IF(OR(AD66="",AH66=""),"",WORKDAY(AD66,IF(AH66="Low",30,IF(AH66="Medium",45,IF(AH66="High",60,"")))))</f>
+        <f t="shared" ref="AI66:AI67" si="11">IF(OR(AD66="",AH66=""),"",WORKDAY(AD66,IF(AH66="Low",30,IF(AH66="Medium",45,IF(AH66="High",60,"")))))</f>
         <v/>
       </c>
       <c r="AK66" s="37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AL66" s="58" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="67" spans="1:38" ht="30" hidden="1" customHeight="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" spans="1:38" ht="30" customHeight="1">
       <c r="A67" s="40">
         <v>65</v>
       </c>
@@ -18205,7 +18265,7 @@
         <v>129</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G67" s="68" t="s">
         <v>37</v>
@@ -18214,7 +18274,7 @@
         <v>130</v>
       </c>
       <c r="I67" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J67" s="2">
         <v>0</v>
@@ -18235,7 +18295,7 @@
         <v>131</v>
       </c>
       <c r="P67" s="2">
-        <f t="shared" ref="P67:P108" si="8">IF(OR(L67="",M67=""),"",SIGN(M67-L67)*(NETWORKDAYS(MIN(L67,M67),MAX(L67,M67))-1))</f>
+        <f t="shared" ref="P67:P108" si="12">IF(OR(L67="",M67=""),"",SIGN(M67-L67)*(NETWORKDAYS(MIN(L67,M67),MAX(L67,M67))-1))</f>
         <v>0</v>
       </c>
       <c r="Q67" s="33">
@@ -18245,11 +18305,11 @@
         <v>46218</v>
       </c>
       <c r="S67" s="34">
-        <f t="shared" ref="S67:S108" si="9">IF(OR(Q67="",R67=""),"",SIGN(R67-Q67)*(NETWORKDAYS(MIN(Q67,R67),MAX(Q67,R67))-1))</f>
+        <f t="shared" ref="S67:S108" si="13">IF(OR(Q67="",R67=""),"",SIGN(R67-Q67)*(NETWORKDAYS(MIN(Q67,R67),MAX(Q67,R67))-1))</f>
         <v>-11</v>
       </c>
       <c r="T67" s="2" t="str">
-        <f t="shared" ref="T67:T108" si="10">IF(AND(N67&gt;=90%,N67&lt;=100%),"Yes","No")</f>
+        <f t="shared" si="3"/>
         <v>Yes</v>
       </c>
       <c r="U67" s="33">
@@ -18278,7 +18338,7 @@
         <v>46262</v>
       </c>
       <c r="AE67" s="98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AF67" s="36">
         <v>10</v>
@@ -18290,14 +18350,14 @@
         <v>141</v>
       </c>
       <c r="AI67" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>46304</v>
       </c>
       <c r="AJ67" s="35">
         <v>46290</v>
       </c>
       <c r="AK67" s="37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>-10</v>
       </c>
       <c r="AL67" s="58"/>
@@ -18313,13 +18373,13 @@
         <v>127</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G68" s="68" t="s">
         <v>37</v>
@@ -18328,7 +18388,7 @@
         <v>130</v>
       </c>
       <c r="I68" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2">
@@ -18338,33 +18398,32 @@
         <v>46211</v>
       </c>
       <c r="M68" s="33"/>
-      <c r="N68" s="46">
-        <v>0.95</v>
-      </c>
+      <c r="N68" s="46"/>
       <c r="O68" s="2"/>
       <c r="P68" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q68" s="33"/>
       <c r="R68" s="33"/>
       <c r="S68" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T68" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v>Yes</v>
+        <f t="shared" ref="T68:T108" si="14">IF(AND(N68&gt;=90%,N68&lt;=100%,M68&lt;&gt;""),"Yes","No")</f>
+        <v>No</v>
       </c>
       <c r="U68" s="33"/>
       <c r="V68" s="33"/>
       <c r="W68" s="58"/>
+      <c r="AE68" s="33"/>
       <c r="AF68" s="36">
         <v>10</v>
       </c>
       <c r="AH68" s="2"/>
       <c r="AK68" s="37" t="str">
-        <f t="shared" ref="AK68:AK108" si="11">IF(OR(AI68="",AJ68=""),"",SIGN(AJ68-AI68)*(NETWORKDAYS(MIN(AI68,AJ68),MAX(AI68,AJ68))-1))</f>
+        <f t="shared" ref="AK68:AK108" si="15">IF(OR(AI68="",AJ68=""),"",SIGN(AJ68-AI68)*(NETWORKDAYS(MIN(AI68,AJ68),MAX(AI68,AJ68))-1))</f>
         <v/>
       </c>
       <c r="AL68" s="58"/>
@@ -18380,13 +18439,13 @@
         <v>127</v>
       </c>
       <c r="D69" s="25" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G69" s="68" t="s">
         <v>37</v>
@@ -18395,9 +18454,11 @@
         <v>43</v>
       </c>
       <c r="I69" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="J69" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="K69" s="2">
         <v>1</v>
       </c>
@@ -18406,22 +18467,24 @@
       </c>
       <c r="M69" s="33"/>
       <c r="N69" s="46">
-        <v>0.95</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="P69" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q69" s="33"/>
       <c r="R69" s="33"/>
       <c r="S69" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T69" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v>Yes</v>
+        <f t="shared" si="14"/>
+        <v>No</v>
       </c>
       <c r="U69" s="33"/>
       <c r="V69" s="33"/>
@@ -18431,7 +18494,7 @@
       </c>
       <c r="AH69" s="2"/>
       <c r="AK69" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL69" s="58"/>
@@ -18447,13 +18510,13 @@
         <v>127</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G70" s="68" t="s">
         <v>37</v>
@@ -18462,9 +18525,11 @@
         <v>43</v>
       </c>
       <c r="I70" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="J70" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="K70" s="2">
         <v>1</v>
       </c>
@@ -18475,19 +18540,21 @@
       <c r="N70" s="46">
         <v>0</v>
       </c>
-      <c r="O70" s="2"/>
+      <c r="O70" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="P70" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q70" s="33"/>
       <c r="R70" s="33"/>
       <c r="S70" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T70" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>No</v>
       </c>
       <c r="U70" s="33"/>
@@ -18498,7 +18565,7 @@
       </c>
       <c r="AH70" s="2"/>
       <c r="AK70" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL70" s="58"/>
@@ -18514,13 +18581,13 @@
         <v>127</v>
       </c>
       <c r="D71" s="25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G71" s="68" t="s">
         <v>37</v>
@@ -18529,9 +18596,11 @@
         <v>43</v>
       </c>
       <c r="I71" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="J71" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="K71" s="2">
         <v>1</v>
       </c>
@@ -18542,19 +18611,21 @@
       <c r="N71" s="46">
         <v>0</v>
       </c>
-      <c r="O71" s="2"/>
+      <c r="O71" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="P71" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q71" s="33"/>
       <c r="R71" s="33"/>
       <c r="S71" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T71" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>No</v>
       </c>
       <c r="U71" s="33"/>
@@ -18565,12 +18636,12 @@
       </c>
       <c r="AH71" s="2"/>
       <c r="AK71" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL71" s="58"/>
     </row>
-    <row r="72" spans="1:38" ht="30" hidden="1" customHeight="1">
+    <row r="72" spans="1:38" ht="30" customHeight="1">
       <c r="A72" s="40">
         <v>69</v>
       </c>
@@ -18587,7 +18658,7 @@
         <v>129</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G72" s="68" t="s">
         <v>37</v>
@@ -18596,7 +18667,7 @@
         <v>43</v>
       </c>
       <c r="I72" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>136</v>
@@ -18631,7 +18702,7 @@
         <v>5</v>
       </c>
       <c r="T72" s="2" t="str">
-        <f>IF(AND(N72&gt;=90%,N72&lt;=100%),"Yes","No")</f>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U72" s="33">
@@ -18662,13 +18733,13 @@
         <v>46276</v>
       </c>
       <c r="AE72" s="98" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AF72" s="36">
         <v>10</v>
       </c>
       <c r="AG72" s="35" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH72" s="2" t="s">
         <v>154</v>
@@ -18681,11 +18752,11 @@
         <v>46283</v>
       </c>
       <c r="AK72" s="37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>-55</v>
       </c>
       <c r="AL72" s="58" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="73" spans="1:38" ht="30" customHeight="1">
@@ -18699,13 +18770,13 @@
         <v>127</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G73" s="68" t="s">
         <v>37</v>
@@ -18714,7 +18785,7 @@
         <v>43</v>
       </c>
       <c r="I73" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2">
@@ -18724,22 +18795,20 @@
         <v>46211</v>
       </c>
       <c r="M73" s="33"/>
-      <c r="N73" s="46">
-        <v>0</v>
-      </c>
+      <c r="N73" s="46"/>
       <c r="O73" s="2"/>
       <c r="P73" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q73" s="33"/>
       <c r="R73" s="33"/>
       <c r="S73" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T73" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>No</v>
       </c>
       <c r="U73" s="33"/>
@@ -18750,7 +18819,7 @@
       </c>
       <c r="AH73" s="2"/>
       <c r="AK73" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL73" s="58"/>
@@ -18763,16 +18832,16 @@
         <v>46210</v>
       </c>
       <c r="C74" s="25" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G74" s="68" t="s">
         <v>40</v>
@@ -18781,7 +18850,7 @@
         <v>130</v>
       </c>
       <c r="I74" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2">
@@ -18798,17 +18867,17 @@
       </c>
       <c r="O74" s="2"/>
       <c r="P74" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q74" s="33"/>
       <c r="R74" s="33"/>
       <c r="S74" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T74" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U74" s="33"/>
@@ -18819,7 +18888,7 @@
       </c>
       <c r="AH74" s="2"/>
       <c r="AK74" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL74" s="58"/>
@@ -18835,13 +18904,13 @@
         <v>127</v>
       </c>
       <c r="D75" s="25" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G75" s="68" t="s">
         <v>37</v>
@@ -18850,7 +18919,7 @@
         <v>130</v>
       </c>
       <c r="I75" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2">
@@ -18860,33 +18929,32 @@
         <v>46211</v>
       </c>
       <c r="M75" s="33"/>
-      <c r="N75" s="46">
-        <v>0.95</v>
-      </c>
+      <c r="N75" s="46"/>
       <c r="O75" s="2"/>
       <c r="P75" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q75" s="33"/>
       <c r="R75" s="33"/>
       <c r="S75" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T75" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v>Yes</v>
+        <f t="shared" si="14"/>
+        <v>No</v>
       </c>
       <c r="U75" s="33"/>
       <c r="V75" s="33"/>
       <c r="W75" s="58"/>
+      <c r="AE75" s="33"/>
       <c r="AF75" s="36">
         <v>10</v>
       </c>
       <c r="AH75" s="2"/>
       <c r="AK75" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL75" s="58"/>
@@ -18899,16 +18967,16 @@
         <v>46210</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G76" s="68" t="s">
         <v>40</v>
@@ -18917,7 +18985,7 @@
         <v>130</v>
       </c>
       <c r="I76" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2">
@@ -18934,17 +19002,17 @@
       </c>
       <c r="O76" s="2"/>
       <c r="P76" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q76" s="33"/>
       <c r="R76" s="33"/>
       <c r="S76" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T76" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U76" s="33"/>
@@ -18955,7 +19023,7 @@
       </c>
       <c r="AH76" s="2"/>
       <c r="AK76" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL76" s="58"/>
@@ -18968,16 +19036,16 @@
         <v>46210</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G77" s="68" t="s">
         <v>40</v>
@@ -18986,7 +19054,7 @@
         <v>130</v>
       </c>
       <c r="I77" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2">
@@ -19003,17 +19071,17 @@
       </c>
       <c r="O77" s="2"/>
       <c r="P77" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q77" s="33"/>
       <c r="R77" s="33"/>
       <c r="S77" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T77" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U77" s="33"/>
@@ -19024,7 +19092,7 @@
       </c>
       <c r="AH77" s="2"/>
       <c r="AK77" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL77" s="58"/>
@@ -19037,16 +19105,16 @@
         <v>46210</v>
       </c>
       <c r="C78" s="25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G78" s="68" t="s">
         <v>40</v>
@@ -19055,7 +19123,7 @@
         <v>130</v>
       </c>
       <c r="I78" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2">
@@ -19072,17 +19140,17 @@
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q78" s="33"/>
       <c r="R78" s="33"/>
       <c r="S78" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T78" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U78" s="33"/>
@@ -19093,7 +19161,7 @@
       </c>
       <c r="AH78" s="2"/>
       <c r="AK78" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL78" s="58"/>
@@ -19106,16 +19174,16 @@
         <v>46210</v>
       </c>
       <c r="C79" s="25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D79" s="25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G79" s="68" t="s">
         <v>40</v>
@@ -19124,7 +19192,7 @@
         <v>130</v>
       </c>
       <c r="I79" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2">
@@ -19141,17 +19209,17 @@
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q79" s="33"/>
       <c r="R79" s="33"/>
       <c r="S79" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T79" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U79" s="33"/>
@@ -19162,7 +19230,7 @@
       </c>
       <c r="AH79" s="2"/>
       <c r="AK79" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL79" s="58"/>
@@ -19175,16 +19243,16 @@
         <v>46210</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G80" s="68" t="s">
         <v>40</v>
@@ -19193,7 +19261,7 @@
         <v>43</v>
       </c>
       <c r="I80" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2">
@@ -19210,17 +19278,17 @@
       </c>
       <c r="O80" s="2"/>
       <c r="P80" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q80" s="33"/>
       <c r="R80" s="33"/>
       <c r="S80" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T80" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U80" s="33"/>
@@ -19231,7 +19299,7 @@
       </c>
       <c r="AH80" s="2"/>
       <c r="AK80" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL80" s="58"/>
@@ -19244,16 +19312,16 @@
         <v>46210</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D81" s="25" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G81" s="68" t="s">
         <v>40</v>
@@ -19262,7 +19330,7 @@
         <v>43</v>
       </c>
       <c r="I81" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2">
@@ -19279,17 +19347,17 @@
       </c>
       <c r="O81" s="2"/>
       <c r="P81" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q81" s="33"/>
       <c r="R81" s="33"/>
       <c r="S81" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T81" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U81" s="33"/>
@@ -19300,7 +19368,7 @@
       </c>
       <c r="AH81" s="2"/>
       <c r="AK81" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL81" s="58"/>
@@ -19313,16 +19381,16 @@
         <v>46210</v>
       </c>
       <c r="C82" s="25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G82" s="68" t="s">
         <v>40</v>
@@ -19331,7 +19399,7 @@
         <v>43</v>
       </c>
       <c r="I82" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2">
@@ -19348,17 +19416,17 @@
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q82" s="33"/>
       <c r="R82" s="33"/>
       <c r="S82" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T82" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U82" s="33"/>
@@ -19369,7 +19437,7 @@
       </c>
       <c r="AH82" s="2"/>
       <c r="AK82" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL82" s="58"/>
@@ -19382,16 +19450,16 @@
         <v>46210</v>
       </c>
       <c r="C83" s="25" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D83" s="25" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G83" s="68" t="s">
         <v>40</v>
@@ -19400,7 +19468,7 @@
         <v>43</v>
       </c>
       <c r="I83" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2">
@@ -19417,17 +19485,17 @@
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q83" s="33"/>
       <c r="R83" s="33"/>
       <c r="S83" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T83" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U83" s="33"/>
@@ -19438,7 +19506,7 @@
       </c>
       <c r="AH83" s="2"/>
       <c r="AK83" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL83" s="58"/>
@@ -19451,16 +19519,16 @@
         <v>46210</v>
       </c>
       <c r="C84" s="25" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G84" s="68" t="s">
         <v>40</v>
@@ -19469,7 +19537,7 @@
         <v>130</v>
       </c>
       <c r="I84" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2">
@@ -19486,17 +19554,17 @@
       </c>
       <c r="O84" s="2"/>
       <c r="P84" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q84" s="33"/>
       <c r="R84" s="33"/>
       <c r="S84" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T84" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U84" s="33"/>
@@ -19507,7 +19575,7 @@
       </c>
       <c r="AH84" s="2"/>
       <c r="AK84" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL84" s="58"/>
@@ -19520,16 +19588,16 @@
         <v>46210</v>
       </c>
       <c r="C85" s="25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D85" s="25" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G85" s="68" t="s">
         <v>40</v>
@@ -19538,7 +19606,7 @@
         <v>130</v>
       </c>
       <c r="I85" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2">
@@ -19555,17 +19623,17 @@
       </c>
       <c r="O85" s="2"/>
       <c r="P85" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q85" s="33"/>
       <c r="R85" s="33"/>
       <c r="S85" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T85" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U85" s="33"/>
@@ -19576,7 +19644,7 @@
       </c>
       <c r="AH85" s="2"/>
       <c r="AK85" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL85" s="58"/>
@@ -19589,16 +19657,16 @@
         <v>46210</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G86" s="68" t="s">
         <v>40</v>
@@ -19607,7 +19675,7 @@
         <v>130</v>
       </c>
       <c r="I86" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2">
@@ -19624,17 +19692,17 @@
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q86" s="33"/>
       <c r="R86" s="33"/>
       <c r="S86" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T86" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U86" s="33"/>
@@ -19645,7 +19713,7 @@
       </c>
       <c r="AH86" s="2"/>
       <c r="AK86" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL86" s="58"/>
@@ -19658,16 +19726,16 @@
         <v>46210</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D87" s="25" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G87" s="68" t="s">
         <v>39</v>
@@ -19676,7 +19744,7 @@
         <v>43</v>
       </c>
       <c r="I87" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2">
@@ -19693,17 +19761,17 @@
       </c>
       <c r="O87" s="2"/>
       <c r="P87" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q87" s="33"/>
       <c r="R87" s="33"/>
       <c r="S87" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T87" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U87" s="33"/>
@@ -19714,7 +19782,7 @@
       </c>
       <c r="AH87" s="2"/>
       <c r="AK87" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL87" s="58"/>
@@ -19727,16 +19795,16 @@
         <v>46210</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G88" s="68" t="s">
         <v>40</v>
@@ -19745,7 +19813,7 @@
         <v>130</v>
       </c>
       <c r="I88" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2">
@@ -19762,17 +19830,17 @@
       </c>
       <c r="O88" s="2"/>
       <c r="P88" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q88" s="33"/>
       <c r="R88" s="33"/>
       <c r="S88" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T88" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U88" s="33"/>
@@ -19783,7 +19851,7 @@
       </c>
       <c r="AH88" s="2"/>
       <c r="AK88" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL88" s="58"/>
@@ -19796,16 +19864,16 @@
         <v>46210</v>
       </c>
       <c r="C89" s="25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D89" s="25" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G89" s="68" t="s">
         <v>40</v>
@@ -19814,7 +19882,7 @@
         <v>130</v>
       </c>
       <c r="I89" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2">
@@ -19831,17 +19899,17 @@
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q89" s="33"/>
       <c r="R89" s="33"/>
       <c r="S89" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T89" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U89" s="33"/>
@@ -19852,7 +19920,7 @@
       </c>
       <c r="AH89" s="2"/>
       <c r="AK89" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL89" s="58"/>
@@ -19865,16 +19933,16 @@
         <v>46210</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G90" s="68" t="s">
         <v>40</v>
@@ -19883,7 +19951,7 @@
         <v>43</v>
       </c>
       <c r="I90" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2">
@@ -19900,17 +19968,17 @@
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q90" s="33"/>
       <c r="R90" s="33"/>
       <c r="S90" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T90" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U90" s="33"/>
@@ -19921,7 +19989,7 @@
       </c>
       <c r="AH90" s="2"/>
       <c r="AK90" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL90" s="58"/>
@@ -19934,16 +20002,16 @@
         <v>46210</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G91" s="68" t="s">
         <v>40</v>
@@ -19952,7 +20020,7 @@
         <v>130</v>
       </c>
       <c r="I91" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2">
@@ -19969,17 +20037,17 @@
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q91" s="33"/>
       <c r="R91" s="33"/>
       <c r="S91" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T91" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U91" s="33"/>
@@ -19990,7 +20058,7 @@
       </c>
       <c r="AH91" s="2"/>
       <c r="AK91" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL91" s="58"/>
@@ -20003,16 +20071,16 @@
         <v>46210</v>
       </c>
       <c r="C92" s="25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G92" s="68" t="s">
         <v>40</v>
@@ -20021,7 +20089,7 @@
         <v>43</v>
       </c>
       <c r="I92" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2">
@@ -20038,17 +20106,17 @@
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q92" s="33"/>
       <c r="R92" s="33"/>
       <c r="S92" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T92" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U92" s="33"/>
@@ -20059,7 +20127,7 @@
       </c>
       <c r="AH92" s="2"/>
       <c r="AK92" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL92" s="58"/>
@@ -20072,16 +20140,16 @@
         <v>46210</v>
       </c>
       <c r="C93" s="25" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D93" s="25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G93" s="68" t="s">
         <v>40</v>
@@ -20090,7 +20158,7 @@
         <v>43</v>
       </c>
       <c r="I93" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J93" s="2"/>
       <c r="K93" s="2">
@@ -20107,17 +20175,17 @@
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q93" s="33"/>
       <c r="R93" s="33"/>
       <c r="S93" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T93" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U93" s="33"/>
@@ -20128,7 +20196,7 @@
       </c>
       <c r="AH93" s="2"/>
       <c r="AK93" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL93" s="58"/>
@@ -20141,16 +20209,16 @@
         <v>46210</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G94" s="68" t="s">
         <v>40</v>
@@ -20159,7 +20227,7 @@
         <v>43</v>
       </c>
       <c r="I94" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2">
@@ -20176,17 +20244,17 @@
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q94" s="33"/>
       <c r="R94" s="33"/>
       <c r="S94" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T94" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U94" s="33"/>
@@ -20197,7 +20265,7 @@
       </c>
       <c r="AH94" s="2"/>
       <c r="AK94" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL94" s="58"/>
@@ -20210,16 +20278,16 @@
         <v>46210</v>
       </c>
       <c r="C95" s="25" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D95" s="25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G95" s="68" t="s">
         <v>40</v>
@@ -20228,7 +20296,7 @@
         <v>43</v>
       </c>
       <c r="I95" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2">
@@ -20245,17 +20313,17 @@
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q95" s="33"/>
       <c r="R95" s="33"/>
       <c r="S95" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T95" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U95" s="33"/>
@@ -20266,7 +20334,7 @@
       </c>
       <c r="AH95" s="2"/>
       <c r="AK95" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL95" s="58"/>
@@ -20288,7 +20356,7 @@
         <v>129</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G96" s="68" t="s">
         <v>37</v>
@@ -20297,7 +20365,7 @@
         <v>43</v>
       </c>
       <c r="I96" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2">
@@ -20307,22 +20375,20 @@
         <v>46211</v>
       </c>
       <c r="M96" s="33"/>
-      <c r="N96" s="46">
-        <v>0</v>
-      </c>
+      <c r="N96" s="46"/>
       <c r="O96" s="2"/>
       <c r="P96" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q96" s="33"/>
       <c r="R96" s="33"/>
       <c r="S96" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T96" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>No</v>
       </c>
       <c r="U96" s="33"/>
@@ -20333,7 +20399,7 @@
       </c>
       <c r="AH96" s="2"/>
       <c r="AK96" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL96" s="58"/>
@@ -20349,13 +20415,13 @@
         <v>127</v>
       </c>
       <c r="D97" s="25" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G97" s="68" t="s">
         <v>37</v>
@@ -20364,7 +20430,7 @@
         <v>130</v>
       </c>
       <c r="I97" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2">
@@ -20374,33 +20440,32 @@
         <v>46211</v>
       </c>
       <c r="M97" s="33"/>
-      <c r="N97" s="46">
-        <v>0.75</v>
-      </c>
+      <c r="N97" s="46"/>
       <c r="O97" s="2"/>
       <c r="P97" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q97" s="33"/>
       <c r="R97" s="33"/>
       <c r="S97" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T97" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>No</v>
       </c>
       <c r="U97" s="33"/>
       <c r="V97" s="33"/>
       <c r="W97" s="58"/>
+      <c r="AE97" s="33"/>
       <c r="AF97" s="36">
         <v>10</v>
       </c>
       <c r="AH97" s="2"/>
       <c r="AK97" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL97" s="58"/>
@@ -20422,7 +20487,7 @@
         <v>129</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G98" s="68" t="s">
         <v>37</v>
@@ -20431,9 +20496,11 @@
         <v>43</v>
       </c>
       <c r="I98" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="J98" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="K98" s="2">
         <v>1</v>
       </c>
@@ -20444,19 +20511,21 @@
       <c r="N98" s="46">
         <v>0</v>
       </c>
-      <c r="O98" s="2"/>
+      <c r="O98" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="P98" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q98" s="33"/>
       <c r="R98" s="33"/>
       <c r="S98" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T98" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>No</v>
       </c>
       <c r="U98" s="33"/>
@@ -20467,7 +20536,7 @@
       </c>
       <c r="AH98" s="2"/>
       <c r="AK98" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL98" s="58"/>
@@ -20489,7 +20558,7 @@
         <v>129</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G99" s="68" t="s">
         <v>37</v>
@@ -20498,9 +20567,11 @@
         <v>43</v>
       </c>
       <c r="I99" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="J99" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="K99" s="2">
         <v>1</v>
       </c>
@@ -20511,19 +20582,21 @@
       <c r="N99" s="46">
         <v>0</v>
       </c>
-      <c r="O99" s="2"/>
+      <c r="O99" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="P99" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="Q99" s="33"/>
       <c r="R99" s="33"/>
       <c r="S99" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T99" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>No</v>
       </c>
       <c r="U99" s="33"/>
@@ -20534,7 +20607,7 @@
       </c>
       <c r="AH99" s="2"/>
       <c r="AK99" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL99" s="58"/>
@@ -20547,16 +20620,16 @@
         <v>46210</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G100" s="68" t="s">
         <v>40</v>
@@ -20565,7 +20638,7 @@
         <v>130</v>
       </c>
       <c r="I100" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2">
@@ -20582,17 +20655,17 @@
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q100" s="33"/>
       <c r="R100" s="33"/>
       <c r="S100" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T100" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U100" s="33"/>
@@ -20603,7 +20676,7 @@
       </c>
       <c r="AH100" s="2"/>
       <c r="AK100" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL100" s="58"/>
@@ -20616,16 +20689,16 @@
         <v>46210</v>
       </c>
       <c r="C101" s="25" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D101" s="25" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G101" s="68" t="s">
         <v>40</v>
@@ -20634,7 +20707,7 @@
         <v>130</v>
       </c>
       <c r="I101" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2">
@@ -20651,17 +20724,17 @@
       </c>
       <c r="O101" s="2"/>
       <c r="P101" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q101" s="33"/>
       <c r="R101" s="33"/>
       <c r="S101" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T101" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U101" s="33"/>
@@ -20672,7 +20745,7 @@
       </c>
       <c r="AH101" s="2"/>
       <c r="AK101" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL101" s="58"/>
@@ -20685,16 +20758,16 @@
         <v>46210</v>
       </c>
       <c r="C102" s="25" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D102" s="25" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G102" s="68" t="s">
         <v>40</v>
@@ -20703,7 +20776,7 @@
         <v>130</v>
       </c>
       <c r="I102" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2">
@@ -20720,17 +20793,17 @@
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q102" s="33"/>
       <c r="R102" s="33"/>
       <c r="S102" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T102" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U102" s="33"/>
@@ -20741,7 +20814,7 @@
       </c>
       <c r="AH102" s="2"/>
       <c r="AK102" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL102" s="58"/>
@@ -20754,16 +20827,16 @@
         <v>46210</v>
       </c>
       <c r="C103" s="25" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D103" s="25" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G103" s="68" t="s">
         <v>40</v>
@@ -20772,7 +20845,7 @@
         <v>130</v>
       </c>
       <c r="I103" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2">
@@ -20789,17 +20862,17 @@
       </c>
       <c r="O103" s="2"/>
       <c r="P103" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q103" s="33"/>
       <c r="R103" s="33"/>
       <c r="S103" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T103" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U103" s="33"/>
@@ -20810,7 +20883,7 @@
       </c>
       <c r="AH103" s="2"/>
       <c r="AK103" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL103" s="58"/>
@@ -20823,16 +20896,16 @@
         <v>46210</v>
       </c>
       <c r="C104" s="25" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D104" s="25" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G104" s="68" t="s">
         <v>40</v>
@@ -20841,7 +20914,7 @@
         <v>43</v>
       </c>
       <c r="I104" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2">
@@ -20858,17 +20931,17 @@
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q104" s="33"/>
       <c r="R104" s="33"/>
       <c r="S104" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T104" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U104" s="33"/>
@@ -20879,7 +20952,7 @@
       </c>
       <c r="AH104" s="2"/>
       <c r="AK104" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL104" s="58"/>
@@ -20892,16 +20965,16 @@
         <v>46210</v>
       </c>
       <c r="C105" s="25" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D105" s="25" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G105" s="68" t="s">
         <v>40</v>
@@ -20910,7 +20983,7 @@
         <v>130</v>
       </c>
       <c r="I105" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2">
@@ -20927,17 +21000,17 @@
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q105" s="33"/>
       <c r="R105" s="33"/>
       <c r="S105" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T105" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="U105" s="33"/>
@@ -20948,7 +21021,7 @@
       </c>
       <c r="AH105" s="2"/>
       <c r="AK105" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL105" s="58"/>
@@ -20961,16 +21034,16 @@
         <v>46210</v>
       </c>
       <c r="C106" s="25" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D106" s="25" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G106" s="68" t="s">
         <v>40</v>
@@ -20979,7 +21052,7 @@
         <v>130</v>
       </c>
       <c r="I106" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K106" s="36">
         <v>1</v>
@@ -20994,16 +21067,16 @@
         <v>1</v>
       </c>
       <c r="P106" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q106" s="33"/>
       <c r="S106" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T106" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="W106" s="59"/>
@@ -21012,7 +21085,7 @@
       </c>
       <c r="AH106" s="2"/>
       <c r="AK106" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL106" s="58"/>
@@ -21025,16 +21098,16 @@
         <v>46210</v>
       </c>
       <c r="C107" s="25" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G107" s="68" t="s">
         <v>40</v>
@@ -21043,7 +21116,7 @@
         <v>130</v>
       </c>
       <c r="I107" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K107" s="36">
         <v>4</v>
@@ -21058,16 +21131,16 @@
         <v>1</v>
       </c>
       <c r="P107" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q107" s="33"/>
       <c r="S107" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T107" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="AF107" s="36">
@@ -21075,7 +21148,7 @@
       </c>
       <c r="AH107" s="2"/>
       <c r="AK107" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL107" s="58"/>
@@ -21088,16 +21161,16 @@
         <v>46210</v>
       </c>
       <c r="C108" s="25" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D108" s="25" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G108" s="68" t="s">
         <v>40</v>
@@ -21106,7 +21179,7 @@
         <v>130</v>
       </c>
       <c r="I108" s="25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K108" s="36">
         <v>6</v>
@@ -21121,16 +21194,16 @@
         <v>1</v>
       </c>
       <c r="P108" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q108" s="33"/>
       <c r="S108" s="34" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T108" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Yes</v>
       </c>
       <c r="AF108" s="36">
@@ -21138,13 +21211,14 @@
       </c>
       <c r="AH108" s="2"/>
       <c r="AK108" s="37" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AL108" s="58"/>
     </row>
     <row r="109" spans="1:38" ht="30" customHeight="1">
       <c r="B109" s="33"/>
+      <c r="AE109" s="98"/>
     </row>
     <row r="110" spans="1:38" ht="30" hidden="1" customHeight="1"/>
     <row r="111" spans="1:38" ht="30" hidden="1" customHeight="1"/>
@@ -21236,11 +21310,7 @@
   <protectedRanges>
     <protectedRange sqref="A1:BD2" name="Range1"/>
   </protectedRanges>
-  <autoFilter ref="A2:BE108" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="14">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:BE108" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="6">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="X1:AL1"/>
@@ -21250,59 +21320,61 @@
     <mergeCell ref="Q1:W1"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="TBA">
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="TBA">
       <formula>NOT(ISERROR(SEARCH("TBA",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:F1048576">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="New">
+  <conditionalFormatting sqref="E1:F42 E44:F1048576">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="New">
       <formula>NOT(ISERROR(SEARCH("New",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="9" priority="15" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="containsText" dxfId="7" priority="14" operator="containsText" text="HW">
+    <cfRule type="containsText" dxfId="8" priority="16" operator="containsText" text="HW">
       <formula>NOT(ISERROR(SEARCH("HW",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="15" operator="containsText" text="Mech">
+    <cfRule type="containsText" dxfId="7" priority="17" operator="containsText" text="Mech">
       <formula>NOT(ISERROR(SEARCH("Mech",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1 P3:P1048576 S3:S1048576 AK3:AK1048576">
-    <cfRule type="cellIs" dxfId="5" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="23" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="24" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1 T2:V1048576">
-    <cfRule type="containsText" dxfId="3" priority="25" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="4" priority="27" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",Q1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH2:AH1048576">
-    <cfRule type="containsText" dxfId="2" priority="16" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="3" priority="18" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",AH2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="17" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="2" priority="19" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",AH2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="18" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="1" priority="20" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",AH2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E43:F43">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="New">
+      <formula>NOT(ISERROR(SEARCH("New",E43)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH3:AH66 AH68:AH108" xr:uid="{2860BD50-1D3D-4543-916D-CBCBA11A9533}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH68:AH108 AH3:AH66" xr:uid="{2860BD50-1D3D-4543-916D-CBCBA11A9533}">
       <formula1>"Low,Medium,High"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E108" xr:uid="{01565254-4645-463C-BFBE-FE90D6D41C51}">
-      <formula1>"New, Carryover"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F108" xr:uid="{AAE6EAB4-8338-4889-86DB-9CF4A4545E11}">
       <formula1>"Eruvaka"</formula1>
@@ -21313,10 +21385,13 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H108" xr:uid="{B10E67EC-BF30-401D-A760-C66D88C5B27F}">
       <formula1>"Mech, HW"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E108" xr:uid="{104ABBF6-8200-4C72-96B1-1742B6F8BB44}">
+      <formula1>"New, Carryover, In-House"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="AK50:AK66 AI23:AI72" emptyCellReference="1"/>
+    <ignoredError sqref="AK50:AK66 AI44:AI72 AI23:AI42" emptyCellReference="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -21342,7 +21417,7 @@
         <v>56</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>27</v>
@@ -21360,7 +21435,7 @@
         <v>31</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -21377,13 +21452,13 @@
         <v>136</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>136</v>
@@ -21397,22 +21472,22 @@
         <v>61</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -21423,22 +21498,22 @@
         <v>62</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -21449,22 +21524,22 @@
         <v>64</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -21475,22 +21550,22 @@
         <v>66</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E6" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>342</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -21501,22 +21576,22 @@
         <v>68</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>341</v>
-      </c>
       <c r="H7" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -21527,22 +21602,22 @@
         <v>70</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>341</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -21553,22 +21628,22 @@
         <v>72</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>343</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -21579,52 +21654,52 @@
         <v>74</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>341</v>
-      </c>
       <c r="G10" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="179"/>
-      <c r="B11" s="179"/>
-      <c r="C11" s="179"/>
-      <c r="D11" s="179"/>
-      <c r="E11" s="179"/>
-      <c r="F11" s="179"/>
-      <c r="G11" s="179"/>
-      <c r="H11" s="179"/>
+      <c r="A11" s="181"/>
+      <c r="B11" s="181"/>
+      <c r="C11" s="181"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="181"/>
+      <c r="F11" s="181"/>
+      <c r="G11" s="181"/>
+      <c r="H11" s="181"/>
     </row>
     <row r="12" spans="1:8" ht="14.45">
-      <c r="A12" s="176" t="s">
-        <v>346</v>
-      </c>
-      <c r="B12" s="177"/>
-      <c r="C12" s="177"/>
-      <c r="D12" s="177"/>
-      <c r="E12" s="177"/>
-      <c r="F12" s="177"/>
-      <c r="G12" s="177"/>
-      <c r="H12" s="178"/>
+      <c r="A12" s="178" t="s">
+        <v>348</v>
+      </c>
+      <c r="B12" s="179"/>
+      <c r="C12" s="179"/>
+      <c r="D12" s="179"/>
+      <c r="E12" s="179"/>
+      <c r="F12" s="179"/>
+      <c r="G12" s="179"/>
+      <c r="H12" s="180"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -21659,46 +21734,46 @@
   <sheetData>
     <row r="1" spans="1:14" s="29" customFormat="1" ht="29.1">
       <c r="A1" s="26" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B1" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J1" s="26" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K1" s="26" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N1" s="26" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="29.1">
@@ -21709,13 +21784,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F2" s="17"/>
       <c r="G2" s="17">
@@ -21729,7 +21804,7 @@
       </c>
       <c r="K2" s="25">
         <f ca="1">IF(H2&lt;&gt;"","",IF(G2="","",G2-TODAY()))</f>
-        <v>-43</v>
+        <v>-54</v>
       </c>
       <c r="L2" s="18" t="str">
         <f ca="1">IF(I2&lt;&gt;"","Completed",IF(G2&lt;TODAY(),"Delayed",IF(G2-TODAY()&lt;=7,"At Risk","On Track")))</f>
@@ -21746,13 +21821,13 @@
         <v>75</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>366</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>364</v>
       </c>
       <c r="F3" s="17">
         <v>46210</v>
@@ -21769,7 +21844,7 @@
       </c>
       <c r="K3" s="25">
         <f t="shared" ref="K3:K7" ca="1" si="1">IF(H3&lt;&gt;"","",IF(G3="","",G3-TODAY()))</f>
-        <v>-41</v>
+        <v>-52</v>
       </c>
       <c r="L3" s="18" t="str">
         <f t="shared" ref="L3:L7" ca="1" si="2">IF(I3&lt;&gt;"","Completed",IF(G3&lt;TODAY(),"Delayed",IF(G3-TODAY()&lt;=7,"At Risk","On Track")))</f>
@@ -21786,13 +21861,13 @@
         <v>29</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F4" s="17">
         <v>46234</v>
@@ -21808,7 +21883,7 @@
       </c>
       <c r="K4" s="25">
         <f t="shared" ca="1" si="1"/>
-        <v>-10</v>
+        <v>-21</v>
       </c>
       <c r="L4" s="18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21825,10 +21900,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E5" s="25" t="s">
         <v>67</v>
@@ -21860,13 +21935,13 @@
         <v>31</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
@@ -21892,16 +21967,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
@@ -21924,10 +21999,10 @@
     </row>
     <row r="9" spans="1:14" ht="21">
       <c r="B9" s="19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D9" s="27"/>
     </row>
